--- a/docs/Financial/BitWealth_Cashflow_Forecast_v3.0.xlsx
+++ b/docs/Financial/BitWealth_Cashflow_Forecast_v3.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davin\Dropbox\BitWealth\bitwealth-lth-pvr\bitwealth-lth-pvr\docs\Financial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95CE26E-C52F-4BA3-93EF-FD7A246FCE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82313866-EEEA-4D0F-8C4F-76B196BDE4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VARIABLES" sheetId="1" r:id="rId1"/>
@@ -1792,148 +1792,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>75000</c:v>
+                  <c:v>85500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25000</c:v>
+                  <c:v>28000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25000</c:v>
+                  <c:v>28000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>35000</c:v>
+                  <c:v>39500</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35000</c:v>
+                  <c:v>39500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>35000</c:v>
+                  <c:v>39500</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>78076.161941041079</c:v>
+                  <c:v>84076.161941041079</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>105683.11656524973</c:v>
+                  <c:v>111683.11656524973</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>147761.93104442907</c:v>
+                  <c:v>153761.93104442907</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>45000</c:v>
+                  <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>173607.01380170003</c:v>
+                  <c:v>179607.01380170003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2242,148 +2242,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>-79413.416666666657</c:v>
+                  <c:v>-91913.416666666657</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-56129.958333333321</c:v>
+                  <c:v>-73629.958333333314</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-68910.059895833328</c:v>
+                  <c:v>-91410.059895833314</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-90580.828300781242</c:v>
+                  <c:v>-119580.82830078123</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-111092.9171872233</c:v>
+                  <c:v>-146592.91718722327</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-130395.48275064139</c:v>
+                  <c:v>-172395.48275064136</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-158436.13826543221</c:v>
+                  <c:v>-208436.13826543221</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-185160.90722504893</c:v>
+                  <c:v>-243160.90722504893</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-210514.17505774955</c:v>
+                  <c:v>-276514.17505774955</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-234438.63937461621</c:v>
+                  <c:v>-308438.63937461621</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-256875.25870518904</c:v>
+                  <c:v>-338875.25870518904</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-310839.36161574017</c:v>
+                  <c:v>-400839.36161574017</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-330115.94451652374</c:v>
+                  <c:v>-428115.94451652374</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-347716.58722475677</c:v>
+                  <c:v>-453716.58722475677</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-363574.74741215992</c:v>
+                  <c:v>-477574.74741215992</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-377621.86300079082</c:v>
+                  <c:v>-499621.86300079082</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-389787.29080746014</c:v>
+                  <c:v>-519787.29080746014</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-399998.24332267971</c:v>
+                  <c:v>-537998.24332267977</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-408179.72356737242</c:v>
+                  <c:v>-554179.72356737242</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-414254.45796884462</c:v>
+                  <c:v>-568254.45796884468</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-418142.82719573984</c:v>
+                  <c:v>-580142.82719573984</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-419762.79488985555</c:v>
+                  <c:v>-589762.79488985555</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-419029.83423081349</c:v>
+                  <c:v>-597029.83423081355</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-476539.96883287263</c:v>
+                  <c:v>-662539.96883287269</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-470837.22851441678</c:v>
+                  <c:v>-664837.22851441684</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-462512.26834882231</c:v>
+                  <c:v>-664512.26834882237</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-451469.81961953692</c:v>
+                  <c:v>-661469.81961953698</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-437611.7210837414</c:v>
+                  <c:v>-655611.72108374152</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-420836.83107645658</c:v>
+                  <c:v>-646836.8310764567</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-401040.93694137014</c:v>
+                  <c:v>-635040.93694137025</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-378116.66170700151</c:v>
+                  <c:v>-620116.66170700162</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-351953.36792434397</c:v>
+                  <c:v>-601953.36792434403</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-322437.05857956631</c:v>
+                  <c:v>-580437.05857956631</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-289450.27499272407</c:v>
+                  <c:v>-555450.27499272407</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-252871.9916107161</c:v>
+                  <c:v>-526871.9916107161</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-315339.43864435412</c:v>
+                  <c:v>-597339.43864435412</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2580,148 +2580,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>8580.0833333333339</c:v>
+                  <c:v>10580.083333333334</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17160.166666666668</c:v>
+                  <c:v>21160.166666666668</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25740.25</c:v>
+                  <c:v>31740.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34320.333333333336</c:v>
+                  <c:v>42320.333333333336</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>42900.416666666672</c:v>
+                  <c:v>52900.416666666672</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51480.500000000007</c:v>
+                  <c:v>63480.500000000007</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>60060.583333333343</c:v>
+                  <c:v>74060.583333333343</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>68640.666666666672</c:v>
+                  <c:v>84640.666666666672</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>77220.75</c:v>
+                  <c:v>95220.75</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>85800.833333333328</c:v>
+                  <c:v>105800.83333333333</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>94380.916666666657</c:v>
+                  <c:v>116380.91666666666</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>102960.99999999999</c:v>
+                  <c:v>126960.99999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>111541.08333333331</c:v>
+                  <c:v>137541.08333333331</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>120121.16666666664</c:v>
+                  <c:v>148121.16666666666</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>128701.24999999997</c:v>
+                  <c:v>158701.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>137281.33333333331</c:v>
+                  <c:v>169281.33333333334</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>145861.41666666666</c:v>
+                  <c:v>179861.41666666669</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>154441.5</c:v>
+                  <c:v>190441.50000000003</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>163021.58333333334</c:v>
+                  <c:v>201021.58333333337</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>171601.66666666669</c:v>
+                  <c:v>211601.66666666672</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>180181.75000000003</c:v>
+                  <c:v>222181.75000000006</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>188761.83333333337</c:v>
+                  <c:v>232761.8333333334</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>197341.91666666672</c:v>
+                  <c:v>243341.91666666674</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>205922.00000000006</c:v>
+                  <c:v>253922.00000000009</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>214502.0833333334</c:v>
+                  <c:v>264502.08333333343</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>223082.16666666674</c:v>
+                  <c:v>275082.16666666674</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>231662.25000000009</c:v>
+                  <c:v>285662.25000000006</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>240242.33333333343</c:v>
+                  <c:v>296242.33333333337</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>248822.41666666677</c:v>
+                  <c:v>306822.41666666669</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>257402.50000000012</c:v>
+                  <c:v>317402.5</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>265982.58333333343</c:v>
+                  <c:v>327982.58333333331</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>274562.66666666674</c:v>
+                  <c:v>338562.66666666663</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>283142.75000000006</c:v>
+                  <c:v>349142.74999999994</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>291722.83333333337</c:v>
+                  <c:v>359722.83333333326</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>300302.91666666669</c:v>
+                  <c:v>370302.91666666657</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>308883</c:v>
+                  <c:v>380882.99999999988</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>291040.93894803978</c:v>
+                  <c:v>357040.93894803966</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>273685.72654334264</c:v>
+                  <c:v>333685.72654334252</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>256824.94537344034</c:v>
+                  <c:v>310824.94537344022</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>240466.23526744498</c:v>
+                  <c:v>288466.23526744486</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>224617.29372838471</c:v>
+                  <c:v>266617.2937283846</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>209285.87636880667</c:v>
+                  <c:v>245285.87636880655</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>194479.79734967154</c:v>
+                  <c:v>224479.79734967143</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>180206.92982256491</c:v>
+                  <c:v>204206.92982256479</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>166475.20637525042</c:v>
+                  <c:v>184475.2063752503</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>153292.6194805897</c:v>
+                  <c:v>165292.61948058958</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>140667.22194885515</c:v>
+                  <c:v>146667.22194885503</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.11358176049543545</c:v>
+                  <c:v>0.11358176037902012</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3279,8 +3279,8 @@
         <v>9</v>
       </c>
       <c r="B9" s="6">
-        <f>308883/36</f>
-        <v>8580.0833333333339</v>
+        <f>380883/36</f>
+        <v>10580.083333333334</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
@@ -3298,7 +3298,8 @@
         <v>12</v>
       </c>
       <c r="B12" s="6">
-        <v>50000</v>
+        <f>50000*1.15</f>
+        <v>57499.999999999993</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>13</v>
@@ -3309,7 +3310,8 @@
         <v>14</v>
       </c>
       <c r="B13" s="6">
-        <v>20000</v>
+        <f>20000*1.15</f>
+        <v>23000</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>15</v>
@@ -3320,7 +3322,8 @@
         <v>16</v>
       </c>
       <c r="B14" s="6">
-        <v>30000</v>
+        <f>30000*1.15</f>
+        <v>34500</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>15</v>
@@ -3331,7 +3334,8 @@
         <v>17</v>
       </c>
       <c r="B15" s="6">
-        <v>40000</v>
+        <f>40000*1.15</f>
+        <v>46000</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>18</v>
@@ -3773,24 +3777,23 @@
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" customWidth="1"/>
     <col min="3" max="3" width="8" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="6" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="10" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="14" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="18" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="8" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="23" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="14" style="2" customWidth="1" collapsed="1"/>
-    <col min="26" max="27" width="14" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="6" width="12" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="14" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="13" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="10" width="12" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="14" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="13" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="14" width="12" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="14" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="13" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="18" width="12" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="14" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="8" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="14" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="23" width="12" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="14" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="27" width="14" style="2" customWidth="1"/>
     <col min="28" max="28" width="15" style="2" customWidth="1"/>
     <col min="29" max="29" width="16" style="2" customWidth="1"/>
     <col min="30" max="30" width="14" style="2" customWidth="1"/>
@@ -4140,11 +4143,11 @@
       </c>
       <c r="AD4" s="7">
         <f>IF($A4=1,VARIABLES!$B$12,0)</f>
-        <v>50000</v>
+        <v>57499.999999999993</v>
       </c>
       <c r="AE4" s="7">
         <f>IF($A4&lt;=3,VARIABLES!$B$13,IF($A4&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="AF4" s="7">
         <f>IF(MOD($A4,12)=0,AC4*VARIABLES!$B$16,0)</f>
@@ -4160,23 +4163,23 @@
       </c>
       <c r="AI4" s="19">
         <f t="shared" ref="AI4:AI51" si="5">AD4+AE4+AF4+AG4+AH4</f>
-        <v>75000</v>
+        <v>85500</v>
       </c>
       <c r="AJ4" s="20">
         <f>IF($A4&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK4" s="21">
         <f t="shared" ref="AK4:AK51" si="6">AB4-AI4-AJ4</f>
-        <v>-79413.416666666657</v>
+        <v>-91913.416666666657</v>
       </c>
       <c r="AL4" s="21">
         <f>AK4</f>
-        <v>-79413.416666666657</v>
+        <v>-91913.416666666657</v>
       </c>
       <c r="AM4" s="22">
         <f>AJ4</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.2">
@@ -4301,7 +4304,7 @@
       </c>
       <c r="AE5" s="25">
         <f>IF($A5&lt;=3,VARIABLES!$B$13,IF($A5&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="AF5" s="25">
         <f>IF(MOD($A5,12)=0,AC5*VARIABLES!$B$16,0)</f>
@@ -4317,23 +4320,23 @@
       </c>
       <c r="AI5" s="19">
         <f t="shared" si="5"/>
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="AJ5" s="20">
         <f>IF($A5&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK5" s="27">
         <f t="shared" si="6"/>
-        <v>23283.458333333336</v>
+        <v>18283.458333333336</v>
       </c>
       <c r="AL5" s="27">
         <f t="shared" ref="AL5:AL51" si="7">IF(AJ5&gt;0,AL4+AK5,AL4)</f>
-        <v>-56129.958333333321</v>
+        <v>-73629.958333333314</v>
       </c>
       <c r="AM5" s="22">
         <f t="shared" ref="AM5:AM51" si="8">IF(AJ5&gt;0,AM4+AJ5,AM4+AK5)</f>
-        <v>17160.166666666668</v>
+        <v>21160.166666666668</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
@@ -4458,7 +4461,7 @@
       </c>
       <c r="AE6" s="7">
         <f>IF($A6&lt;=3,VARIABLES!$B$13,IF($A6&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="AF6" s="7">
         <f>IF(MOD($A6,12)=0,AC6*VARIABLES!$B$16,0)</f>
@@ -4474,23 +4477,23 @@
       </c>
       <c r="AI6" s="19">
         <f t="shared" si="5"/>
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="AJ6" s="20">
         <f>IF($A6&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" si="6"/>
-        <v>-12780.101562500002</v>
+        <v>-17780.1015625</v>
       </c>
       <c r="AL6" s="21">
         <f t="shared" si="7"/>
-        <v>-68910.059895833328</v>
+        <v>-91410.059895833314</v>
       </c>
       <c r="AM6" s="22">
         <f t="shared" si="8"/>
-        <v>25740.25</v>
+        <v>31740.25</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.2">
@@ -4615,7 +4618,7 @@
       </c>
       <c r="AE7" s="25">
         <f>IF($A7&lt;=3,VARIABLES!$B$13,IF($A7&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>30000</v>
+        <v>34500</v>
       </c>
       <c r="AF7" s="25">
         <f>IF(MOD($A7,12)=0,AC7*VARIABLES!$B$16,0)</f>
@@ -4631,23 +4634,23 @@
       </c>
       <c r="AI7" s="19">
         <f t="shared" si="5"/>
-        <v>35000</v>
+        <v>39500</v>
       </c>
       <c r="AJ7" s="20">
         <f>IF($A7&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK7" s="27">
         <f t="shared" si="6"/>
-        <v>-21670.768404947914</v>
+        <v>-28170.768404947914</v>
       </c>
       <c r="AL7" s="27">
         <f t="shared" si="7"/>
-        <v>-90580.828300781242</v>
+        <v>-119580.82830078123</v>
       </c>
       <c r="AM7" s="22">
         <f t="shared" si="8"/>
-        <v>34320.333333333336</v>
+        <v>42320.333333333336</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.2">
@@ -4772,7 +4775,7 @@
       </c>
       <c r="AE8" s="7">
         <f>IF($A8&lt;=3,VARIABLES!$B$13,IF($A8&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>30000</v>
+        <v>34500</v>
       </c>
       <c r="AF8" s="7">
         <f>IF(MOD($A8,12)=0,AC8*VARIABLES!$B$16,0)</f>
@@ -4788,23 +4791,23 @@
       </c>
       <c r="AI8" s="19">
         <f t="shared" si="5"/>
-        <v>35000</v>
+        <v>39500</v>
       </c>
       <c r="AJ8" s="20">
         <f>IF($A8&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="6"/>
-        <v>-20512.088886442056</v>
+        <v>-27012.088886442056</v>
       </c>
       <c r="AL8" s="21">
         <f t="shared" si="7"/>
-        <v>-111092.9171872233</v>
+        <v>-146592.91718722327</v>
       </c>
       <c r="AM8" s="22">
         <f t="shared" si="8"/>
-        <v>42900.416666666672</v>
+        <v>52900.416666666672</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.2">
@@ -4929,7 +4932,7 @@
       </c>
       <c r="AE9" s="25">
         <f>IF($A9&lt;=3,VARIABLES!$B$13,IF($A9&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>30000</v>
+        <v>34500</v>
       </c>
       <c r="AF9" s="25">
         <f>IF(MOD($A9,12)=0,AC9*VARIABLES!$B$16,0)</f>
@@ -4945,23 +4948,23 @@
       </c>
       <c r="AI9" s="19">
         <f t="shared" si="5"/>
-        <v>35000</v>
+        <v>39500</v>
       </c>
       <c r="AJ9" s="20">
         <f>IF($A9&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK9" s="27">
         <f t="shared" si="6"/>
-        <v>-19302.565563418088</v>
+        <v>-25802.565563418088</v>
       </c>
       <c r="AL9" s="27">
         <f t="shared" si="7"/>
-        <v>-130395.48275064139</v>
+        <v>-172395.48275064136</v>
       </c>
       <c r="AM9" s="22">
         <f t="shared" si="8"/>
-        <v>51480.500000000007</v>
+        <v>63480.500000000007</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.2">
@@ -5086,7 +5089,7 @@
       </c>
       <c r="AE10" s="7">
         <f>IF($A10&lt;=3,VARIABLES!$B$13,IF($A10&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF10" s="7">
         <f>IF(MOD($A10,12)=0,AC10*VARIABLES!$B$16,0)</f>
@@ -5102,23 +5105,23 @@
       </c>
       <c r="AI10" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ10" s="20">
         <f>IF($A10&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="6"/>
-        <v>-28040.655514790837</v>
+        <v>-36040.655514790837</v>
       </c>
       <c r="AL10" s="21">
         <f t="shared" si="7"/>
-        <v>-158436.13826543221</v>
+        <v>-208436.13826543221</v>
       </c>
       <c r="AM10" s="22">
         <f t="shared" si="8"/>
-        <v>60060.583333333343</v>
+        <v>74060.583333333343</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.2">
@@ -5243,7 +5246,7 @@
       </c>
       <c r="AE11" s="25">
         <f>IF($A11&lt;=3,VARIABLES!$B$13,IF($A11&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF11" s="25">
         <f>IF(MOD($A11,12)=0,AC11*VARIABLES!$B$16,0)</f>
@@ -5259,23 +5262,23 @@
       </c>
       <c r="AI11" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ11" s="20">
         <f>IF($A11&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK11" s="27">
         <f t="shared" si="6"/>
-        <v>-26724.768959616718</v>
+        <v>-34724.768959616718</v>
       </c>
       <c r="AL11" s="27">
         <f t="shared" si="7"/>
-        <v>-185160.90722504893</v>
+        <v>-243160.90722504893</v>
       </c>
       <c r="AM11" s="22">
         <f t="shared" si="8"/>
-        <v>68640.666666666672</v>
+        <v>84640.666666666672</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.2">
@@ -5400,7 +5403,7 @@
       </c>
       <c r="AE12" s="7">
         <f>IF($A12&lt;=3,VARIABLES!$B$13,IF($A12&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF12" s="7">
         <f>IF(MOD($A12,12)=0,AC12*VARIABLES!$B$16,0)</f>
@@ -5416,23 +5419,23 @@
       </c>
       <c r="AI12" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ12" s="20">
         <f>IF($A12&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="6"/>
-        <v>-25353.267832700629</v>
+        <v>-33353.267832700629</v>
       </c>
       <c r="AL12" s="21">
         <f t="shared" si="7"/>
-        <v>-210514.17505774955</v>
+        <v>-276514.17505774955</v>
       </c>
       <c r="AM12" s="22">
         <f t="shared" si="8"/>
-        <v>77220.75</v>
+        <v>95220.75</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.2">
@@ -5557,7 +5560,7 @@
       </c>
       <c r="AE13" s="25">
         <f>IF($A13&lt;=3,VARIABLES!$B$13,IF($A13&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF13" s="25">
         <f>IF(MOD($A13,12)=0,AC13*VARIABLES!$B$16,0)</f>
@@ -5573,23 +5576,23 @@
       </c>
       <c r="AI13" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ13" s="20">
         <f>IF($A13&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK13" s="27">
         <f t="shared" si="6"/>
-        <v>-23924.464316866666</v>
+        <v>-31924.464316866666</v>
       </c>
       <c r="AL13" s="27">
         <f t="shared" si="7"/>
-        <v>-234438.63937461621</v>
+        <v>-308438.63937461621</v>
       </c>
       <c r="AM13" s="22">
         <f t="shared" si="8"/>
-        <v>85800.833333333328</v>
+        <v>105800.83333333333</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.2">
@@ -5714,7 +5717,7 @@
       </c>
       <c r="AE14" s="7">
         <f>IF($A14&lt;=3,VARIABLES!$B$13,IF($A14&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF14" s="7">
         <f>IF(MOD($A14,12)=0,AC14*VARIABLES!$B$16,0)</f>
@@ -5730,23 +5733,23 @@
       </c>
       <c r="AI14" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ14" s="20">
         <f>IF($A14&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="6"/>
-        <v>-22436.619330572852</v>
+        <v>-30436.619330572852</v>
       </c>
       <c r="AL14" s="21">
         <f t="shared" si="7"/>
-        <v>-256875.25870518904</v>
+        <v>-338875.25870518904</v>
       </c>
       <c r="AM14" s="22">
         <f t="shared" si="8"/>
-        <v>94380.916666666657</v>
+        <v>116380.91666666666</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.2">
@@ -5871,7 +5874,7 @@
       </c>
       <c r="AE15" s="25">
         <f>IF($A15&lt;=3,VARIABLES!$B$13,IF($A15&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF15" s="25">
         <f>IF(MOD($A15,12)=0,AC15*VARIABLES!$B$16,0)</f>
@@ -5887,23 +5890,23 @@
       </c>
       <c r="AI15" s="19">
         <f t="shared" si="5"/>
-        <v>78076.161941041079</v>
+        <v>84076.161941041079</v>
       </c>
       <c r="AJ15" s="20">
         <f>IF($A15&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK15" s="27">
         <f t="shared" si="6"/>
-        <v>-53964.102910551148</v>
+        <v>-61964.102910551148</v>
       </c>
       <c r="AL15" s="27">
         <f t="shared" si="7"/>
-        <v>-310839.36161574017</v>
+        <v>-400839.36161574017</v>
       </c>
       <c r="AM15" s="22">
         <f t="shared" si="8"/>
-        <v>102960.99999999999</v>
+        <v>126960.99999999999</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.2">
@@ -6028,7 +6031,7 @@
       </c>
       <c r="AE16" s="7">
         <f>IF($A16&lt;=3,VARIABLES!$B$13,IF($A16&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF16" s="7">
         <f>IF(MOD($A16,12)=0,AC16*VARIABLES!$B$16,0)</f>
@@ -6044,23 +6047,23 @@
       </c>
       <c r="AI16" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ16" s="20">
         <f>IF($A16&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK16" s="21">
         <f t="shared" si="6"/>
-        <v>-19276.582900783564</v>
+        <v>-27276.582900783564</v>
       </c>
       <c r="AL16" s="21">
         <f t="shared" si="7"/>
-        <v>-330115.94451652374</v>
+        <v>-428115.94451652374</v>
       </c>
       <c r="AM16" s="22">
         <f t="shared" si="8"/>
-        <v>111541.08333333331</v>
+        <v>137541.08333333331</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.2">
@@ -6185,7 +6188,7 @@
       </c>
       <c r="AE17" s="25">
         <f>IF($A17&lt;=3,VARIABLES!$B$13,IF($A17&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF17" s="25">
         <f>IF(MOD($A17,12)=0,AC17*VARIABLES!$B$16,0)</f>
@@ -6201,23 +6204,23 @@
       </c>
       <c r="AI17" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ17" s="20">
         <f>IF($A17&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK17" s="27">
         <f t="shared" si="6"/>
-        <v>-17600.642708233034</v>
+        <v>-25600.642708233034</v>
       </c>
       <c r="AL17" s="27">
         <f t="shared" si="7"/>
-        <v>-347716.58722475677</v>
+        <v>-453716.58722475677</v>
       </c>
       <c r="AM17" s="22">
         <f t="shared" si="8"/>
-        <v>120121.16666666664</v>
+        <v>148121.16666666666</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.2">
@@ -6342,7 +6345,7 @@
       </c>
       <c r="AE18" s="7">
         <f>IF($A18&lt;=3,VARIABLES!$B$13,IF($A18&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF18" s="7">
         <f>IF(MOD($A18,12)=0,AC18*VARIABLES!$B$16,0)</f>
@@ -6358,23 +6361,23 @@
       </c>
       <c r="AI18" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ18" s="20">
         <f>IF($A18&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="6"/>
-        <v>-15858.160187403168</v>
+        <v>-23858.160187403169</v>
       </c>
       <c r="AL18" s="21">
         <f t="shared" si="7"/>
-        <v>-363574.74741215992</v>
+        <v>-477574.74741215992</v>
       </c>
       <c r="AM18" s="22">
         <f t="shared" si="8"/>
-        <v>128701.24999999997</v>
+        <v>158701.25</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.2">
@@ -6499,7 +6502,7 @@
       </c>
       <c r="AE19" s="25">
         <f>IF($A19&lt;=3,VARIABLES!$B$13,IF($A19&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF19" s="25">
         <f>IF(MOD($A19,12)=0,AC19*VARIABLES!$B$16,0)</f>
@@ -6515,23 +6518,23 @@
       </c>
       <c r="AI19" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ19" s="20">
         <f>IF($A19&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK19" s="27">
         <f t="shared" si="6"/>
-        <v>-14047.115588630897</v>
+        <v>-22047.115588630899</v>
       </c>
       <c r="AL19" s="27">
         <f t="shared" si="7"/>
-        <v>-377621.86300079082</v>
+        <v>-499621.86300079082</v>
       </c>
       <c r="AM19" s="22">
         <f t="shared" si="8"/>
-        <v>137281.33333333331</v>
+        <v>169281.33333333334</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.2">
@@ -6656,7 +6659,7 @@
       </c>
       <c r="AE20" s="7">
         <f>IF($A20&lt;=3,VARIABLES!$B$13,IF($A20&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF20" s="7">
         <f>IF(MOD($A20,12)=0,AC20*VARIABLES!$B$16,0)</f>
@@ -6672,23 +6675,23 @@
       </c>
       <c r="AI20" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ20" s="20">
         <f>IF($A20&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="6"/>
-        <v>-12165.427806669313</v>
+        <v>-20165.427806669315</v>
       </c>
       <c r="AL20" s="21">
         <f t="shared" si="7"/>
-        <v>-389787.29080746014</v>
+        <v>-519787.29080746014</v>
       </c>
       <c r="AM20" s="22">
         <f t="shared" si="8"/>
-        <v>145861.41666666666</v>
+        <v>179861.41666666669</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.2">
@@ -6813,7 +6816,7 @@
       </c>
       <c r="AE21" s="25">
         <f>IF($A21&lt;=3,VARIABLES!$B$13,IF($A21&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF21" s="25">
         <f>IF(MOD($A21,12)=0,AC21*VARIABLES!$B$16,0)</f>
@@ -6829,23 +6832,23 @@
       </c>
       <c r="AI21" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ21" s="20">
         <f>IF($A21&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK21" s="27">
         <f t="shared" si="6"/>
-        <v>-10210.952515219569</v>
+        <v>-18210.952515219571</v>
       </c>
       <c r="AL21" s="27">
         <f t="shared" si="7"/>
-        <v>-399998.24332267971</v>
+        <v>-537998.24332267977</v>
       </c>
       <c r="AM21" s="22">
         <f t="shared" si="8"/>
-        <v>154441.5</v>
+        <v>190441.50000000003</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.2">
@@ -6970,7 +6973,7 @@
       </c>
       <c r="AE22" s="7">
         <f>IF($A22&lt;=3,VARIABLES!$B$13,IF($A22&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF22" s="7">
         <f>IF(MOD($A22,12)=0,AC22*VARIABLES!$B$16,0)</f>
@@ -6986,23 +6989,23 @@
       </c>
       <c r="AI22" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ22" s="20">
         <f>IF($A22&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK22" s="21">
         <f t="shared" si="6"/>
-        <v>-8181.4802446926897</v>
+        <v>-16181.48024469269</v>
       </c>
       <c r="AL22" s="21">
         <f t="shared" si="7"/>
-        <v>-408179.72356737242</v>
+        <v>-554179.72356737242</v>
       </c>
       <c r="AM22" s="22">
         <f t="shared" si="8"/>
-        <v>163021.58333333334</v>
+        <v>201021.58333333337</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.2">
@@ -7127,7 +7130,7 @@
       </c>
       <c r="AE23" s="25">
         <f>IF($A23&lt;=3,VARIABLES!$B$13,IF($A23&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF23" s="25">
         <f>IF(MOD($A23,12)=0,AC23*VARIABLES!$B$16,0)</f>
@@ -7143,23 +7146,23 @@
       </c>
       <c r="AI23" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ23" s="20">
         <f>IF($A23&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK23" s="27">
         <f t="shared" si="6"/>
-        <v>-6074.7344014722094</v>
+        <v>-14074.734401472209</v>
       </c>
       <c r="AL23" s="27">
         <f t="shared" si="7"/>
-        <v>-414254.45796884462</v>
+        <v>-568254.45796884468</v>
       </c>
       <c r="AM23" s="22">
         <f t="shared" si="8"/>
-        <v>171601.66666666669</v>
+        <v>211601.66666666672</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.2">
@@ -7284,7 +7287,7 @@
       </c>
       <c r="AE24" s="7">
         <f>IF($A24&lt;=3,VARIABLES!$B$13,IF($A24&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF24" s="7">
         <f>IF(MOD($A24,12)=0,AC24*VARIABLES!$B$16,0)</f>
@@ -7300,23 +7303,23 @@
       </c>
       <c r="AI24" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ24" s="20">
         <f>IF($A24&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="6"/>
-        <v>-3888.3692268952127</v>
+        <v>-11888.369226895213</v>
       </c>
       <c r="AL24" s="21">
         <f t="shared" si="7"/>
-        <v>-418142.82719573984</v>
+        <v>-580142.82719573984</v>
       </c>
       <c r="AM24" s="22">
         <f t="shared" si="8"/>
-        <v>180181.75000000003</v>
+        <v>222181.75000000006</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.2">
@@ -7441,7 +7444,7 @@
       </c>
       <c r="AE25" s="25">
         <f>IF($A25&lt;=3,VARIABLES!$B$13,IF($A25&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF25" s="25">
         <f>IF(MOD($A25,12)=0,AC25*VARIABLES!$B$16,0)</f>
@@ -7457,23 +7460,23 @@
       </c>
       <c r="AI25" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ25" s="20">
         <f>IF($A25&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK25" s="27">
         <f t="shared" si="6"/>
-        <v>-1619.9676941157286</v>
+        <v>-9619.9676941157286</v>
       </c>
       <c r="AL25" s="27">
         <f t="shared" si="7"/>
-        <v>-419762.79488985555</v>
+        <v>-589762.79488985555</v>
       </c>
       <c r="AM25" s="22">
         <f t="shared" si="8"/>
-        <v>188761.83333333337</v>
+        <v>232761.8333333334</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.2">
@@ -7598,7 +7601,7 @@
       </c>
       <c r="AE26" s="7">
         <f>IF($A26&lt;=3,VARIABLES!$B$13,IF($A26&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF26" s="7">
         <f>IF(MOD($A26,12)=0,AC26*VARIABLES!$B$16,0)</f>
@@ -7614,23 +7617,23 @@
       </c>
       <c r="AI26" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ26" s="20">
         <f>IF($A26&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="6"/>
-        <v>732.96065904203897</v>
+        <v>-7267.039340957961</v>
       </c>
       <c r="AL26" s="21">
         <f t="shared" si="7"/>
-        <v>-419029.83423081349</v>
+        <v>-597029.83423081355</v>
       </c>
       <c r="AM26" s="22">
         <f t="shared" si="8"/>
-        <v>197341.91666666672</v>
+        <v>243341.91666666674</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.2">
@@ -7755,7 +7758,7 @@
       </c>
       <c r="AE27" s="25">
         <f>IF($A27&lt;=3,VARIABLES!$B$13,IF($A27&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF27" s="25">
         <f>IF(MOD($A27,12)=0,AC27*VARIABLES!$B$16,0)</f>
@@ -7771,23 +7774,23 @@
       </c>
       <c r="AI27" s="19">
         <f t="shared" si="5"/>
-        <v>105683.11656524973</v>
+        <v>111683.11656524973</v>
       </c>
       <c r="AJ27" s="20">
         <f>IF($A27&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK27" s="27">
         <f t="shared" si="6"/>
-        <v>-57510.134602059123</v>
+        <v>-65510.134602059123</v>
       </c>
       <c r="AL27" s="27">
         <f t="shared" si="7"/>
-        <v>-476539.96883287263</v>
+        <v>-662539.96883287269</v>
       </c>
       <c r="AM27" s="22">
         <f t="shared" si="8"/>
-        <v>205922.00000000006</v>
+        <v>253922.00000000009</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.2">
@@ -7912,7 +7915,7 @@
       </c>
       <c r="AE28" s="7">
         <f>IF($A28&lt;=3,VARIABLES!$B$13,IF($A28&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF28" s="7">
         <f>IF(MOD($A28,12)=0,AC28*VARIABLES!$B$16,0)</f>
@@ -7928,23 +7931,23 @@
       </c>
       <c r="AI28" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ28" s="20">
         <f>IF($A28&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="6"/>
-        <v>5702.7403184558661</v>
+        <v>-2297.2596815441339</v>
       </c>
       <c r="AL28" s="21">
         <f t="shared" si="7"/>
-        <v>-470837.22851441678</v>
+        <v>-664837.22851441684</v>
       </c>
       <c r="AM28" s="22">
         <f t="shared" si="8"/>
-        <v>214502.0833333334</v>
+        <v>264502.08333333343</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.2">
@@ -8069,7 +8072,7 @@
       </c>
       <c r="AE29" s="25">
         <f>IF($A29&lt;=3,VARIABLES!$B$13,IF($A29&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF29" s="25">
         <f>IF(MOD($A29,12)=0,AC29*VARIABLES!$B$16,0)</f>
@@ -8085,23 +8088,23 @@
       </c>
       <c r="AI29" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ29" s="20">
         <f>IF($A29&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK29" s="27">
         <f t="shared" si="6"/>
-        <v>8324.9601655944516</v>
+        <v>324.96016559445161</v>
       </c>
       <c r="AL29" s="27">
         <f t="shared" si="7"/>
-        <v>-462512.26834882231</v>
+        <v>-664512.26834882237</v>
       </c>
       <c r="AM29" s="22">
         <f t="shared" si="8"/>
-        <v>223082.16666666674</v>
+        <v>275082.16666666674</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.2">
@@ -8226,7 +8229,7 @@
       </c>
       <c r="AE30" s="7">
         <f>IF($A30&lt;=3,VARIABLES!$B$13,IF($A30&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF30" s="7">
         <f>IF(MOD($A30,12)=0,AC30*VARIABLES!$B$16,0)</f>
@@ -8242,23 +8245,23 @@
       </c>
       <c r="AI30" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ30" s="20">
         <f>IF($A30&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="6"/>
-        <v>11042.448729285376</v>
+        <v>3042.4487292853755</v>
       </c>
       <c r="AL30" s="21">
         <f t="shared" si="7"/>
-        <v>-451469.81961953692</v>
+        <v>-661469.81961953698</v>
       </c>
       <c r="AM30" s="22">
         <f t="shared" si="8"/>
-        <v>231662.25000000009</v>
+        <v>285662.25000000006</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.2">
@@ -8383,7 +8386,7 @@
       </c>
       <c r="AE31" s="25">
         <f>IF($A31&lt;=3,VARIABLES!$B$13,IF($A31&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF31" s="25">
         <f>IF(MOD($A31,12)=0,AC31*VARIABLES!$B$16,0)</f>
@@ -8399,23 +8402,23 @@
       </c>
       <c r="AI31" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ31" s="20">
         <f>IF($A31&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK31" s="27">
         <f t="shared" si="6"/>
-        <v>13858.098535795516</v>
+        <v>5858.098535795516</v>
       </c>
       <c r="AL31" s="27">
         <f t="shared" si="7"/>
-        <v>-437611.7210837414</v>
+        <v>-655611.72108374152</v>
       </c>
       <c r="AM31" s="22">
         <f t="shared" si="8"/>
-        <v>240242.33333333343</v>
+        <v>296242.33333333337</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.2">
@@ -8540,7 +8543,7 @@
       </c>
       <c r="AE32" s="7">
         <f>IF($A32&lt;=3,VARIABLES!$B$13,IF($A32&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF32" s="7">
         <f>IF(MOD($A32,12)=0,AC32*VARIABLES!$B$16,0)</f>
@@ -8556,23 +8559,23 @@
       </c>
       <c r="AI32" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ32" s="20">
         <f>IF($A32&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="6"/>
-        <v>16774.890007284826</v>
+        <v>8774.8900072848282</v>
       </c>
       <c r="AL32" s="21">
         <f t="shared" si="7"/>
-        <v>-420836.83107645658</v>
+        <v>-646836.8310764567</v>
       </c>
       <c r="AM32" s="22">
         <f t="shared" si="8"/>
-        <v>248822.41666666677</v>
+        <v>306822.41666666669</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.2">
@@ -8697,7 +8700,7 @@
       </c>
       <c r="AE33" s="25">
         <f>IF($A33&lt;=3,VARIABLES!$B$13,IF($A33&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF33" s="25">
         <f>IF(MOD($A33,12)=0,AC33*VARIABLES!$B$16,0)</f>
@@ -8713,23 +8716,23 @@
       </c>
       <c r="AI33" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ33" s="20">
         <f>IF($A33&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK33" s="27">
         <f t="shared" si="6"/>
-        <v>19795.89413508647</v>
+        <v>11795.894135086472</v>
       </c>
       <c r="AL33" s="27">
         <f t="shared" si="7"/>
-        <v>-401040.93694137014</v>
+        <v>-635040.93694137025</v>
       </c>
       <c r="AM33" s="22">
         <f t="shared" si="8"/>
-        <v>257402.50000000012</v>
+        <v>317402.5</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.2">
@@ -8854,7 +8857,7 @@
       </c>
       <c r="AE34" s="7">
         <f>IF($A34&lt;=3,VARIABLES!$B$13,IF($A34&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF34" s="7">
         <f>IF(MOD($A34,12)=0,AC34*VARIABLES!$B$16,0)</f>
@@ -8870,23 +8873,23 @@
       </c>
       <c r="AI34" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ34" s="20">
         <f>IF($A34&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK34" s="21">
         <f t="shared" si="6"/>
-        <v>22924.275234368637</v>
+        <v>14924.275234368639</v>
       </c>
       <c r="AL34" s="21">
         <f t="shared" si="7"/>
-        <v>-378116.66170700151</v>
+        <v>-620116.66170700162</v>
       </c>
       <c r="AM34" s="22">
         <f t="shared" si="8"/>
-        <v>265982.58333333343</v>
+        <v>327982.58333333331</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.2">
@@ -9011,7 +9014,7 @@
       </c>
       <c r="AE35" s="25">
         <f>IF($A35&lt;=3,VARIABLES!$B$13,IF($A35&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF35" s="25">
         <f>IF(MOD($A35,12)=0,AC35*VARIABLES!$B$16,0)</f>
@@ -9027,23 +9030,23 @@
       </c>
       <c r="AI35" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ35" s="20">
         <f>IF($A35&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK35" s="27">
         <f t="shared" si="6"/>
-        <v>26163.293782657543</v>
+        <v>18163.293782657543</v>
       </c>
       <c r="AL35" s="27">
         <f t="shared" si="7"/>
-        <v>-351953.36792434397</v>
+        <v>-601953.36792434403</v>
       </c>
       <c r="AM35" s="22">
         <f t="shared" si="8"/>
-        <v>274562.66666666674</v>
+        <v>338562.66666666663</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.2">
@@ -9168,7 +9171,7 @@
       </c>
       <c r="AE36" s="7">
         <f>IF($A36&lt;=3,VARIABLES!$B$13,IF($A36&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF36" s="7">
         <f>IF(MOD($A36,12)=0,AC36*VARIABLES!$B$16,0)</f>
@@ -9184,23 +9187,23 @@
       </c>
       <c r="AI36" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ36" s="20">
         <f>IF($A36&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK36" s="21">
         <f t="shared" si="6"/>
-        <v>29516.30934477767</v>
+        <v>21516.30934477767</v>
       </c>
       <c r="AL36" s="21">
         <f t="shared" si="7"/>
-        <v>-322437.05857956631</v>
+        <v>-580437.05857956631</v>
       </c>
       <c r="AM36" s="22">
         <f t="shared" si="8"/>
-        <v>283142.75000000006</v>
+        <v>349142.74999999994</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.2">
@@ -9325,7 +9328,7 @@
       </c>
       <c r="AE37" s="25">
         <f>IF($A37&lt;=3,VARIABLES!$B$13,IF($A37&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF37" s="25">
         <f>IF(MOD($A37,12)=0,AC37*VARIABLES!$B$16,0)</f>
@@ -9341,23 +9344,23 @@
       </c>
       <c r="AI37" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ37" s="20">
         <f>IF($A37&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK37" s="27">
         <f t="shared" si="6"/>
-        <v>32986.783586842219</v>
+        <v>24986.783586842219</v>
       </c>
       <c r="AL37" s="27">
         <f t="shared" si="7"/>
-        <v>-289450.27499272407</v>
+        <v>-555450.27499272407</v>
       </c>
       <c r="AM37" s="22">
         <f t="shared" si="8"/>
-        <v>291722.83333333337</v>
+        <v>359722.83333333326</v>
       </c>
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.2">
@@ -9482,7 +9485,7 @@
       </c>
       <c r="AE38" s="7">
         <f>IF($A38&lt;=3,VARIABLES!$B$13,IF($A38&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF38" s="7">
         <f>IF(MOD($A38,12)=0,AC38*VARIABLES!$B$16,0)</f>
@@ -9498,23 +9501,23 @@
       </c>
       <c r="AI38" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ38" s="20">
         <f>IF($A38&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="6"/>
-        <v>36578.283382007976</v>
+        <v>28578.283382007976</v>
       </c>
       <c r="AL38" s="21">
         <f t="shared" si="7"/>
-        <v>-252871.9916107161</v>
+        <v>-526871.9916107161</v>
       </c>
       <c r="AM38" s="22">
         <f t="shared" si="8"/>
-        <v>300302.91666666669</v>
+        <v>370302.91666666657</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.2">
@@ -9639,7 +9642,7 @@
       </c>
       <c r="AE39" s="25">
         <f>IF($A39&lt;=3,VARIABLES!$B$13,IF($A39&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF39" s="25">
         <f>IF(MOD($A39,12)=0,AC39*VARIABLES!$B$16,0)</f>
@@ -9655,23 +9658,23 @@
       </c>
       <c r="AI39" s="19">
         <f t="shared" si="5"/>
-        <v>147761.93104442907</v>
+        <v>153761.93104442907</v>
       </c>
       <c r="AJ39" s="20">
         <f>IF($A39&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
-        <v>8580.0833333333339</v>
+        <v>10580.083333333334</v>
       </c>
       <c r="AK39" s="27">
         <f t="shared" si="6"/>
-        <v>-62467.447033637996</v>
+        <v>-70467.447033637989</v>
       </c>
       <c r="AL39" s="27">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM39" s="22">
         <f t="shared" si="8"/>
-        <v>308883</v>
+        <v>380882.99999999988</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.2">
@@ -9796,7 +9799,7 @@
       </c>
       <c r="AE40" s="7">
         <f>IF($A40&lt;=3,VARIABLES!$B$13,IF($A40&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF40" s="7">
         <f>IF(MOD($A40,12)=0,AC40*VARIABLES!$B$16,0)</f>
@@ -9812,7 +9815,7 @@
       </c>
       <c r="AI40" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ40" s="20">
         <f>IF($A40&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -9820,15 +9823,15 @@
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="6"/>
-        <v>-17842.061051960249</v>
+        <v>-23842.061051960249</v>
       </c>
       <c r="AL40" s="21">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM40" s="22">
         <f t="shared" si="8"/>
-        <v>291040.93894803978</v>
+        <v>357040.93894803966</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.2">
@@ -9953,7 +9956,7 @@
       </c>
       <c r="AE41" s="25">
         <f>IF($A41&lt;=3,VARIABLES!$B$13,IF($A41&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF41" s="25">
         <f>IF(MOD($A41,12)=0,AC41*VARIABLES!$B$16,0)</f>
@@ -9969,7 +9972,7 @@
       </c>
       <c r="AI41" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ41" s="20">
         <f>IF($A41&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -9977,15 +9980,15 @@
       </c>
       <c r="AK41" s="27">
         <f t="shared" si="6"/>
-        <v>-17355.212404697151</v>
+        <v>-23355.212404697151</v>
       </c>
       <c r="AL41" s="27">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM41" s="22">
         <f t="shared" si="8"/>
-        <v>273685.72654334264</v>
+        <v>333685.72654334252</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.2">
@@ -10110,7 +10113,7 @@
       </c>
       <c r="AE42" s="7">
         <f>IF($A42&lt;=3,VARIABLES!$B$13,IF($A42&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF42" s="7">
         <f>IF(MOD($A42,12)=0,AC42*VARIABLES!$B$16,0)</f>
@@ -10126,7 +10129,7 @@
       </c>
       <c r="AI42" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ42" s="20">
         <f>IF($A42&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -10134,15 +10137,15 @@
       </c>
       <c r="AK42" s="21">
         <f t="shared" si="6"/>
-        <v>-16860.781169902297</v>
+        <v>-22860.781169902297</v>
       </c>
       <c r="AL42" s="21">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM42" s="22">
         <f t="shared" si="8"/>
-        <v>256824.94537344034</v>
+        <v>310824.94537344022</v>
       </c>
     </row>
     <row r="43" spans="1:39" x14ac:dyDescent="0.2">
@@ -10267,7 +10270,7 @@
       </c>
       <c r="AE43" s="25">
         <f>IF($A43&lt;=3,VARIABLES!$B$13,IF($A43&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF43" s="25">
         <f>IF(MOD($A43,12)=0,AC43*VARIABLES!$B$16,0)</f>
@@ -10283,7 +10286,7 @@
       </c>
       <c r="AI43" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ43" s="20">
         <f>IF($A43&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -10291,15 +10294,15 @@
       </c>
       <c r="AK43" s="27">
         <f t="shared" si="6"/>
-        <v>-16358.710105995364</v>
+        <v>-22358.710105995364</v>
       </c>
       <c r="AL43" s="27">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM43" s="22">
         <f t="shared" si="8"/>
-        <v>240466.23526744498</v>
+        <v>288466.23526744486</v>
       </c>
     </row>
     <row r="44" spans="1:39" x14ac:dyDescent="0.2">
@@ -10424,7 +10427,7 @@
       </c>
       <c r="AE44" s="7">
         <f>IF($A44&lt;=3,VARIABLES!$B$13,IF($A44&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF44" s="7">
         <f>IF(MOD($A44,12)=0,AC44*VARIABLES!$B$16,0)</f>
@@ -10440,7 +10443,7 @@
       </c>
       <c r="AI44" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ44" s="20">
         <f>IF($A44&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -10448,15 +10451,15 @@
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="6"/>
-        <v>-15848.941539060266</v>
+        <v>-21848.941539060266</v>
       </c>
       <c r="AL44" s="21">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM44" s="22">
         <f t="shared" si="8"/>
-        <v>224617.29372838471</v>
+        <v>266617.2937283846</v>
       </c>
     </row>
     <row r="45" spans="1:39" x14ac:dyDescent="0.2">
@@ -10581,7 +10584,7 @@
       </c>
       <c r="AE45" s="25">
         <f>IF($A45&lt;=3,VARIABLES!$B$13,IF($A45&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF45" s="25">
         <f>IF(MOD($A45,12)=0,AC45*VARIABLES!$B$16,0)</f>
@@ -10597,7 +10600,7 @@
       </c>
       <c r="AI45" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ45" s="20">
         <f>IF($A45&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -10605,15 +10608,15 @@
       </c>
       <c r="AK45" s="27">
         <f t="shared" si="6"/>
-        <v>-15331.417359578048</v>
+        <v>-21331.417359578048</v>
       </c>
       <c r="AL45" s="27">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM45" s="22">
         <f t="shared" si="8"/>
-        <v>209285.87636880667</v>
+        <v>245285.87636880655</v>
       </c>
     </row>
     <row r="46" spans="1:39" x14ac:dyDescent="0.2">
@@ -10738,7 +10741,7 @@
       </c>
       <c r="AE46" s="7">
         <f>IF($A46&lt;=3,VARIABLES!$B$13,IF($A46&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF46" s="7">
         <f>IF(MOD($A46,12)=0,AC46*VARIABLES!$B$16,0)</f>
@@ -10754,7 +10757,7 @@
       </c>
       <c r="AI46" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ46" s="20">
         <f>IF($A46&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -10762,15 +10765,15 @@
       </c>
       <c r="AK46" s="21">
         <f t="shared" si="6"/>
-        <v>-14806.079019135133</v>
+        <v>-20806.079019135133</v>
       </c>
       <c r="AL46" s="21">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM46" s="22">
         <f t="shared" si="8"/>
-        <v>194479.79734967154</v>
+        <v>224479.79734967143</v>
       </c>
     </row>
     <row r="47" spans="1:39" x14ac:dyDescent="0.2">
@@ -10895,7 +10898,7 @@
       </c>
       <c r="AE47" s="25">
         <f>IF($A47&lt;=3,VARIABLES!$B$13,IF($A47&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF47" s="25">
         <f>IF(MOD($A47,12)=0,AC47*VARIABLES!$B$16,0)</f>
@@ -10911,7 +10914,7 @@
       </c>
       <c r="AI47" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ47" s="20">
         <f>IF($A47&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -10919,15 +10922,15 @@
       </c>
       <c r="AK47" s="27">
         <f t="shared" si="6"/>
-        <v>-14272.86752710662</v>
+        <v>-20272.86752710662</v>
       </c>
       <c r="AL47" s="27">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM47" s="22">
         <f t="shared" si="8"/>
-        <v>180206.92982256491</v>
+        <v>204206.92982256479</v>
       </c>
     </row>
     <row r="48" spans="1:39" x14ac:dyDescent="0.2">
@@ -11052,7 +11055,7 @@
       </c>
       <c r="AE48" s="7">
         <f>IF($A48&lt;=3,VARIABLES!$B$13,IF($A48&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF48" s="7">
         <f>IF(MOD($A48,12)=0,AC48*VARIABLES!$B$16,0)</f>
@@ -11068,7 +11071,7 @@
       </c>
       <c r="AI48" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ48" s="20">
         <f>IF($A48&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -11076,15 +11079,15 @@
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="6"/>
-        <v>-13731.723447314507</v>
+        <v>-19731.723447314507</v>
       </c>
       <c r="AL48" s="21">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM48" s="22">
         <f t="shared" si="8"/>
-        <v>166475.20637525042</v>
+        <v>184475.2063752503</v>
       </c>
     </row>
     <row r="49" spans="1:39" x14ac:dyDescent="0.2">
@@ -11209,7 +11212,7 @@
       </c>
       <c r="AE49" s="25">
         <f>IF($A49&lt;=3,VARIABLES!$B$13,IF($A49&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF49" s="25">
         <f>IF(MOD($A49,12)=0,AC49*VARIABLES!$B$16,0)</f>
@@ -11225,7 +11228,7 @@
       </c>
       <c r="AI49" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ49" s="20">
         <f>IF($A49&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -11233,15 +11236,15 @@
       </c>
       <c r="AK49" s="27">
         <f t="shared" si="6"/>
-        <v>-13182.58689466073</v>
+        <v>-19182.58689466073</v>
       </c>
       <c r="AL49" s="27">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM49" s="22">
         <f t="shared" si="8"/>
-        <v>153292.6194805897</v>
+        <v>165292.61948058958</v>
       </c>
     </row>
     <row r="50" spans="1:39" x14ac:dyDescent="0.2">
@@ -11366,7 +11369,7 @@
       </c>
       <c r="AE50" s="7">
         <f>IF($A50&lt;=3,VARIABLES!$B$13,IF($A50&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF50" s="7">
         <f>IF(MOD($A50,12)=0,AC50*VARIABLES!$B$16,0)</f>
@@ -11382,7 +11385,7 @@
       </c>
       <c r="AI50" s="19">
         <f t="shared" si="5"/>
-        <v>45000</v>
+        <v>51000</v>
       </c>
       <c r="AJ50" s="20">
         <f>IF($A50&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -11390,15 +11393,15 @@
       </c>
       <c r="AK50" s="21">
         <f t="shared" si="6"/>
-        <v>-12625.397531734561</v>
+        <v>-18625.397531734561</v>
       </c>
       <c r="AL50" s="21">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM50" s="22">
         <f t="shared" si="8"/>
-        <v>140667.22194885515</v>
+        <v>146667.22194885503</v>
       </c>
     </row>
     <row r="51" spans="1:39" x14ac:dyDescent="0.2">
@@ -11523,7 +11526,7 @@
       </c>
       <c r="AE51" s="25">
         <f>IF($A51&lt;=3,VARIABLES!$B$13,IF($A51&lt;=6,VARIABLES!$B$14,VARIABLES!$B$15))</f>
-        <v>40000</v>
+        <v>46000</v>
       </c>
       <c r="AF51" s="25">
         <f>IF(MOD($A51,12)=0,AC51*VARIABLES!$B$16,0)</f>
@@ -11539,7 +11542,7 @@
       </c>
       <c r="AI51" s="19">
         <f t="shared" si="5"/>
-        <v>173607.01380170003</v>
+        <v>179607.01380170003</v>
       </c>
       <c r="AJ51" s="20">
         <f>IF($A51&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -11547,15 +11550,15 @@
       </c>
       <c r="AK51" s="27">
         <f t="shared" si="6"/>
-        <v>-140667.10836709465</v>
+        <v>-146667.10836709465</v>
       </c>
       <c r="AL51" s="27">
         <f t="shared" si="7"/>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM51" s="22">
         <f t="shared" si="8"/>
-        <v>0.11358176049543545</v>
+        <v>0.11358176037902012</v>
       </c>
     </row>
     <row r="52" spans="1:39" x14ac:dyDescent="0.2">
@@ -11585,11 +11588,11 @@
       </c>
       <c r="AD52" s="28">
         <f t="shared" ref="AD52:AK52" si="9">SUM(AD4:AD51)</f>
-        <v>50000</v>
+        <v>57499.999999999993</v>
       </c>
       <c r="AE52" s="28">
         <f t="shared" si="9"/>
-        <v>1830000</v>
+        <v>2104500</v>
       </c>
       <c r="AF52" s="28">
         <f t="shared" si="9"/>
@@ -11605,23 +11608,23 @@
       </c>
       <c r="AI52" s="28">
         <f t="shared" si="9"/>
-        <v>2445128.2233524197</v>
+        <v>2727128.2233524197</v>
       </c>
       <c r="AJ52" s="28">
         <f t="shared" si="9"/>
-        <v>308883</v>
+        <v>380882.99999999988</v>
       </c>
       <c r="AK52" s="28">
         <f t="shared" si="9"/>
-        <v>-624222.32506259368</v>
+        <v>-978222.32506259379</v>
       </c>
       <c r="AL52" s="28">
         <f>AL51</f>
-        <v>-315339.43864435412</v>
+        <v>-597339.43864435412</v>
       </c>
       <c r="AM52" s="28">
         <f>AM51</f>
-        <v>0.11358176049543545</v>
+        <v>0.11358176037902012</v>
       </c>
     </row>
     <row r="54" spans="1:39" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/docs/Financial/BitWealth_Cashflow_Forecast_v3.0.xlsx
+++ b/docs/Financial/BitWealth_Cashflow_Forecast_v3.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davin\Dropbox\BitWealth\bitwealth-lth-pvr\bitwealth-lth-pvr\docs\Financial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82313866-EEEA-4D0F-8C4F-76B196BDE4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4EF3C8-C68C-4906-9364-E43E1ACB561A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -703,31 +703,10 @@
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -735,6 +714,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -747,6 +729,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -986,148 +986,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>516250.00000000006</c:v>
+                  <c:v>524375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5951378.125</c:v>
+                  <c:v>6047463.28125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6456819.9140625</c:v>
+                  <c:v>6652526.6162109375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6983204.5962695321</c:v>
+                  <c:v>7291050.7350012213</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7531180.9216982927</c:v>
+                  <c:v>7964590.5096637793</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8101417.7679849891</c:v>
+                  <c:v>8674773.1769010462</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8694604.7657659464</c:v>
+                  <c:v>9423301.7112612296</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9311452.9435844272</c:v>
+                  <c:v>10211958.355810855</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9952695.3928699438</c:v>
+                  <c:v>11042608.317657929</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10619087.953615811</c:v>
+                  <c:v>11917203.636035109</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11311409.921400245</c:v>
+                  <c:v>12837787.231013281</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12030464.77641643</c:v>
+                  <c:v>13806497.141294109</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12777080.935197763</c:v>
+                  <c:v>14825570.959925728</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>13552112.525745921</c:v>
+                  <c:v>15897350.477200346</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14356440.186791524</c:v>
+                  <c:v>17024286.54042612</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15190971.891939875</c:v>
+                  <c:v>18208944.140719958</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>16056643.799477873</c:v>
+                  <c:v>19454007.737443283</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>16954421.128642362</c:v>
+                  <c:v>20762286.831400715</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>17885299.063175134</c:v>
+                  <c:v>22136721.798442636</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>18850303.683015779</c:v>
+                  <c:v>23580389.995658357</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>19850492.925009869</c:v>
+                  <c:v>25096512.152917713</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>20886957.573537651</c:v>
+                  <c:v>26688459.063117161</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>21960822.281996533</c:v>
+                  <c:v>28359758.585112344</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>23073246.626099892</c:v>
+                  <c:v>30114102.973974865</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>24225426.189984772</c:v>
+                  <c:v>31955356.553897146</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>25418593.686152007</c:v>
+                  <c:v>33887563.749788001</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>26654020.110294458</c:v>
+                  <c:v>35914957.494353503</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>27933015.932101812</c:v>
+                  <c:v>38041968.028245926</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>29256932.32316459</c:v>
+                  <c:v>40273232.111687519</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>30627162.423134997</c:v>
+                  <c:v>42613602.666839801</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>32045142.645338465</c:v>
+                  <c:v>45068158.871092588</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>33512354.023067091</c:v>
+                  <c:v>47642216.722393699</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>35030323.597824551</c:v>
+                  <c:v>50341340.09873084</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>36600625.850831866</c:v>
+                  <c:v>53171352.334914826</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>38224884.179144263</c:v>
+                  <c:v>56138348.340899467</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>39904772.417771623</c:v>
+                  <c:v>59248707.287010461</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>40702833.415638342</c:v>
+                  <c:v>60196273.719616465</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>41512137.239840023</c:v>
+                  <c:v>61156240.22994414</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>42332769.998008579</c:v>
+                  <c:v>62128701.897190891</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>43164818.458097979</c:v>
+                  <c:v>63113754.53053686</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>44008370.053454518</c:v>
+                  <c:v>64111494.674757004</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>44863512.887926221</c:v>
+                  <c:v>65122019.615876377</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>45730335.741011404</c:v>
+                  <c:v>66145427.386868998</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>46608928.073046945</c:v>
+                  <c:v>67181816.77340053</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>47499380.030436307</c:v>
+                  <c:v>68231287.319615245</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>48401782.450917944</c:v>
+                  <c:v>69293939.333967432</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>49316226.868873991</c:v>
+                  <c:v>70369873.895097822</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>50242805.52068001</c:v>
+                  <c:v>71459192.857755229</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1454,148 +1454,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>4166.666666666667</c:v>
+                  <c:v>4375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56863.541666666672</c:v>
+                  <c:v>65580.46875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20799.981770833332</c:v>
+                  <c:v>30422.3291015625</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21909.314928385418</c:v>
+                  <c:v>32502.212020263672</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23067.994446891276</c:v>
+                  <c:v>34700.262087501527</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24277.517769915248</c:v>
+                  <c:v>37021.858245923475</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25539.427818542499</c:v>
+                  <c:v>39472.624484868022</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>26855.314373716617</c:v>
+                  <c:v>42058.441013436634</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>28226.815500632703</c:v>
+                  <c:v>44785.455943469868</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29655.619016466666</c:v>
+                  <c:v>47660.097505720507</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>31143.46400276048</c:v>
+                  <c:v>50689.086823581136</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>32692.142363823263</c:v>
+                  <c:v>53879.451269838042</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>34303.500432549772</c:v>
+                  <c:v>57238.538433087284</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>35979.440625100302</c:v>
+                  <c:v>60774.03072166795</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>37721.923145930166</c:v>
+                  <c:v>64493.960634240444</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>39532.967744702437</c:v>
+                  <c:v>68406.726727470974</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41414.655526664021</c:v>
+                  <c:v>72521.11031267549</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>43369.130818113765</c:v>
+                  <c:v>76846.292914734557</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>45398.603088640644</c:v>
+                  <c:v>81391.874528113229</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>47505.348931861125</c:v>
+                  <c:v>86167.892706414437</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>49691.714106438121</c:v>
+                  <c:v>91184.842523560335</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>51960.115639217605</c:v>
+                  <c:v>96453.69744643895</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>54313.043992375373</c:v>
+                  <c:v>101985.93116067642</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>56753.065296523942</c:v>
+                  <c:v>107793.54039310047</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>59282.8236517892</c:v>
+                  <c:v>113889.06877645561</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>61905.043498927786</c:v>
+                  <c:v>120285.63180401287</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>64622.532062618709</c:v>
+                  <c:v>126996.94292390031</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>67438.18186912885</c:v>
+                  <c:v>134037.34082525712</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>70354.973340618162</c:v>
+                  <c:v>141421.81797070184</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>73375.977468419806</c:v>
+                  <c:v>149166.05043209658</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>76504.358567701973</c:v>
+                  <c:v>157286.42908919885</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>79743.377115990879</c:v>
+                  <c:v>165800.09225351908</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>83096.392678111006</c:v>
+                  <c:v>174724.95978255486</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>86566.866920175555</c:v>
+                  <c:v>184079.76875255664</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>90158.366715341312</c:v>
+                  <c:v>193884.11076109807</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>93874.567344124414</c:v>
+                  <c:v>204158.4709339893</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>27157.938948039751</c:v>
+                  <c:v>38851.961452413663</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>27644.787595302849</c:v>
+                  <c:v>39427.437335797062</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>28139.218830097703</c:v>
+                  <c:v>40011.168002780243</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>28641.289894004636</c:v>
+                  <c:v>40603.21579728488</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>29151.058460939734</c:v>
+                  <c:v>41203.643534330564</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>29668.582640421952</c:v>
+                  <c:v>41812.514503596605</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>30193.920980864867</c:v>
+                  <c:v>42429.892473010812</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>30727.13247289338</c:v>
+                  <c:v>43055.841692365379</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>31268.276552685493</c:v>
+                  <c:v>43690.426896960198</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>31817.41310533927</c:v>
+                  <c:v>44333.713311273699</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>32374.602468265439</c:v>
+                  <c:v>44985.76665266139</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>32939.905434605382</c:v>
+                  <c:v>45646.653135082524</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1825,7 +1825,7 @@
                   <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>84076.161941041079</c:v>
+                  <c:v>88516.242853235279</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>51000</c:v>
@@ -1861,7 +1861,7 @@
                   <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>111683.11656524973</c:v>
+                  <c:v>129285.25743493716</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>51000</c:v>
@@ -1897,7 +1897,7 @@
                   <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>153761.93104442907</c:v>
+                  <c:v>202121.76821752614</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>51000</c:v>
@@ -1933,7 +1933,7 @@
                   <c:v>51000</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>179607.01380170003</c:v>
+                  <c:v>232647.98214438808</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2242,148 +2242,148 @@
                 <c:formatCode>\R\ #\ ##0;[Red]\(\R\ #\ ##0\)</c:formatCode>
                 <c:ptCount val="48"/>
                 <c:pt idx="0">
-                  <c:v>-91913.416666666657</c:v>
+                  <c:v>-91705.083333333328</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-73629.958333333314</c:v>
+                  <c:v>-64704.697916666664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-91410.059895833314</c:v>
+                  <c:v>-72862.4521484375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-119580.82830078123</c:v>
+                  <c:v>-90440.323461507156</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-146592.91718722327</c:v>
+                  <c:v>-105820.14470733896</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-172395.48275064136</c:v>
+                  <c:v>-118878.36979474881</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-208436.13826543221</c:v>
+                  <c:v>-140985.82864321413</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-243160.90722504893</c:v>
+                  <c:v>-160507.47096311083</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-276514.17505774955</c:v>
+                  <c:v>-177302.09835297428</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-308438.63937461621</c:v>
+                  <c:v>-191222.08418058712</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-338875.25870518904</c:v>
+                  <c:v>-202113.08069033932</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-400839.36161574017</c:v>
+                  <c:v>-247329.95560706989</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-428115.94451652374</c:v>
+                  <c:v>-251671.50050731594</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-453716.58722475677</c:v>
+                  <c:v>-252477.55311898133</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-477574.74741215992</c:v>
+                  <c:v>-249563.67581807423</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-499621.86300079082</c:v>
+                  <c:v>-242737.03242393659</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-519787.29080746014</c:v>
+                  <c:v>-231796.00544459443</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-537998.24332267977</c:v>
+                  <c:v>-216529.7958631932</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-554179.72356737242</c:v>
+                  <c:v>-196718.00466841331</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-568254.45796884468</c:v>
+                  <c:v>-172130.1952953322</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-580142.82719573984</c:v>
+                  <c:v>-142525.43610510521</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-589762.79488985555</c:v>
+                  <c:v>-107651.8219919996</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-597029.83423081355</c:v>
+                  <c:v>-67245.974164656509</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-662539.96883287269</c:v>
+                  <c:v>-99317.774539826525</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-664837.22851441684</c:v>
+                  <c:v>-47008.789096704255</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-664512.26834882237</c:v>
+                  <c:v>11696.759373975277</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-661469.81961953698</c:v>
+                  <c:v>77113.618964542256</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-655611.72108374152</c:v>
+                  <c:v>149570.87645646604</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-646836.8310764567</c:v>
+                  <c:v>229412.61109383457</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-635040.93694137025</c:v>
+                  <c:v>316998.57819259784</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-620116.66170700162</c:v>
+                  <c:v>412704.92394846334</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-601953.36792434403</c:v>
+                  <c:v>516924.93286864908</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-580437.05857956631</c:v>
+                  <c:v>630069.80931787065</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-555450.27499272407</c:v>
+                  <c:v>752569.49473709392</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-526871.9916107161</c:v>
+                  <c:v>884873.52216485864</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-597339.43864435412</c:v>
+                  <c:v>876330.14154798852</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2688,40 +2688,40 @@
                   <c:v>380882.99999999988</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>357040.93894803966</c:v>
+                  <c:v>368734.96145241352</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>333685.72654334252</c:v>
+                  <c:v>357162.39878821059</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>310824.94537344022</c:v>
+                  <c:v>346173.56679099082</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>288466.23526744486</c:v>
+                  <c:v>335776.78258827573</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>266617.2937283846</c:v>
+                  <c:v>325980.42612260627</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>245285.87636880655</c:v>
+                  <c:v>316792.94062620285</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>224479.79734967143</c:v>
+                  <c:v>308222.83309921366</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>204206.92982256479</c:v>
+                  <c:v>300278.67479157902</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>184475.2063752503</c:v>
+                  <c:v>292969.1016885392</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>165292.61948058958</c:v>
+                  <c:v>286302.81499981292</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>146667.22194885503</c:v>
+                  <c:v>280288.5816524743</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.11358176037902012</c:v>
+                  <c:v>93287.252643168729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3210,21 +3210,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="30"/>
@@ -3235,7 +3235,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>117</v>
@@ -3268,7 +3268,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>8</v>
@@ -3287,7 +3287,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="30"/>
@@ -3375,7 +3375,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="40" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="30"/>
@@ -3435,7 +3435,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="40" t="s">
         <v>34</v>
       </c>
       <c r="B27" s="30"/>
@@ -3491,7 +3491,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="40" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="30"/>
@@ -3551,7 +3551,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="40" t="s">
         <v>114</v>
       </c>
       <c r="B41" s="30"/>
@@ -3607,7 +3607,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="35" t="s">
+      <c r="A48" s="43" t="s">
         <v>41</v>
       </c>
       <c r="B48" s="30"/>
@@ -3702,7 +3702,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="34" t="s">
+      <c r="A58" s="42" t="s">
         <v>55</v>
       </c>
       <c r="B58" s="30"/>
@@ -3723,7 +3723,7 @@
       <c r="A60" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="8">
         <v>2026</v>
       </c>
       <c r="C60" s="1" t="s">
@@ -3742,7 +3742,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="39" t="s">
         <v>62</v>
       </c>
       <c r="B64" s="30"/>
@@ -3777,23 +3777,24 @@
     <col min="1" max="1" width="6" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2" customWidth="1"/>
     <col min="3" max="3" width="8" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="6" width="12" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="14" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="13" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="10" width="12" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="14" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="13" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="14" width="12" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="14" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="13" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="18" width="12" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="14" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="8" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="14" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="23" width="12" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="14" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="27" width="14" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="6" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="10" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="14" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="13" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="18" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="8" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="23" width="12" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="14" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="14" style="2" customWidth="1" collapsed="1"/>
+    <col min="26" max="27" width="14" style="2" customWidth="1"/>
     <col min="28" max="28" width="15" style="2" customWidth="1"/>
     <col min="29" max="29" width="16" style="2" customWidth="1"/>
     <col min="30" max="30" width="14" style="2" customWidth="1"/>
@@ -3807,7 +3808,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="30"/>
@@ -3850,12 +3851,12 @@
       <c r="AM1" s="30"/>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="33" t="s">
         <v>64</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="32" t="s">
         <v>65</v>
       </c>
       <c r="E2" s="30"/>
@@ -3873,23 +3874,23 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="30"/>
       <c r="S2" s="30"/>
-      <c r="T2" s="44" t="s">
+      <c r="T2" s="38" t="s">
         <v>66</v>
       </c>
       <c r="U2" s="30"/>
       <c r="V2" s="30"/>
       <c r="W2" s="30"/>
       <c r="X2" s="30"/>
-      <c r="Y2" s="44" t="s">
+      <c r="Y2" s="38" t="s">
         <v>67</v>
       </c>
       <c r="Z2" s="30"/>
       <c r="AA2" s="30"/>
       <c r="AB2" s="30"/>
-      <c r="AC2" s="42" t="s">
+      <c r="AC2" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="AD2" s="41" t="s">
+      <c r="AD2" s="35" t="s">
         <v>69</v>
       </c>
       <c r="AE2" s="30"/>
@@ -3897,10 +3898,10 @@
       <c r="AG2" s="30"/>
       <c r="AH2" s="30"/>
       <c r="AI2" s="30"/>
-      <c r="AJ2" s="38" t="s">
+      <c r="AJ2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="AK2" s="42" t="s">
+      <c r="AK2" s="36" t="s">
         <v>71</v>
       </c>
       <c r="AL2" s="30"/>
@@ -4035,7 +4036,7 @@
       </c>
       <c r="C4" s="15">
         <f>IF($A4&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D4" s="7">
         <f>IF($A4&lt;VARIABLES!$B$21,0,IF($A4=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4047,11 +4048,11 @@
       </c>
       <c r="F4" s="7">
         <f>IF($A4&lt;VARIABLES!$B$21,0,(IF($A4=VARIABLES!$B$21,0,G3)+D4)*C4*VARIABLES!$B$25)</f>
-        <v>416.66666666666674</v>
+        <v>625</v>
       </c>
       <c r="G4" s="7">
         <f>IF($A4&lt;VARIABLES!$B$21,0,(IF($A4=VARIABLES!$B$21,0,G3)+D4)*(1+C4)-F4)</f>
-        <v>516250.00000000006</v>
+        <v>524375</v>
       </c>
       <c r="H4" s="7">
         <f>IF($A4&lt;VARIABLES!$B$28,0,IF($A4=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4131,15 +4132,15 @@
       </c>
       <c r="AA4" s="7">
         <f t="shared" ref="AA4:AA51" si="2">F4+J4+N4+R4+W4</f>
-        <v>416.66666666666674</v>
+        <v>625</v>
       </c>
       <c r="AB4" s="17">
         <f t="shared" ref="AB4:AB51" si="3">Z4+AA4</f>
-        <v>4166.666666666667</v>
+        <v>4375</v>
       </c>
       <c r="AC4" s="18">
         <f t="shared" ref="AC4:AC51" si="4">G4+K4+O4+S4+X4</f>
-        <v>516250.00000000006</v>
+        <v>524375</v>
       </c>
       <c r="AD4" s="7">
         <f>IF($A4=1,VARIABLES!$B$12,0)</f>
@@ -4171,11 +4172,11 @@
       </c>
       <c r="AK4" s="21">
         <f t="shared" ref="AK4:AK51" si="6">AB4-AI4-AJ4</f>
-        <v>-91913.416666666657</v>
+        <v>-91705.083333333328</v>
       </c>
       <c r="AL4" s="21">
         <f>AK4</f>
-        <v>-91913.416666666657</v>
+        <v>-91705.083333333328</v>
       </c>
       <c r="AM4" s="22">
         <f>AJ4</f>
@@ -4192,7 +4193,7 @@
       </c>
       <c r="C5" s="24">
         <f>IF($A5&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$21,0,IF($A5=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4204,11 +4205,11 @@
       </c>
       <c r="F5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$21,0,(IF($A5=VARIABLES!$B$21,0,G4)+D5)*C5*VARIABLES!$B$25)</f>
-        <v>596.875</v>
+        <v>905.46875</v>
       </c>
       <c r="G5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$21,0,(IF($A5=VARIABLES!$B$21,0,G4)+D5)*(1+C5)-F5)</f>
-        <v>739528.12500000012</v>
+        <v>759688.28125</v>
       </c>
       <c r="H5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$28,0,IF($A5=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4220,11 +4221,11 @@
       </c>
       <c r="J5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$28,0,(IF($A5=VARIABLES!$B$28,0,K4)+H5)*C5*VARIABLES!$B$32)</f>
-        <v>133.33333333333334</v>
+        <v>200</v>
       </c>
       <c r="K5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$28,0,(IF($A5=VARIABLES!$B$28,0,K4)+H5)*(1+C5)-J5)</f>
-        <v>41200</v>
+        <v>41800</v>
       </c>
       <c r="L5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$35,0,IF($A5=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4236,11 +4237,11 @@
       </c>
       <c r="N5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$35,0,(IF($A5=VARIABLES!$B$35,0,O4)+L5)*C5*VARIABLES!$B$39)</f>
-        <v>16666.666666666668</v>
+        <v>25000</v>
       </c>
       <c r="O5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$35,0,(IF($A5=VARIABLES!$B$35,0,O4)+L5)*(1+C5)-N5)</f>
-        <v>5150000</v>
+        <v>5225000</v>
       </c>
       <c r="P5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$42,0,IF($A5=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4252,11 +4253,11 @@
       </c>
       <c r="R5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$42,0,(IF($A5=VARIABLES!$B$42,0,S4)+P5)*C5*VARIABLES!$B$46)</f>
-        <v>16.666666666666668</v>
+        <v>25</v>
       </c>
       <c r="S5" s="25">
         <f>IF($A5&lt;VARIABLES!$B$42,0,(IF($A5=VARIABLES!$B$42,0,S4)+P5)*(1+C5)-R5)</f>
-        <v>20650</v>
+        <v>20975</v>
       </c>
       <c r="T5" s="26">
         <f>IF($A5&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A5-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -4288,15 +4289,15 @@
       </c>
       <c r="AA5" s="25">
         <f t="shared" si="2"/>
-        <v>17413.541666666668</v>
+        <v>26130.46875</v>
       </c>
       <c r="AB5" s="17">
         <f t="shared" si="3"/>
-        <v>56863.541666666672</v>
+        <v>65580.46875</v>
       </c>
       <c r="AC5" s="18">
         <f t="shared" si="4"/>
-        <v>5951378.125</v>
+        <v>6047463.28125</v>
       </c>
       <c r="AD5" s="25">
         <f>IF($A5=1,VARIABLES!$B$12,0)</f>
@@ -4328,11 +4329,11 @@
       </c>
       <c r="AK5" s="27">
         <f t="shared" si="6"/>
-        <v>18283.458333333336</v>
+        <v>27000.385416666664</v>
       </c>
       <c r="AL5" s="27">
         <f t="shared" ref="AL5:AL51" si="7">IF(AJ5&gt;0,AL4+AK5,AL4)</f>
-        <v>-73629.958333333314</v>
+        <v>-64704.697916666664</v>
       </c>
       <c r="AM5" s="22">
         <f t="shared" ref="AM5:AM51" si="8">IF(AJ5&gt;0,AM4+AJ5,AM4+AK5)</f>
@@ -4349,7 +4350,7 @@
       </c>
       <c r="C6" s="15">
         <f>IF($A6&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$21,0,IF($A6=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4361,11 +4362,11 @@
       </c>
       <c r="F6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$21,0,(IF($A6=VARIABLES!$B$21,0,G5)+D6)*C6*VARIABLES!$B$25)</f>
-        <v>782.94010416666686</v>
+        <v>1199.6103515624998</v>
       </c>
       <c r="G6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$21,0,(IF($A6=VARIABLES!$B$21,0,G5)+D6)*(1+C6)-F6)</f>
-        <v>970062.78906250023</v>
+        <v>1006473.0849609375</v>
       </c>
       <c r="H6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$28,0,IF($A6=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4377,11 +4378,11 @@
       </c>
       <c r="J6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$28,0,(IF($A6=VARIABLES!$B$28,0,K5)+H6)*C6*VARIABLES!$B$32)</f>
-        <v>270.66666666666669</v>
+        <v>409</v>
       </c>
       <c r="K6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$28,0,(IF($A6=VARIABLES!$B$28,0,K5)+H6)*(1+C6)-J6)</f>
-        <v>83636</v>
+        <v>85481</v>
       </c>
       <c r="L6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$35,0,IF($A6=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4393,11 +4394,11 @@
       </c>
       <c r="N6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$35,0,(IF($A6=VARIABLES!$B$35,0,O5)+L6)*C6*VARIABLES!$B$39)</f>
-        <v>17166.666666666668</v>
+        <v>26125</v>
       </c>
       <c r="O6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$35,0,(IF($A6=VARIABLES!$B$35,0,O5)+L6)*(1+C6)-N6)</f>
-        <v>5304500</v>
+        <v>5460125</v>
       </c>
       <c r="P6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$42,0,IF($A6=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4409,11 +4410,11 @@
       </c>
       <c r="R6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$42,0,(IF($A6=VARIABLES!$B$42,0,S5)+P6)*C6*VARIABLES!$B$46)</f>
-        <v>33.875</v>
+        <v>51.21875</v>
       </c>
       <c r="S6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$42,0,(IF($A6=VARIABLES!$B$42,0,S5)+P6)*(1+C6)-R6)</f>
-        <v>41971.125000000007</v>
+        <v>42972.53125</v>
       </c>
       <c r="T6" s="16">
         <f>IF($A6&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A6-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -4429,11 +4430,11 @@
       </c>
       <c r="W6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$50,0,(IF($A6&lt;VARIABLES!$B$50+1,0,X5)+U6)*C6*VARIABLES!$B$56)</f>
-        <v>183.33333333333334</v>
+        <v>274.99999999999994</v>
       </c>
       <c r="X6" s="7">
         <f>IF($A6&lt;VARIABLES!$B$50,0,(IF($A6&lt;VARIABLES!$B$50+1,0,X5)+U6)*(1+C6)-W6)</f>
-        <v>56650</v>
+        <v>57475</v>
       </c>
       <c r="Y6" s="7">
         <f t="shared" si="0"/>
@@ -4445,15 +4446,15 @@
       </c>
       <c r="AA6" s="7">
         <f t="shared" si="2"/>
-        <v>18437.481770833332</v>
+        <v>28059.8291015625</v>
       </c>
       <c r="AB6" s="17">
         <f t="shared" si="3"/>
-        <v>20799.981770833332</v>
+        <v>30422.3291015625</v>
       </c>
       <c r="AC6" s="18">
         <f t="shared" si="4"/>
-        <v>6456819.9140625</v>
+        <v>6652526.6162109375</v>
       </c>
       <c r="AD6" s="7">
         <f>IF($A6=1,VARIABLES!$B$12,0)</f>
@@ -4485,11 +4486,11 @@
       </c>
       <c r="AK6" s="21">
         <f t="shared" si="6"/>
-        <v>-17780.1015625</v>
+        <v>-8157.7542317708339</v>
       </c>
       <c r="AL6" s="21">
         <f t="shared" si="7"/>
-        <v>-91410.059895833314</v>
+        <v>-72862.4521484375</v>
       </c>
       <c r="AM6" s="22">
         <f t="shared" si="8"/>
@@ -4506,7 +4507,7 @@
       </c>
       <c r="C7" s="24">
         <f>IF($A7&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$21,0,IF($A7=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4518,11 +4519,11 @@
       </c>
       <c r="F7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$21,0,(IF($A7=VARIABLES!$B$21,0,G6)+D7)*C7*VARIABLES!$B$25)</f>
-        <v>975.0523242187503</v>
+        <v>1508.0913562011719</v>
       </c>
       <c r="G7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$21,0,(IF($A7=VARIABLES!$B$21,0,G6)+D7)*(1+C7)-F7)</f>
-        <v>1208089.8297070316</v>
+        <v>1265288.6478527833</v>
       </c>
       <c r="H7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$28,0,IF($A7=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4534,11 +4535,11 @@
       </c>
       <c r="J7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$28,0,(IF($A7=VARIABLES!$B$28,0,K6)+H7)*C7*VARIABLES!$B$32)</f>
-        <v>412.12</v>
+        <v>627.40499999999997</v>
       </c>
       <c r="K7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$28,0,(IF($A7=VARIABLES!$B$28,0,K6)+H7)*(1+C7)-J7)</f>
-        <v>127345.08000000002</v>
+        <v>131127.64500000002</v>
       </c>
       <c r="L7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$35,0,IF($A7=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4550,11 +4551,11 @@
       </c>
       <c r="N7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$35,0,(IF($A7=VARIABLES!$B$35,0,O6)+L7)*C7*VARIABLES!$B$39)</f>
-        <v>17681.666666666668</v>
+        <v>27300.625</v>
       </c>
       <c r="O7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$35,0,(IF($A7=VARIABLES!$B$35,0,O6)+L7)*(1+C7)-N7)</f>
-        <v>5463635</v>
+        <v>5705830.625</v>
       </c>
       <c r="P7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$42,0,IF($A7=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4566,11 +4567,11 @@
       </c>
       <c r="R7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$42,0,(IF($A7=VARIABLES!$B$42,0,S6)+P7)*C7*VARIABLES!$B$46)</f>
-        <v>51.642604166666672</v>
+        <v>78.715664062499997</v>
       </c>
       <c r="S7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$42,0,(IF($A7=VARIABLES!$B$42,0,S6)+P7)*(1+C7)-R7)</f>
-        <v>63985.186562500014</v>
+        <v>66042.442148437505</v>
       </c>
       <c r="T7" s="26">
         <f>IF($A7&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A7-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -4586,11 +4587,11 @@
       </c>
       <c r="W7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$50,0,(IF($A7&lt;VARIABLES!$B$50+1,0,X6)+U7)*C7*VARIABLES!$B$56)</f>
-        <v>388.83333333333337</v>
+        <v>587.37499999999989</v>
       </c>
       <c r="X7" s="25">
         <f>IF($A7&lt;VARIABLES!$B$50,0,(IF($A7&lt;VARIABLES!$B$50+1,0,X6)+U7)*(1+C7)-W7)</f>
-        <v>120149.50000000001</v>
+        <v>122761.375</v>
       </c>
       <c r="Y7" s="25">
         <f t="shared" si="0"/>
@@ -4602,15 +4603,15 @@
       </c>
       <c r="AA7" s="25">
         <f t="shared" si="2"/>
-        <v>19509.314928385418</v>
+        <v>30102.212020263672</v>
       </c>
       <c r="AB7" s="17">
         <f t="shared" si="3"/>
-        <v>21909.314928385418</v>
+        <v>32502.212020263672</v>
       </c>
       <c r="AC7" s="18">
         <f t="shared" si="4"/>
-        <v>6983204.5962695321</v>
+        <v>7291050.7350012213</v>
       </c>
       <c r="AD7" s="25">
         <f>IF($A7=1,VARIABLES!$B$12,0)</f>
@@ -4642,11 +4643,11 @@
       </c>
       <c r="AK7" s="27">
         <f t="shared" si="6"/>
-        <v>-28170.768404947914</v>
+        <v>-17577.871313069663</v>
       </c>
       <c r="AL7" s="27">
         <f t="shared" si="7"/>
-        <v>-119580.82830078123</v>
+        <v>-90440.323461507156</v>
       </c>
       <c r="AM7" s="22">
         <f t="shared" si="8"/>
@@ -4663,7 +4664,7 @@
       </c>
       <c r="C8" s="15">
         <f>IF($A8&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$21,0,IF($A8=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4675,11 +4676,11 @@
       </c>
       <c r="F8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$21,0,(IF($A8=VARIABLES!$B$21,0,G7)+D8)*C8*VARIABLES!$B$25)</f>
-        <v>1173.4081914225264</v>
+        <v>1831.6108098159793</v>
       </c>
       <c r="G8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$21,0,(IF($A8=VARIABLES!$B$21,0,G7)+D8)*(1+C8)-F8)</f>
-        <v>1453852.7491725103</v>
+        <v>1536721.4694356066</v>
       </c>
       <c r="H8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$28,0,IF($A8=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4691,11 +4692,11 @@
       </c>
       <c r="J8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$28,0,(IF($A8=VARIABLES!$B$28,0,K7)+H8)*C8*VARIABLES!$B$32)</f>
-        <v>557.8169333333334</v>
+        <v>855.63822500000015</v>
       </c>
       <c r="K8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$28,0,(IF($A8=VARIABLES!$B$28,0,K7)+H8)*(1+C8)-J8)</f>
-        <v>172365.43240000005</v>
+        <v>178828.38902500001</v>
       </c>
       <c r="L8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$35,0,IF($A8=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4707,11 +4708,11 @@
       </c>
       <c r="N8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$35,0,(IF($A8=VARIABLES!$B$35,0,O7)+L8)*C8*VARIABLES!$B$39)</f>
-        <v>18212.116666666665</v>
+        <v>28529.153125000001</v>
       </c>
       <c r="O8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$35,0,(IF($A8=VARIABLES!$B$35,0,O7)+L8)*(1+C8)-N8)</f>
-        <v>5627544.0500000007</v>
+        <v>5962593.0031249998</v>
       </c>
       <c r="P8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$42,0,IF($A8=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4723,11 +4724,11 @@
       </c>
       <c r="R8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$42,0,(IF($A8=VARIABLES!$B$42,0,S7)+P8)*C8*VARIABLES!$B$46)</f>
-        <v>69.98765546875002</v>
+        <v>107.55305268554687</v>
       </c>
       <c r="S8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$42,0,(IF($A8=VARIABLES!$B$42,0,S7)+P8)*(1+C8)-R8)</f>
-        <v>86714.705125781285</v>
+        <v>90237.011203173839</v>
       </c>
       <c r="T8" s="16">
         <f>IF($A8&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A8-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -4743,11 +4744,11 @@
       </c>
       <c r="W8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$50,0,(IF($A8&lt;VARIABLES!$B$50+1,0,X7)+U8)*C8*VARIABLES!$B$56)</f>
-        <v>617.16499999999996</v>
+        <v>938.80687499999988</v>
       </c>
       <c r="X8" s="7">
         <f>IF($A8&lt;VARIABLES!$B$50,0,(IF($A8&lt;VARIABLES!$B$50+1,0,X7)+U8)*(1+C8)-W8)</f>
-        <v>190703.98500000002</v>
+        <v>196210.636875</v>
       </c>
       <c r="Y8" s="7">
         <f t="shared" si="0"/>
@@ -4759,15 +4760,15 @@
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="2"/>
-        <v>20630.494446891276</v>
+        <v>32262.762087501527</v>
       </c>
       <c r="AB8" s="17">
         <f t="shared" si="3"/>
-        <v>23067.994446891276</v>
+        <v>34700.262087501527</v>
       </c>
       <c r="AC8" s="18">
         <f t="shared" si="4"/>
-        <v>7531180.9216982927</v>
+        <v>7964590.5096637793</v>
       </c>
       <c r="AD8" s="7">
         <f>IF($A8=1,VARIABLES!$B$12,0)</f>
@@ -4799,11 +4800,11 @@
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="6"/>
-        <v>-27012.088886442056</v>
+        <v>-15379.821245831807</v>
       </c>
       <c r="AL8" s="21">
         <f t="shared" si="7"/>
-        <v>-146592.91718722327</v>
+        <v>-105820.14470733896</v>
       </c>
       <c r="AM8" s="22">
         <f t="shared" si="8"/>
@@ -4820,7 +4821,7 @@
       </c>
       <c r="C9" s="24">
         <f>IF($A9&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$21,0,IF($A9=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4832,11 +4833,11 @@
       </c>
       <c r="F9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$21,0,(IF($A9=VARIABLES!$B$21,0,G8)+D9)*C9*VARIABLES!$B$25)</f>
-        <v>1378.2106243104254</v>
+        <v>2170.9018367945082</v>
       </c>
       <c r="G9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$21,0,(IF($A9=VARIABLES!$B$21,0,G8)+D9)*(1+C9)-F9)</f>
-        <v>1707602.9635206172</v>
+        <v>1821386.6410705924</v>
       </c>
       <c r="H9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$28,0,IF($A9=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -4848,11 +4849,11 @@
       </c>
       <c r="J9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$28,0,(IF($A9=VARIABLES!$B$28,0,K8)+H9)*C9*VARIABLES!$B$32)</f>
-        <v>707.88477466666689</v>
+        <v>1094.1419451250001</v>
       </c>
       <c r="K9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$28,0,(IF($A9=VARIABLES!$B$28,0,K8)+H9)*(1+C9)-J9)</f>
-        <v>218736.39537200009</v>
+        <v>228675.666531125</v>
       </c>
       <c r="L9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$35,0,IF($A9=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -4864,11 +4865,11 @@
       </c>
       <c r="N9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$35,0,(IF($A9=VARIABLES!$B$35,0,O8)+L9)*C9*VARIABLES!$B$39)</f>
-        <v>18758.480166666672</v>
+        <v>29812.965015624999</v>
       </c>
       <c r="O9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$35,0,(IF($A9=VARIABLES!$B$35,0,O8)+L9)*(1+C9)-N9)</f>
-        <v>5796370.3715000022</v>
+        <v>6230909.6882656254</v>
       </c>
       <c r="P9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$42,0,IF($A9=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -4880,11 +4881,11 @@
       </c>
       <c r="R9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$42,0,(IF($A9=VARIABLES!$B$42,0,S8)+P9)*C9*VARIABLES!$B$46)</f>
-        <v>88.928920938151066</v>
+        <v>137.79626400396728</v>
       </c>
       <c r="S9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$42,0,(IF($A9=VARIABLES!$B$42,0,S8)+P9)*(1+C9)-R9)</f>
-        <v>110182.93304236919</v>
+        <v>115611.06549932857</v>
       </c>
       <c r="T9" s="26">
         <f>IF($A9&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A9-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -4900,11 +4901,11 @@
       </c>
       <c r="W9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$50,0,(IF($A9&lt;VARIABLES!$B$50+1,0,X8)+U9)*C9*VARIABLES!$B$56)</f>
-        <v>869.01328333333333</v>
+        <v>1331.0531843749998</v>
       </c>
       <c r="X9" s="25">
         <f>IF($A9&lt;VARIABLES!$B$50,0,(IF($A9&lt;VARIABLES!$B$50+1,0,X8)+U9)*(1+C9)-W9)</f>
-        <v>268525.10455000005</v>
+        <v>278190.11553437501</v>
       </c>
       <c r="Y9" s="25">
         <f t="shared" si="0"/>
@@ -4916,15 +4917,15 @@
       </c>
       <c r="AA9" s="25">
         <f t="shared" si="2"/>
-        <v>21802.517769915248</v>
+        <v>34546.858245923475</v>
       </c>
       <c r="AB9" s="17">
         <f t="shared" si="3"/>
-        <v>24277.517769915248</v>
+        <v>37021.858245923475</v>
       </c>
       <c r="AC9" s="18">
         <f t="shared" si="4"/>
-        <v>8101417.7679849891</v>
+        <v>8674773.1769010462</v>
       </c>
       <c r="AD9" s="25">
         <f>IF($A9=1,VARIABLES!$B$12,0)</f>
@@ -4956,11 +4957,11 @@
       </c>
       <c r="AK9" s="27">
         <f t="shared" si="6"/>
-        <v>-25802.565563418088</v>
+        <v>-13058.225087409859</v>
       </c>
       <c r="AL9" s="27">
         <f t="shared" si="7"/>
-        <v>-172395.48275064136</v>
+        <v>-118878.36979474881</v>
       </c>
       <c r="AM9" s="22">
         <f t="shared" si="8"/>
@@ -4977,7 +4978,7 @@
       </c>
       <c r="C10" s="15">
         <f>IF($A10&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$21,0,IF($A10=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -4989,11 +4990,11 @@
       </c>
       <c r="F10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$21,0,(IF($A10=VARIABLES!$B$21,0,G9)+D10)*C10*VARIABLES!$B$25)</f>
-        <v>1589.6691362671811</v>
+        <v>2526.7333013382404</v>
       </c>
       <c r="G10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$21,0,(IF($A10=VARIABLES!$B$21,0,G9)+D10)*(1+C10)-F10)</f>
-        <v>1969600.0598350374</v>
+        <v>2119929.239822784</v>
       </c>
       <c r="H10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$28,0,IF($A10=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5005,11 +5006,11 @@
       </c>
       <c r="J10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$28,0,(IF($A10=VARIABLES!$B$28,0,K9)+H10)*C10*VARIABLES!$B$32)</f>
-        <v>862.4546512400002</v>
+        <v>1343.3783326556249</v>
       </c>
       <c r="K10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$28,0,(IF($A10=VARIABLES!$B$28,0,K9)+H10)*(1+C10)-J10)</f>
-        <v>266498.48723316006</v>
+        <v>280766.07152502559</v>
       </c>
       <c r="L10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$35,0,IF($A10=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5021,11 +5022,11 @@
       </c>
       <c r="N10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$35,0,(IF($A10=VARIABLES!$B$35,0,O9)+L10)*C10*VARIABLES!$B$39)</f>
-        <v>19321.234571666675</v>
+        <v>31154.548441328127</v>
       </c>
       <c r="O10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$35,0,(IF($A10=VARIABLES!$B$35,0,O9)+L10)*(1+C10)-N10)</f>
-        <v>5970261.4826450031</v>
+        <v>6511300.6242375784</v>
       </c>
       <c r="P10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$42,0,IF($A10=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5037,11 +5038,11 @@
       </c>
       <c r="R10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$42,0,(IF($A10=VARIABLES!$B$42,0,S9)+P10)*C10*VARIABLES!$B$46)</f>
-        <v>108.48577753530765</v>
+        <v>169.5138318741607</v>
       </c>
       <c r="S10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$42,0,(IF($A10=VARIABLES!$B$42,0,S9)+P10)*(1+C10)-R10)</f>
-        <v>134413.87836624621</v>
+        <v>142222.10494242085</v>
       </c>
       <c r="T10" s="16">
         <f>IF($A10&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A10-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -5057,11 +5058,11 @@
       </c>
       <c r="W10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$50,0,(IF($A10&lt;VARIABLES!$B$50+1,0,X9)+U10)*C10*VARIABLES!$B$56)</f>
-        <v>1145.0836818333335</v>
+        <v>1765.9505776718752</v>
       </c>
       <c r="X10" s="7">
         <f>IF($A10&lt;VARIABLES!$B$50,0,(IF($A10&lt;VARIABLES!$B$50+1,0,X9)+U10)*(1+C10)-W10)</f>
-        <v>353830.85768650007</v>
+        <v>369083.67073342192</v>
       </c>
       <c r="Y10" s="7">
         <f t="shared" si="0"/>
@@ -5073,15 +5074,15 @@
       </c>
       <c r="AA10" s="7">
         <f t="shared" si="2"/>
-        <v>23026.927818542499</v>
+        <v>36960.124484868022</v>
       </c>
       <c r="AB10" s="17">
         <f t="shared" si="3"/>
-        <v>25539.427818542499</v>
+        <v>39472.624484868022</v>
       </c>
       <c r="AC10" s="18">
         <f t="shared" si="4"/>
-        <v>8694604.7657659464</v>
+        <v>9423301.7112612296</v>
       </c>
       <c r="AD10" s="7">
         <f>IF($A10=1,VARIABLES!$B$12,0)</f>
@@ -5113,11 +5114,11 @@
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="6"/>
-        <v>-36040.655514790837</v>
+        <v>-22107.458848465314</v>
       </c>
       <c r="AL10" s="21">
         <f t="shared" si="7"/>
-        <v>-208436.13826543221</v>
+        <v>-140985.82864321413</v>
       </c>
       <c r="AM10" s="22">
         <f t="shared" si="8"/>
@@ -5134,7 +5135,7 @@
       </c>
       <c r="C11" s="24">
         <f>IF($A11&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$21,0,IF($A11=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5146,11 +5147,11 @@
       </c>
       <c r="F11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$21,0,(IF($A11=VARIABLES!$B$21,0,G10)+D11)*C11*VARIABLES!$B$25)</f>
-        <v>1808.0000498625313</v>
+        <v>2899.9115497784801</v>
       </c>
       <c r="G11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$21,0,(IF($A11=VARIABLES!$B$21,0,G10)+D11)*(1+C11)-F11)</f>
-        <v>2240112.061779676</v>
+        <v>2433025.7902641445</v>
       </c>
       <c r="H11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$28,0,IF($A11=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5162,11 +5163,11 @@
       </c>
       <c r="J11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$28,0,(IF($A11=VARIABLES!$B$28,0,K10)+H11)*C11*VARIABLES!$B$32)</f>
-        <v>1021.6616241105336</v>
+        <v>1603.8303576251278</v>
       </c>
       <c r="K11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$28,0,(IF($A11=VARIABLES!$B$28,0,K10)+H11)*(1+C11)-J11)</f>
-        <v>315693.44185015489</v>
+        <v>335200.54474365176</v>
       </c>
       <c r="L11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$35,0,IF($A11=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5178,11 +5179,11 @@
       </c>
       <c r="N11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$35,0,(IF($A11=VARIABLES!$B$35,0,O10)+L11)*C11*VARIABLES!$B$39)</f>
-        <v>19900.87160881668</v>
+        <v>32556.503121187889</v>
       </c>
       <c r="O11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$35,0,(IF($A11=VARIABLES!$B$35,0,O10)+L11)*(1+C11)-N11)</f>
-        <v>6149369.3271243535</v>
+        <v>6804309.1523282696</v>
       </c>
       <c r="P11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$42,0,IF($A11=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5194,11 +5195,11 @@
       </c>
       <c r="R11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$42,0,(IF($A11=VARIABLES!$B$42,0,S10)+P11)*C11*VARIABLES!$B$46)</f>
-        <v>128.67823197187184</v>
+        <v>202.77763117802604</v>
       </c>
       <c r="S11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$42,0,(IF($A11=VARIABLES!$B$42,0,S10)+P11)*(1+C11)-R11)</f>
-        <v>159432.32941314924</v>
+        <v>170130.43255836386</v>
       </c>
       <c r="T11" s="26">
         <f>IF($A11&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A11-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -5214,11 +5215,11 @@
       </c>
       <c r="W11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$50,0,(IF($A11&lt;VARIABLES!$B$50+1,0,X10)+U11)*C11*VARIABLES!$B$56)</f>
-        <v>1446.1028589550003</v>
+        <v>2245.4183536671094</v>
       </c>
       <c r="X11" s="25">
         <f>IF($A11&lt;VARIABLES!$B$50,0,(IF($A11&lt;VARIABLES!$B$50+1,0,X10)+U11)*(1+C11)-W11)</f>
-        <v>446845.78341709514</v>
+        <v>469292.43591642589</v>
       </c>
       <c r="Y11" s="25">
         <f t="shared" si="0"/>
@@ -5230,15 +5231,15 @@
       </c>
       <c r="AA11" s="25">
         <f t="shared" si="2"/>
-        <v>24305.314373716617</v>
+        <v>39508.441013436634</v>
       </c>
       <c r="AB11" s="17">
         <f t="shared" si="3"/>
-        <v>26855.314373716617</v>
+        <v>42058.441013436634</v>
       </c>
       <c r="AC11" s="18">
         <f t="shared" si="4"/>
-        <v>9311452.9435844272</v>
+        <v>10211958.355810855</v>
       </c>
       <c r="AD11" s="25">
         <f>IF($A11=1,VARIABLES!$B$12,0)</f>
@@ -5270,11 +5271,11 @@
       </c>
       <c r="AK11" s="27">
         <f t="shared" si="6"/>
-        <v>-34724.768959616718</v>
+        <v>-19521.642319896702</v>
       </c>
       <c r="AL11" s="27">
         <f t="shared" si="7"/>
-        <v>-243160.90722504893</v>
+        <v>-160507.47096311083</v>
       </c>
       <c r="AM11" s="22">
         <f t="shared" si="8"/>
@@ -5291,7 +5292,7 @@
       </c>
       <c r="C12" s="15">
         <f>IF($A12&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$21,0,IF($A12=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5303,11 +5304,11 @@
       </c>
       <c r="F12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$21,0,(IF($A12=VARIABLES!$B$21,0,G11)+D12)*C12*VARIABLES!$B$25)</f>
-        <v>2033.42671814973</v>
+        <v>3291.2822378301807</v>
       </c>
       <c r="G12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$21,0,(IF($A12=VARIABLES!$B$21,0,G11)+D12)*(1+C12)-F12)</f>
-        <v>2519415.7037875159</v>
+        <v>2761385.7975395219</v>
       </c>
       <c r="H12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$28,0,IF($A12=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5319,11 +5320,11 @@
       </c>
       <c r="J12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$28,0,(IF($A12=VARIABLES!$B$28,0,K11)+H12)*C12*VARIABLES!$B$32)</f>
-        <v>1185.6448061671831</v>
+        <v>1876.0027237182585</v>
       </c>
       <c r="K12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$28,0,(IF($A12=VARIABLES!$B$28,0,K11)+H12)*(1+C12)-J12)</f>
-        <v>366364.24510565959</v>
+        <v>392084.56925711612</v>
       </c>
       <c r="L12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$35,0,IF($A12=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5335,11 +5336,11 @@
       </c>
       <c r="N12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$35,0,(IF($A12=VARIABLES!$B$35,0,O11)+L12)*C12*VARIABLES!$B$39)</f>
-        <v>20497.89775708118</v>
+        <v>34021.545761641348</v>
       </c>
       <c r="O12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$35,0,(IF($A12=VARIABLES!$B$35,0,O11)+L12)*(1+C12)-N12)</f>
-        <v>6333850.4069380844</v>
+        <v>7110503.0641830424</v>
       </c>
       <c r="P12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$42,0,IF($A12=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5351,11 +5352,11 @@
       </c>
       <c r="R12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$42,0,(IF($A12=VARIABLES!$B$42,0,S11)+P12)*C12*VARIABLES!$B$46)</f>
-        <v>149.52694117762437</v>
+        <v>237.66304069795478</v>
       </c>
       <c r="S12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$42,0,(IF($A12=VARIABLES!$B$42,0,S11)+P12)*(1+C12)-R12)</f>
-        <v>185263.88011907664</v>
+        <v>199399.29114558411</v>
       </c>
       <c r="T12" s="16">
         <f>IF($A12&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A12-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -5371,11 +5372,11 @@
       </c>
       <c r="W12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$50,0,(IF($A12&lt;VARIABLES!$B$50+1,0,X11)+U12)*C12*VARIABLES!$B$56)</f>
-        <v>1772.8192780569841</v>
+        <v>2771.4621795821295</v>
       </c>
       <c r="X12" s="7">
         <f>IF($A12&lt;VARIABLES!$B$50,0,(IF($A12&lt;VARIABLES!$B$50+1,0,X11)+U12)*(1+C12)-W12)</f>
-        <v>547801.15691960813</v>
+        <v>579235.59553266515</v>
       </c>
       <c r="Y12" s="7">
         <f t="shared" si="0"/>
@@ -5387,15 +5388,15 @@
       </c>
       <c r="AA12" s="7">
         <f t="shared" si="2"/>
-        <v>25639.315500632703</v>
+        <v>42197.955943469868</v>
       </c>
       <c r="AB12" s="17">
         <f t="shared" si="3"/>
-        <v>28226.815500632703</v>
+        <v>44785.455943469868</v>
       </c>
       <c r="AC12" s="18">
         <f t="shared" si="4"/>
-        <v>9952695.3928699438</v>
+        <v>11042608.317657929</v>
       </c>
       <c r="AD12" s="7">
         <f>IF($A12=1,VARIABLES!$B$12,0)</f>
@@ -5427,11 +5428,11 @@
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="6"/>
-        <v>-33353.267832700629</v>
+        <v>-16794.627389863468</v>
       </c>
       <c r="AL12" s="21">
         <f t="shared" si="7"/>
-        <v>-276514.17505774955</v>
+        <v>-177302.09835297428</v>
       </c>
       <c r="AM12" s="22">
         <f t="shared" si="8"/>
@@ -5448,7 +5449,7 @@
       </c>
       <c r="C13" s="24">
         <f>IF($A13&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$21,0,IF($A13=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5460,11 +5461,11 @@
       </c>
       <c r="F13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$21,0,(IF($A13=VARIABLES!$B$21,0,G12)+D13)*C13*VARIABLES!$B$25)</f>
-        <v>2266.1797531562634</v>
+        <v>3701.7322469244023</v>
       </c>
       <c r="G13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$21,0,(IF($A13=VARIABLES!$B$21,0,G12)+D13)*(1+C13)-F13)</f>
-        <v>2807796.7141606105</v>
+        <v>3105753.3551695738</v>
       </c>
       <c r="H13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$28,0,IF($A13=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5476,11 +5477,11 @@
       </c>
       <c r="J13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$28,0,(IF($A13=VARIABLES!$B$28,0,K12)+H13)*C13*VARIABLES!$B$32)</f>
-        <v>1354.5474836855319</v>
+        <v>2160.4228462855804</v>
       </c>
       <c r="K13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$28,0,(IF($A13=VARIABLES!$B$28,0,K12)+H13)*(1+C13)-J13)</f>
-        <v>418555.17245882942</v>
+        <v>451528.37487368635</v>
       </c>
       <c r="L13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$35,0,IF($A13=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5492,11 +5493,11 @@
       </c>
       <c r="N13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$35,0,(IF($A13=VARIABLES!$B$35,0,O12)+L13)*C13*VARIABLES!$B$39)</f>
-        <v>21112.834689793614</v>
+        <v>35552.515320915212</v>
       </c>
       <c r="O13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$35,0,(IF($A13=VARIABLES!$B$35,0,O12)+L13)*(1+C13)-N13)</f>
-        <v>6523865.9191462277</v>
+        <v>7430475.7020712802</v>
       </c>
       <c r="P13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$42,0,IF($A13=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5508,11 +5509,11 @@
       </c>
       <c r="R13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$42,0,(IF($A13=VARIABLES!$B$42,0,S12)+P13)*C13*VARIABLES!$B$46)</f>
-        <v>171.05323343256387</v>
+        <v>274.24911393198016</v>
       </c>
       <c r="S13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$42,0,(IF($A13=VARIABLES!$B$42,0,S12)+P13)*(1+C13)-R13)</f>
-        <v>211934.95622294667</v>
+        <v>230095.00658893134</v>
       </c>
       <c r="T13" s="26">
         <f>IF($A13&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A13-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -5528,11 +5529,11 @@
       </c>
       <c r="W13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$50,0,(IF($A13&lt;VARIABLES!$B$50+1,0,X12)+U13)*C13*VARIABLES!$B$56)</f>
-        <v>2126.0038563986941</v>
+        <v>3346.1779776633252</v>
       </c>
       <c r="X13" s="25">
         <f>IF($A13&lt;VARIABLES!$B$50,0,(IF($A13&lt;VARIABLES!$B$50+1,0,X12)+U13)*(1+C13)-W13)</f>
-        <v>656935.19162719639</v>
+        <v>699351.19733163505</v>
       </c>
       <c r="Y13" s="25">
         <f t="shared" si="0"/>
@@ -5544,15 +5545,15 @@
       </c>
       <c r="AA13" s="25">
         <f t="shared" si="2"/>
-        <v>27030.619016466666</v>
+        <v>45035.097505720507</v>
       </c>
       <c r="AB13" s="17">
         <f t="shared" si="3"/>
-        <v>29655.619016466666</v>
+        <v>47660.097505720507</v>
       </c>
       <c r="AC13" s="18">
         <f t="shared" si="4"/>
-        <v>10619087.953615811</v>
+        <v>11917203.636035109</v>
       </c>
       <c r="AD13" s="25">
         <f>IF($A13=1,VARIABLES!$B$12,0)</f>
@@ -5584,11 +5585,11 @@
       </c>
       <c r="AK13" s="27">
         <f t="shared" si="6"/>
-        <v>-31924.464316866666</v>
+        <v>-13919.985827612827</v>
       </c>
       <c r="AL13" s="27">
         <f t="shared" si="7"/>
-        <v>-308438.63937461621</v>
+        <v>-191222.08418058712</v>
       </c>
       <c r="AM13" s="22">
         <f t="shared" si="8"/>
@@ -5605,7 +5606,7 @@
       </c>
       <c r="C14" s="15">
         <f>IF($A14&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$21,0,IF($A14=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5617,11 +5618,11 @@
       </c>
       <c r="F14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$21,0,(IF($A14=VARIABLES!$B$21,0,G13)+D14)*C14*VARIABLES!$B$25)</f>
-        <v>2506.4972618005086</v>
+        <v>4132.1916939619668</v>
       </c>
       <c r="G14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$21,0,(IF($A14=VARIABLES!$B$21,0,G13)+D14)*(1+C14)-F14)</f>
-        <v>3105550.1073708306</v>
+        <v>3466908.8312340905</v>
       </c>
       <c r="H14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$28,0,IF($A14=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5633,11 +5634,11 @@
       </c>
       <c r="J14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$28,0,(IF($A14=VARIABLES!$B$28,0,K13)+H14)*C14*VARIABLES!$B$32)</f>
-        <v>1528.5172415294314</v>
+        <v>2457.6418743684317</v>
       </c>
       <c r="K14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$28,0,(IF($A14=VARIABLES!$B$28,0,K13)+H14)*(1+C14)-J14)</f>
-        <v>472311.82763259433</v>
+        <v>513647.15174300229</v>
       </c>
       <c r="L14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$35,0,IF($A14=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5649,11 +5650,11 @@
       </c>
       <c r="N14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$35,0,(IF($A14=VARIABLES!$B$35,0,O13)+L14)*C14*VARIABLES!$B$39)</f>
-        <v>21746.219730487428</v>
+        <v>37152.378510356401</v>
       </c>
       <c r="O14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$35,0,(IF($A14=VARIABLES!$B$35,0,O13)+L14)*(1+C14)-N14)</f>
-        <v>6719581.8967206152</v>
+        <v>7764847.1086644884</v>
       </c>
       <c r="P14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$42,0,IF($A14=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5665,11 +5666,11 @@
       </c>
       <c r="R14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$42,0,(IF($A14=VARIABLES!$B$42,0,S13)+P14)*C14*VARIABLES!$B$46)</f>
-        <v>193.27913018578889</v>
+        <v>312.61875823616418</v>
       </c>
       <c r="S14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$42,0,(IF($A14=VARIABLES!$B$42,0,S13)+P14)*(1+C14)-R14)</f>
-        <v>239472.84230019248</v>
+        <v>262287.13816014177</v>
       </c>
       <c r="T14" s="16">
         <f>IF($A14&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A14-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -5685,11 +5686,11 @@
       </c>
       <c r="W14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$50,0,(IF($A14&lt;VARIABLES!$B$50+1,0,X13)+U14)*C14*VARIABLES!$B$56)</f>
-        <v>2506.4506387573215</v>
+        <v>3971.7559866581755</v>
       </c>
       <c r="X14" s="7">
         <f>IF($A14&lt;VARIABLES!$B$50,0,(IF($A14&lt;VARIABLES!$B$50+1,0,X13)+U14)*(1+C14)-W14)</f>
-        <v>774493.24737601238</v>
+        <v>830097.0012115587</v>
       </c>
       <c r="Y14" s="7">
         <f t="shared" si="0"/>
@@ -5701,15 +5702,15 @@
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="2"/>
-        <v>28480.96400276048</v>
+        <v>48026.586823581136</v>
       </c>
       <c r="AB14" s="17">
         <f t="shared" si="3"/>
-        <v>31143.46400276048</v>
+        <v>50689.086823581136</v>
       </c>
       <c r="AC14" s="18">
         <f t="shared" si="4"/>
-        <v>11311409.921400245</v>
+        <v>12837787.231013281</v>
       </c>
       <c r="AD14" s="7">
         <f>IF($A14=1,VARIABLES!$B$12,0)</f>
@@ -5741,11 +5742,11 @@
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="6"/>
-        <v>-30436.619330572852</v>
+        <v>-10890.996509752198</v>
       </c>
       <c r="AL14" s="21">
         <f t="shared" si="7"/>
-        <v>-338875.25870518904</v>
+        <v>-202113.08069033932</v>
       </c>
       <c r="AM14" s="22">
         <f t="shared" si="8"/>
@@ -5762,7 +5763,7 @@
       </c>
       <c r="C15" s="24">
         <f>IF($A15&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$21,0,IF($A15=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5774,11 +5775,11 @@
       </c>
       <c r="F15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$21,0,(IF($A15=VARIABLES!$B$21,0,G14)+D15)*C15*VARIABLES!$B$25)</f>
-        <v>2754.6250894756922</v>
+        <v>4583.6360390426125</v>
       </c>
       <c r="G15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$21,0,(IF($A15=VARIABLES!$B$21,0,G14)+D15)*(1+C15)-F15)</f>
-        <v>3412980.4858603827</v>
+        <v>3845670.6367567526</v>
       </c>
       <c r="H15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$28,0,IF($A15=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5790,11 +5791,11 @@
       </c>
       <c r="J15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$28,0,(IF($A15=VARIABLES!$B$28,0,K14)+H15)*C15*VARIABLES!$B$32)</f>
-        <v>1707.7060921086479</v>
+        <v>2768.2357587150109</v>
       </c>
       <c r="K15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$28,0,(IF($A15=VARIABLES!$B$28,0,K14)+H15)*(1+C15)-J15)</f>
-        <v>527681.18246157223</v>
+        <v>578561.27357143746</v>
       </c>
       <c r="L15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$35,0,IF($A15=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5806,11 +5807,11 @@
       </c>
       <c r="N15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$35,0,(IF($A15=VARIABLES!$B$35,0,O14)+L15)*C15*VARIABLES!$B$39)</f>
-        <v>22398.606322402051</v>
+        <v>38824.235543322444</v>
       </c>
       <c r="O15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$35,0,(IF($A15=VARIABLES!$B$35,0,O14)+L15)*(1+C15)-N15)</f>
-        <v>6921169.3536222344</v>
+        <v>8114265.2285543904</v>
       </c>
       <c r="P15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$42,0,IF($A15=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5822,11 +5823,11 @@
       </c>
       <c r="R15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$42,0,(IF($A15=VARIABLES!$B$42,0,S14)+P15)*C15*VARIABLES!$B$46)</f>
-        <v>216.22736858349373</v>
+        <v>352.85892270017717</v>
       </c>
       <c r="S15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$42,0,(IF($A15=VARIABLES!$B$42,0,S14)+P15)*(1+C15)-R15)</f>
-        <v>267905.70967494877</v>
+        <v>296048.63614544872</v>
       </c>
       <c r="T15" s="26">
         <f>IF($A15&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A15-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -5842,11 +5843,11 @@
       </c>
       <c r="W15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$50,0,(IF($A15&lt;VARIABLES!$B$50+1,0,X14)+U15)*C15*VARIABLES!$B$56)</f>
-        <v>2914.9774912533749</v>
+        <v>4650.4850060577937</v>
       </c>
       <c r="X15" s="25">
         <f>IF($A15&lt;VARIABLES!$B$50,0,(IF($A15&lt;VARIABLES!$B$50+1,0,X14)+U15)*(1+C15)-W15)</f>
-        <v>900728.04479729279</v>
+        <v>971951.3662660789</v>
       </c>
       <c r="Y15" s="25">
         <f t="shared" si="0"/>
@@ -5858,15 +5859,15 @@
       </c>
       <c r="AA15" s="25">
         <f t="shared" si="2"/>
-        <v>29992.142363823263</v>
+        <v>51179.451269838042</v>
       </c>
       <c r="AB15" s="17">
         <f t="shared" si="3"/>
-        <v>32692.142363823263</v>
+        <v>53879.451269838042</v>
       </c>
       <c r="AC15" s="18">
         <f t="shared" si="4"/>
-        <v>12030464.77641643</v>
+        <v>13806497.141294109</v>
       </c>
       <c r="AD15" s="25">
         <f>IF($A15=1,VARIABLES!$B$12,0)</f>
@@ -5878,7 +5879,7 @@
       </c>
       <c r="AF15" s="25">
         <f>IF(MOD($A15,12)=0,AC15*VARIABLES!$B$16,0)</f>
-        <v>30076.161941041075</v>
+        <v>34516.242853235271</v>
       </c>
       <c r="AG15" s="25">
         <f>VARIABLES!$B$17</f>
@@ -5890,7 +5891,7 @@
       </c>
       <c r="AI15" s="19">
         <f t="shared" si="5"/>
-        <v>84076.161941041079</v>
+        <v>88516.242853235279</v>
       </c>
       <c r="AJ15" s="20">
         <f>IF($A15&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -5898,11 +5899,11 @@
       </c>
       <c r="AK15" s="27">
         <f t="shared" si="6"/>
-        <v>-61964.102910551148</v>
+        <v>-45216.874916730572</v>
       </c>
       <c r="AL15" s="27">
         <f t="shared" si="7"/>
-        <v>-400839.36161574017</v>
+        <v>-247329.95560706989</v>
       </c>
       <c r="AM15" s="22">
         <f t="shared" si="8"/>
@@ -5919,7 +5920,7 @@
       </c>
       <c r="C16" s="15">
         <f>IF($A16&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$21,0,IF($A16=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -5931,11 +5932,11 @@
       </c>
       <c r="F16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$21,0,(IF($A16=VARIABLES!$B$21,0,G15)+D16)*C16*VARIABLES!$B$25)</f>
-        <v>3010.8170715503188</v>
+        <v>5057.0882959459414</v>
       </c>
       <c r="G16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$21,0,(IF($A16=VARIABLES!$B$21,0,G15)+D16)*(1+C16)-F16)</f>
-        <v>3730402.3516508453</v>
+        <v>4242897.0802986445</v>
       </c>
       <c r="H16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$28,0,IF($A16=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -5947,11 +5948,11 @@
       </c>
       <c r="J16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$28,0,(IF($A16=VARIABLES!$B$28,0,K15)+H16)*C16*VARIABLES!$B$32)</f>
-        <v>1892.2706082052407</v>
+        <v>3092.8063678571871</v>
       </c>
       <c r="K16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$28,0,(IF($A16=VARIABLES!$B$28,0,K15)+H16)*(1+C16)-J16)</f>
-        <v>584711.61793541943</v>
+        <v>646396.53088215226</v>
       </c>
       <c r="L16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$35,0,IF($A16=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -5963,11 +5964,11 @@
       </c>
       <c r="N16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$35,0,(IF($A16=VARIABLES!$B$35,0,O15)+L16)*C16*VARIABLES!$B$39)</f>
-        <v>23070.564512074114</v>
+        <v>40571.326142771955</v>
       </c>
       <c r="O16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$35,0,(IF($A16=VARIABLES!$B$35,0,O15)+L16)*(1+C16)-N16)</f>
-        <v>7128804.4342309022</v>
+        <v>8479407.1638393383</v>
       </c>
       <c r="P16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$42,0,IF($A16=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -5979,11 +5980,11 @@
       </c>
       <c r="R16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$42,0,(IF($A16=VARIABLES!$B$42,0,S15)+P16)*C16*VARIABLES!$B$46)</f>
-        <v>239.92142472912397</v>
+        <v>395.06079518181087</v>
       </c>
       <c r="S16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$42,0,(IF($A16=VARIABLES!$B$42,0,S15)+P16)*(1+C16)-R16)</f>
-        <v>297262.64523938467</v>
+        <v>331456.00715753931</v>
       </c>
       <c r="T16" s="16">
         <f>IF($A16&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A16-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -5999,11 +6000,11 @@
       </c>
       <c r="W16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$50,0,(IF($A16&lt;VARIABLES!$B$50+1,0,X15)+U16)*C16*VARIABLES!$B$56)</f>
-        <v>3352.4268159909757</v>
+        <v>5384.7568313303937</v>
       </c>
       <c r="X16" s="7">
         <f>IF($A16&lt;VARIABLES!$B$50,0,(IF($A16&lt;VARIABLES!$B$50+1,0,X15)+U16)*(1+C16)-W16)</f>
-        <v>1035899.8861412117</v>
+        <v>1125414.1777480524</v>
       </c>
       <c r="Y16" s="7">
         <f t="shared" si="0"/>
@@ -6015,15 +6016,15 @@
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="2"/>
-        <v>31566.000432549772</v>
+        <v>54501.038433087284</v>
       </c>
       <c r="AB16" s="17">
         <f t="shared" si="3"/>
-        <v>34303.500432549772</v>
+        <v>57238.538433087284</v>
       </c>
       <c r="AC16" s="18">
         <f t="shared" si="4"/>
-        <v>12777080.935197763</v>
+        <v>14825570.959925728</v>
       </c>
       <c r="AD16" s="7">
         <f>IF($A16=1,VARIABLES!$B$12,0)</f>
@@ -6055,11 +6056,11 @@
       </c>
       <c r="AK16" s="21">
         <f t="shared" si="6"/>
-        <v>-27276.582900783564</v>
+        <v>-4341.54490024605</v>
       </c>
       <c r="AL16" s="21">
         <f t="shared" si="7"/>
-        <v>-428115.94451652374</v>
+        <v>-251671.50050731594</v>
       </c>
       <c r="AM16" s="22">
         <f t="shared" si="8"/>
@@ -6076,7 +6077,7 @@
       </c>
       <c r="C17" s="24">
         <f>IF($A17&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$21,0,IF($A17=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6088,11 +6089,11 @@
       </c>
       <c r="F17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$21,0,(IF($A17=VARIABLES!$B$21,0,G16)+D17)*C17*VARIABLES!$B$25)</f>
-        <v>3275.3352930423712</v>
+        <v>5553.6213503733052</v>
       </c>
       <c r="G17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$21,0,(IF($A17=VARIABLES!$B$21,0,G16)+D17)*(1+C17)-F17)</f>
-        <v>4058140.428079498</v>
+        <v>4659488.3129632035</v>
       </c>
       <c r="H17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$28,0,IF($A17=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6104,11 +6105,11 @@
       </c>
       <c r="J17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$28,0,(IF($A17=VARIABLES!$B$28,0,K16)+H17)*C17*VARIABLES!$B$32)</f>
-        <v>2082.3720597847314</v>
+        <v>3431.9826544107609</v>
       </c>
       <c r="K17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$28,0,(IF($A17=VARIABLES!$B$28,0,K16)+H17)*(1+C17)-J17)</f>
-        <v>643452.96647348208</v>
+        <v>717284.37477184914</v>
       </c>
       <c r="L17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$35,0,IF($A17=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6120,11 +6121,11 @@
       </c>
       <c r="N17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$35,0,(IF($A17=VARIABLES!$B$35,0,O16)+L17)*C17*VARIABLES!$B$39)</f>
-        <v>23762.681447436342</v>
+        <v>42397.035819196695</v>
       </c>
       <c r="O17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$35,0,(IF($A17=VARIABLES!$B$35,0,O16)+L17)*(1+C17)-N17)</f>
-        <v>7342668.5672578299</v>
+        <v>8860980.4862121083</v>
       </c>
       <c r="P17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$42,0,IF($A17=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6136,11 +6137,11 @@
       </c>
       <c r="R17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$42,0,(IF($A17=VARIABLES!$B$42,0,S16)+P17)*C17*VARIABLES!$B$46)</f>
-        <v>264.3855376994872</v>
+        <v>439.32000894692413</v>
       </c>
       <c r="S17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$42,0,(IF($A17=VARIABLES!$B$42,0,S16)+P17)*(1+C17)-R17)</f>
-        <v>327573.68120966468</v>
+        <v>368589.48750646936</v>
       </c>
       <c r="T17" s="26">
         <f>IF($A17&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A17-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -6156,11 +6157,11 @@
       </c>
       <c r="W17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$50,0,(IF($A17&lt;VARIABLES!$B$50+1,0,X16)+U17)*C17*VARIABLES!$B$56)</f>
-        <v>3819.6662871373724</v>
+        <v>6177.0708887402616</v>
       </c>
       <c r="X17" s="25">
         <f>IF($A17&lt;VARIABLES!$B$50,0,(IF($A17&lt;VARIABLES!$B$50+1,0,X16)+U17)*(1+C17)-W17)</f>
-        <v>1180276.8827254481</v>
+        <v>1291007.8157467148</v>
       </c>
       <c r="Y17" s="25">
         <f t="shared" si="0"/>
@@ -6172,15 +6173,15 @@
       </c>
       <c r="AA17" s="25">
         <f t="shared" si="2"/>
-        <v>33204.440625100302</v>
+        <v>57999.03072166795</v>
       </c>
       <c r="AB17" s="17">
         <f t="shared" si="3"/>
-        <v>35979.440625100302</v>
+        <v>60774.03072166795</v>
       </c>
       <c r="AC17" s="18">
         <f t="shared" si="4"/>
-        <v>13552112.525745921</v>
+        <v>15897350.477200346</v>
       </c>
       <c r="AD17" s="25">
         <f>IF($A17=1,VARIABLES!$B$12,0)</f>
@@ -6212,11 +6213,11 @@
       </c>
       <c r="AK17" s="27">
         <f t="shared" si="6"/>
-        <v>-25600.642708233034</v>
+        <v>-806.05261166538367</v>
       </c>
       <c r="AL17" s="27">
         <f t="shared" si="7"/>
-        <v>-453716.58722475677</v>
+        <v>-252477.55311898133</v>
       </c>
       <c r="AM17" s="22">
         <f t="shared" si="8"/>
@@ -6233,7 +6234,7 @@
       </c>
       <c r="C18" s="15">
         <f>IF($A18&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$21,0,IF($A18=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6245,11 +6246,11 @@
       </c>
       <c r="F18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$21,0,(IF($A18=VARIABLES!$B$21,0,G17)+D18)*C18*VARIABLES!$B$25)</f>
-        <v>3548.4503567329152</v>
+        <v>6074.3603912040044</v>
       </c>
       <c r="G18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$21,0,(IF($A18=VARIABLES!$B$21,0,G17)+D18)*(1+C18)-F18)</f>
-        <v>4396529.9919920824</v>
+        <v>5096388.3682201598</v>
       </c>
       <c r="H18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$28,0,IF($A18=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6261,11 +6262,11 @@
       </c>
       <c r="J18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$28,0,(IF($A18=VARIABLES!$B$28,0,K17)+H18)*C18*VARIABLES!$B$32)</f>
-        <v>2278.1765549116071</v>
+        <v>3786.4218738592458</v>
       </c>
       <c r="K18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$28,0,(IF($A18=VARIABLES!$B$28,0,K17)+H18)*(1+C18)-J18)</f>
-        <v>703956.55546768662</v>
+        <v>791362.17163658235</v>
       </c>
       <c r="L18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$35,0,IF($A18=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6277,11 +6278,11 @@
       </c>
       <c r="N18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$35,0,(IF($A18=VARIABLES!$B$35,0,O17)+L18)*C18*VARIABLES!$B$39)</f>
-        <v>24475.561890859433</v>
+        <v>44304.902431060538</v>
       </c>
       <c r="O18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$35,0,(IF($A18=VARIABLES!$B$35,0,O17)+L18)*(1+C18)-N18)</f>
-        <v>7562948.6242755661</v>
+        <v>9259724.6080916543</v>
       </c>
       <c r="P18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$42,0,IF($A18=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6293,11 +6294,11 @@
       </c>
       <c r="R18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$42,0,(IF($A18=VARIABLES!$B$42,0,S17)+P18)*C18*VARIABLES!$B$46)</f>
-        <v>289.64473434138722</v>
+        <v>485.73685938308665</v>
       </c>
       <c r="S18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$42,0,(IF($A18=VARIABLES!$B$42,0,S17)+P18)*(1+C18)-R18)</f>
-        <v>358869.82584897883</v>
+        <v>407533.22502240981</v>
       </c>
       <c r="T18" s="16">
         <f>IF($A18&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A18-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -6313,11 +6314,11 @@
       </c>
       <c r="W18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$50,0,(IF($A18&lt;VARIABLES!$B$50+1,0,X17)+U18)*C18*VARIABLES!$B$56)</f>
-        <v>4317.5896090848273</v>
+        <v>7030.0390787335746</v>
       </c>
       <c r="X18" s="7">
         <f>IF($A18&lt;VARIABLES!$B$50,0,(IF($A18&lt;VARIABLES!$B$50+1,0,X17)+U18)*(1+C18)-W18)</f>
-        <v>1334135.1892072116</v>
+        <v>1469278.167455317</v>
       </c>
       <c r="Y18" s="7">
         <f t="shared" si="0"/>
@@ -6329,15 +6330,15 @@
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="2"/>
-        <v>34909.423145930166</v>
+        <v>61681.460634240444</v>
       </c>
       <c r="AB18" s="17">
         <f t="shared" si="3"/>
-        <v>37721.923145930166</v>
+        <v>64493.960634240444</v>
       </c>
       <c r="AC18" s="18">
         <f t="shared" si="4"/>
-        <v>14356440.186791524</v>
+        <v>17024286.54042612</v>
       </c>
       <c r="AD18" s="7">
         <f>IF($A18=1,VARIABLES!$B$12,0)</f>
@@ -6369,11 +6370,11 @@
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="6"/>
-        <v>-23858.160187403169</v>
+        <v>2913.8773009071101</v>
       </c>
       <c r="AL18" s="21">
         <f t="shared" si="7"/>
-        <v>-477574.74741215992</v>
+        <v>-249563.67581807423</v>
       </c>
       <c r="AM18" s="22">
         <f t="shared" si="8"/>
@@ -6390,7 +6391,7 @@
       </c>
       <c r="C19" s="24">
         <f>IF($A19&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$21,0,IF($A19=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6402,11 +6403,11 @@
       </c>
       <c r="F19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$21,0,(IF($A19=VARIABLES!$B$21,0,G18)+D19)*C19*VARIABLES!$B$25)</f>
-        <v>3830.441659993402</v>
+        <v>6620.4854602751993</v>
       </c>
       <c r="G19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$21,0,(IF($A19=VARIABLES!$B$21,0,G18)+D19)*(1+C19)-F19)</f>
-        <v>4745917.2167318258</v>
+        <v>5554587.301170893</v>
       </c>
       <c r="H19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$28,0,IF($A19=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6418,11 +6419,11 @@
       </c>
       <c r="J19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$28,0,(IF($A19=VARIABLES!$B$28,0,K18)+H19)*C19*VARIABLES!$B$32)</f>
-        <v>2479.8551848922889</v>
+        <v>4156.8108581829119</v>
       </c>
       <c r="K19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$28,0,(IF($A19=VARIABLES!$B$28,0,K18)+H19)*(1+C19)-J19)</f>
-        <v>766275.25213171728</v>
+        <v>868773.46936022851</v>
       </c>
       <c r="L19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$35,0,IF($A19=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6434,11 +6435,11 @@
       </c>
       <c r="N19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$35,0,(IF($A19=VARIABLES!$B$35,0,O18)+L19)*C19*VARIABLES!$B$39)</f>
-        <v>25209.828747585223</v>
+        <v>46298.623040458275</v>
       </c>
       <c r="O19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$35,0,(IF($A19=VARIABLES!$B$35,0,O18)+L19)*(1+C19)-N19)</f>
-        <v>7789837.0830038339</v>
+        <v>9676412.2154557798</v>
       </c>
       <c r="P19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$42,0,IF($A19=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6450,11 +6451,11 @@
       </c>
       <c r="R19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$42,0,(IF($A19=VARIABLES!$B$42,0,S18)+P19)*C19*VARIABLES!$B$46)</f>
-        <v>315.72485487414906</v>
+        <v>534.41653127801226</v>
       </c>
       <c r="S19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$42,0,(IF($A19=VARIABLES!$B$42,0,S18)+P19)*(1+C19)-R19)</f>
-        <v>391183.09518907068</v>
+        <v>448375.46974225232</v>
       </c>
       <c r="T19" s="26">
         <f>IF($A19&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A19-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -6470,11 +6471,11 @@
       </c>
       <c r="W19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$50,0,(IF($A19&lt;VARIABLES!$B$50+1,0,X18)+U19)*C19*VARIABLES!$B$56)</f>
-        <v>4847.1172973573721</v>
+        <v>7946.3908372765845</v>
       </c>
       <c r="X19" s="25">
         <f>IF($A19&lt;VARIABLES!$B$50,0,(IF($A19&lt;VARIABLES!$B$50+1,0,X18)+U19)*(1+C19)-W19)</f>
-        <v>1497759.2448834281</v>
+        <v>1660795.6849908063</v>
       </c>
       <c r="Y19" s="25">
         <f t="shared" si="0"/>
@@ -6486,15 +6487,15 @@
       </c>
       <c r="AA19" s="25">
         <f t="shared" si="2"/>
-        <v>36682.967744702437</v>
+        <v>65556.726727470974</v>
       </c>
       <c r="AB19" s="17">
         <f t="shared" si="3"/>
-        <v>39532.967744702437</v>
+        <v>68406.726727470974</v>
       </c>
       <c r="AC19" s="18">
         <f t="shared" si="4"/>
-        <v>15190971.891939875</v>
+        <v>18208944.140719958</v>
       </c>
       <c r="AD19" s="25">
         <f>IF($A19=1,VARIABLES!$B$12,0)</f>
@@ -6526,11 +6527,11 @@
       </c>
       <c r="AK19" s="27">
         <f t="shared" si="6"/>
-        <v>-22047.115588630899</v>
+        <v>6826.6433941376399</v>
       </c>
       <c r="AL19" s="27">
         <f t="shared" si="7"/>
-        <v>-499621.86300079082</v>
+        <v>-242737.03242393659</v>
       </c>
       <c r="AM19" s="22">
         <f t="shared" si="8"/>
@@ -6547,7 +6548,7 @@
       </c>
       <c r="C20" s="15">
         <f>IF($A20&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$21,0,IF($A20=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6559,11 +6560,11 @@
       </c>
       <c r="F20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$21,0,(IF($A20=VARIABLES!$B$21,0,G19)+D20)*C20*VARIABLES!$B$25)</f>
-        <v>4121.5976806098552</v>
+        <v>7193.2341264636161</v>
       </c>
       <c r="G20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$21,0,(IF($A20=VARIABLES!$B$21,0,G19)+D20)*(1+C20)-F20)</f>
-        <v>5106659.5262756106</v>
+        <v>6035123.4321029745</v>
       </c>
       <c r="H20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$28,0,IF($A20=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6575,11 +6576,11 @@
       </c>
       <c r="J20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$28,0,(IF($A20=VARIABLES!$B$28,0,K19)+H20)*C20*VARIABLES!$B$32)</f>
-        <v>2687.5841737723913</v>
+        <v>4543.867346801143</v>
       </c>
       <c r="K20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$28,0,(IF($A20=VARIABLES!$B$28,0,K19)+H20)*(1+C20)-J20)</f>
-        <v>830463.50969566894</v>
+        <v>949668.27548143885</v>
       </c>
       <c r="L20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$35,0,IF($A20=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6591,11 +6592,11 @@
       </c>
       <c r="N20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$35,0,(IF($A20=VARIABLES!$B$35,0,O19)+L20)*C20*VARIABLES!$B$39)</f>
-        <v>25966.123610012783</v>
+        <v>48382.061077278893</v>
       </c>
       <c r="O20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$35,0,(IF($A20=VARIABLES!$B$35,0,O19)+L20)*(1+C20)-N20)</f>
-        <v>8023532.1954939496</v>
+        <v>10111850.76515129</v>
       </c>
       <c r="P20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$42,0,IF($A20=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6607,11 +6608,11 @@
       </c>
       <c r="R20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$42,0,(IF($A20=VARIABLES!$B$42,0,S19)+P20)*C20*VARIABLES!$B$46)</f>
-        <v>342.6525793242256</v>
+        <v>585.46933717781531</v>
       </c>
       <c r="S20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$42,0,(IF($A20=VARIABLES!$B$42,0,S19)+P20)*(1+C20)-R20)</f>
-        <v>424546.54578271555</v>
+        <v>491208.77389218716</v>
       </c>
       <c r="T20" s="16">
         <f>IF($A20&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A20-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -6627,11 +6628,11 @@
       </c>
       <c r="W20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$50,0,(IF($A20&lt;VARIABLES!$B$50+1,0,X19)+U20)*C20*VARIABLES!$B$56)</f>
-        <v>5409.1974829447608</v>
+        <v>8928.9784249540298</v>
       </c>
       <c r="X20" s="7">
         <f>IF($A20&lt;VARIABLES!$B$50,0,(IF($A20&lt;VARIABLES!$B$50+1,0,X19)+U20)*(1+C20)-W20)</f>
-        <v>1671442.0222299311</v>
+        <v>1866156.4908153927</v>
       </c>
       <c r="Y20" s="7">
         <f t="shared" si="0"/>
@@ -6643,15 +6644,15 @@
       </c>
       <c r="AA20" s="7">
         <f t="shared" si="2"/>
-        <v>38527.155526664021</v>
+        <v>69633.61031267549</v>
       </c>
       <c r="AB20" s="17">
         <f t="shared" si="3"/>
-        <v>41414.655526664021</v>
+        <v>72521.11031267549</v>
       </c>
       <c r="AC20" s="18">
         <f t="shared" si="4"/>
-        <v>16056643.799477873</v>
+        <v>19454007.737443283</v>
       </c>
       <c r="AD20" s="7">
         <f>IF($A20=1,VARIABLES!$B$12,0)</f>
@@ -6683,11 +6684,11 @@
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="6"/>
-        <v>-20165.427806669315</v>
+        <v>10941.026979342156</v>
       </c>
       <c r="AL20" s="21">
         <f t="shared" si="7"/>
-        <v>-519787.29080746014</v>
+        <v>-231796.00544459443</v>
       </c>
       <c r="AM20" s="22">
         <f t="shared" si="8"/>
@@ -6704,7 +6705,7 @@
       </c>
       <c r="C21" s="24">
         <f>IF($A21&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$21,0,IF($A21=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6716,11 +6717,11 @@
       </c>
       <c r="F21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$21,0,(IF($A21=VARIABLES!$B$21,0,G20)+D21)*C21*VARIABLES!$B$25)</f>
-        <v>4422.2162718963427</v>
+        <v>7793.9042901287175</v>
       </c>
       <c r="G21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$21,0,(IF($A21=VARIABLES!$B$21,0,G20)+D21)*(1+C21)-F21)</f>
-        <v>5479125.9608795689</v>
+        <v>6539085.6994179953</v>
       </c>
       <c r="H21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$28,0,IF($A21=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6732,11 +6733,11 @@
       </c>
       <c r="J21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$28,0,(IF($A21=VARIABLES!$B$28,0,K20)+H21)*C21*VARIABLES!$B$32)</f>
-        <v>2901.5450323188966</v>
+        <v>4948.3413774071942</v>
       </c>
       <c r="K21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$28,0,(IF($A21=VARIABLES!$B$28,0,K20)+H21)*(1+C21)-J21)</f>
-        <v>896577.41498653905</v>
+        <v>1034203.3478781036</v>
       </c>
       <c r="L21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$35,0,IF($A21=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6748,11 +6749,11 @@
       </c>
       <c r="N21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$35,0,(IF($A21=VARIABLES!$B$35,0,O20)+L21)*C21*VARIABLES!$B$39)</f>
-        <v>26745.107318313167</v>
+        <v>50559.253825756452</v>
       </c>
       <c r="O21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$35,0,(IF($A21=VARIABLES!$B$35,0,O20)+L21)*(1+C21)-N21)</f>
-        <v>8264238.1613587691</v>
+        <v>10566884.0495831</v>
       </c>
       <c r="P21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$42,0,IF($A21=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6764,11 +6765,11 @@
       </c>
       <c r="R21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$42,0,(IF($A21=VARIABLES!$B$42,0,S20)+P21)*C21*VARIABLES!$B$46)</f>
-        <v>370.45545481892964</v>
+        <v>639.01096736523391</v>
       </c>
       <c r="S21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$42,0,(IF($A21=VARIABLES!$B$42,0,S20)+P21)*(1+C21)-R21)</f>
-        <v>458994.30852065387</v>
+        <v>536130.20161943126</v>
       </c>
       <c r="T21" s="26">
         <f>IF($A21&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A21-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -6784,11 +6785,11 @@
       </c>
       <c r="W21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$50,0,(IF($A21&lt;VARIABLES!$B$50+1,0,X20)+U21)*C21*VARIABLES!$B$56)</f>
-        <v>6004.8067407664375</v>
+        <v>9980.7824540769634</v>
       </c>
       <c r="X21" s="25">
         <f>IF($A21&lt;VARIABLES!$B$50,0,(IF($A21&lt;VARIABLES!$B$50+1,0,X20)+U21)*(1+C21)-W21)</f>
-        <v>1855485.2828968293</v>
+        <v>2085983.5329020855</v>
       </c>
       <c r="Y21" s="25">
         <f t="shared" si="0"/>
@@ -6800,15 +6801,15 @@
       </c>
       <c r="AA21" s="25">
         <f t="shared" si="2"/>
-        <v>40444.130818113765</v>
+        <v>73921.292914734557</v>
       </c>
       <c r="AB21" s="17">
         <f t="shared" si="3"/>
-        <v>43369.130818113765</v>
+        <v>76846.292914734557</v>
       </c>
       <c r="AC21" s="18">
         <f t="shared" si="4"/>
-        <v>16954421.128642362</v>
+        <v>20762286.831400715</v>
       </c>
       <c r="AD21" s="25">
         <f>IF($A21=1,VARIABLES!$B$12,0)</f>
@@ -6840,11 +6841,11 @@
       </c>
       <c r="AK21" s="27">
         <f t="shared" si="6"/>
-        <v>-18210.952515219571</v>
+        <v>15266.209581401223</v>
       </c>
       <c r="AL21" s="27">
         <f t="shared" si="7"/>
-        <v>-537998.24332267977</v>
+        <v>-216529.7958631932</v>
       </c>
       <c r="AM21" s="22">
         <f t="shared" si="8"/>
@@ -6861,7 +6862,7 @@
       </c>
       <c r="C22" s="15">
         <f>IF($A22&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$21,0,IF($A22=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -6873,11 +6874,11 @@
       </c>
       <c r="F22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$21,0,(IF($A22=VARIABLES!$B$21,0,G21)+D22)*C22*VARIABLES!$B$25)</f>
-        <v>4732.6049673996413</v>
+        <v>8423.8571242724938</v>
       </c>
       <c r="G22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$21,0,(IF($A22=VARIABLES!$B$21,0,G21)+D22)*(1+C22)-F22)</f>
-        <v>5863697.554608156</v>
+        <v>7067616.1272646226</v>
       </c>
       <c r="H22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$28,0,IF($A22=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -6889,11 +6890,11 @@
       </c>
       <c r="J22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$28,0,(IF($A22=VARIABLES!$B$28,0,K21)+H22)*C22*VARIABLES!$B$32)</f>
-        <v>3121.924716621797</v>
+        <v>5371.0167393905176</v>
       </c>
       <c r="K22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$28,0,(IF($A22=VARIABLES!$B$28,0,K21)+H22)*(1+C22)-J22)</f>
-        <v>964674.73743613542</v>
+        <v>1122542.4985326184</v>
       </c>
       <c r="L22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$35,0,IF($A22=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -6905,11 +6906,11 @@
       </c>
       <c r="N22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$35,0,(IF($A22=VARIABLES!$B$35,0,O21)+L22)*C22*VARIABLES!$B$39)</f>
-        <v>27547.460537862564</v>
+        <v>52834.420247915492</v>
       </c>
       <c r="O22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$35,0,(IF($A22=VARIABLES!$B$35,0,O21)+L22)*(1+C22)-N22)</f>
-        <v>8512165.3061995339</v>
+        <v>11042393.831814339</v>
       </c>
       <c r="P22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$42,0,IF($A22=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -6921,11 +6922,11 @@
       </c>
       <c r="R22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$42,0,(IF($A22=VARIABLES!$B$42,0,S21)+P22)*C22*VARIABLES!$B$46)</f>
-        <v>399.16192376721159</v>
+        <v>695.16275202428915</v>
       </c>
       <c r="S22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$42,0,(IF($A22=VARIABLES!$B$42,0,S21)+P22)*(1+C22)-R22)</f>
-        <v>494561.6235475752</v>
+        <v>583241.54894837865</v>
       </c>
       <c r="T22" s="16">
         <f>IF($A22&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A22-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -6941,11 +6942,11 @@
       </c>
       <c r="W22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$50,0,(IF($A22&lt;VARIABLES!$B$50+1,0,X21)+U22)*C22*VARIABLES!$B$56)</f>
-        <v>6634.9509429894315</v>
+        <v>11104.917664510425</v>
       </c>
       <c r="X22" s="7">
         <f>IF($A22&lt;VARIABLES!$B$50,0,(IF($A22&lt;VARIABLES!$B$50+1,0,X21)+U22)*(1+C22)-W22)</f>
-        <v>2050199.8413837345</v>
+        <v>2320927.7918826793</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" si="0"/>
@@ -6957,15 +6958,15 @@
       </c>
       <c r="AA22" s="7">
         <f t="shared" si="2"/>
-        <v>42436.103088640644</v>
+        <v>78429.374528113229</v>
       </c>
       <c r="AB22" s="17">
         <f t="shared" si="3"/>
-        <v>45398.603088640644</v>
+        <v>81391.874528113229</v>
       </c>
       <c r="AC22" s="18">
         <f t="shared" si="4"/>
-        <v>17885299.063175134</v>
+        <v>22136721.798442636</v>
       </c>
       <c r="AD22" s="7">
         <f>IF($A22=1,VARIABLES!$B$12,0)</f>
@@ -6997,11 +6998,11 @@
       </c>
       <c r="AK22" s="21">
         <f t="shared" si="6"/>
-        <v>-16181.48024469269</v>
+        <v>19811.791194779893</v>
       </c>
       <c r="AL22" s="21">
         <f t="shared" si="7"/>
-        <v>-554179.72356737242</v>
+        <v>-196718.00466841331</v>
       </c>
       <c r="AM22" s="22">
         <f t="shared" si="8"/>
@@ -7018,7 +7019,7 @@
       </c>
       <c r="C23" s="24">
         <f>IF($A23&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$21,0,IF($A23=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7030,11 +7031,11 @@
       </c>
       <c r="F23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$21,0,(IF($A23=VARIABLES!$B$21,0,G22)+D23)*C23*VARIABLES!$B$25)</f>
-        <v>5053.0812955067968</v>
+        <v>9084.5201590807774</v>
       </c>
       <c r="G23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$21,0,(IF($A23=VARIABLES!$B$21,0,G22)+D23)*(1+C23)-F23)</f>
-        <v>6260767.7251329217</v>
+        <v>7621912.4134687735</v>
       </c>
       <c r="H23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$28,0,IF($A23=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7046,11 +7047,11 @@
       </c>
       <c r="J23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$28,0,(IF($A23=VARIABLES!$B$28,0,K22)+H23)*C23*VARIABLES!$B$32)</f>
-        <v>3348.915791453785</v>
+        <v>5812.7124926630922</v>
       </c>
       <c r="K23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$28,0,(IF($A23=VARIABLES!$B$28,0,K22)+H23)*(1+C23)-J23)</f>
-        <v>1034814.9795592196</v>
+        <v>1214856.9109665861</v>
       </c>
       <c r="L23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$35,0,IF($A23=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7062,11 +7063,11 @@
       </c>
       <c r="N23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$35,0,(IF($A23=VARIABLES!$B$35,0,O22)+L23)*C23*VARIABLES!$B$39)</f>
-        <v>28373.884353998445</v>
+        <v>55211.969159071698</v>
       </c>
       <c r="O23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$35,0,(IF($A23=VARIABLES!$B$35,0,O22)+L23)*(1+C23)-N23)</f>
-        <v>8767530.2653855197</v>
+        <v>11539301.554245984</v>
       </c>
       <c r="P23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$42,0,IF($A23=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7078,11 +7079,11 @@
       </c>
       <c r="R23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$42,0,(IF($A23=VARIABLES!$B$42,0,S22)+P23)*C23*VARIABLES!$B$46)</f>
-        <v>428.80135295631266</v>
+        <v>754.05193618547332</v>
       </c>
       <c r="S23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$42,0,(IF($A23=VARIABLES!$B$42,0,S22)+P23)*(1+C23)-R23)</f>
-        <v>531284.87631287146</v>
+        <v>632649.57445961214</v>
       </c>
       <c r="T23" s="26">
         <f>IF($A23&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A23-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -7098,11 +7099,11 @@
       </c>
       <c r="W23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$50,0,(IF($A23&lt;VARIABLES!$B$50+1,0,X22)+U23)*C23*VARIABLES!$B$56)</f>
-        <v>7300.6661379457837</v>
+        <v>12304.638959413396</v>
       </c>
       <c r="X23" s="25">
         <f>IF($A23&lt;VARIABLES!$B$50,0,(IF($A23&lt;VARIABLES!$B$50+1,0,X22)+U23)*(1+C23)-W23)</f>
-        <v>2255905.8366252468</v>
+        <v>2571669.5425173999</v>
       </c>
       <c r="Y23" s="25">
         <f t="shared" si="0"/>
@@ -7114,15 +7115,15 @@
       </c>
       <c r="AA23" s="25">
         <f t="shared" si="2"/>
-        <v>44505.348931861125</v>
+        <v>83167.892706414437</v>
       </c>
       <c r="AB23" s="17">
         <f t="shared" si="3"/>
-        <v>47505.348931861125</v>
+        <v>86167.892706414437</v>
       </c>
       <c r="AC23" s="18">
         <f t="shared" si="4"/>
-        <v>18850303.683015779</v>
+        <v>23580389.995658357</v>
       </c>
       <c r="AD23" s="25">
         <f>IF($A23=1,VARIABLES!$B$12,0)</f>
@@ -7154,11 +7155,11 @@
       </c>
       <c r="AK23" s="27">
         <f t="shared" si="6"/>
-        <v>-14074.734401472209</v>
+        <v>24587.809373081102</v>
       </c>
       <c r="AL23" s="27">
         <f t="shared" si="7"/>
-        <v>-568254.45796884468</v>
+        <v>-172130.1952953322</v>
       </c>
       <c r="AM23" s="22">
         <f t="shared" si="8"/>
@@ -7175,7 +7176,7 @@
       </c>
       <c r="C24" s="15">
         <f>IF($A24&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$21,0,IF($A24=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7187,11 +7188,11 @@
       </c>
       <c r="F24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$21,0,(IF($A24=VARIABLES!$B$21,0,G23)+D24)*C24*VARIABLES!$B$25)</f>
-        <v>5383.9731042774347</v>
+        <v>9777.390516835967</v>
       </c>
       <c r="G24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$21,0,(IF($A24=VARIABLES!$B$21,0,G23)+D24)*(1+C24)-F24)</f>
-        <v>6670742.6761997426</v>
+        <v>8203230.6436253767</v>
       </c>
       <c r="H24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$28,0,IF($A24=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7203,11 +7204,11 @@
       </c>
       <c r="J24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$28,0,(IF($A24=VARIABLES!$B$28,0,K23)+H24)*C24*VARIABLES!$B$32)</f>
-        <v>3582.7165985307315</v>
+        <v>6274.2845548329306</v>
       </c>
       <c r="K24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$28,0,(IF($A24=VARIABLES!$B$28,0,K23)+H24)*(1+C24)-J24)</f>
-        <v>1107059.4289459961</v>
+        <v>1311325.4719600827</v>
       </c>
       <c r="L24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$35,0,IF($A24=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7219,11 +7220,11 @@
       </c>
       <c r="N24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$35,0,(IF($A24=VARIABLES!$B$35,0,O23)+L24)*C24*VARIABLES!$B$39)</f>
-        <v>29225.100884618401</v>
+        <v>57696.507771229924</v>
       </c>
       <c r="O24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$35,0,(IF($A24=VARIABLES!$B$35,0,O23)+L24)*(1+C24)-N24)</f>
-        <v>9030556.1733470857</v>
+        <v>12058570.124187054</v>
       </c>
       <c r="P24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$42,0,IF($A24=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7235,11 +7236,11 @@
       </c>
       <c r="R24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$42,0,(IF($A24=VARIABLES!$B$42,0,S23)+P24)*C24*VARIABLES!$B$46)</f>
-        <v>459.40406359405955</v>
+        <v>815.81196807451511</v>
       </c>
       <c r="S24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$42,0,(IF($A24=VARIABLES!$B$42,0,S23)+P24)*(1+C24)-R24)</f>
-        <v>569201.63479303988</v>
+        <v>684466.2412145182</v>
       </c>
       <c r="T24" s="16">
         <f>IF($A24&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A24-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -7255,11 +7256,11 @@
       </c>
       <c r="W24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$50,0,(IF($A24&lt;VARIABLES!$B$50+1,0,X23)+U24)*C24*VARIABLES!$B$56)</f>
-        <v>8003.0194554174886</v>
+        <v>13583.347712586998</v>
       </c>
       <c r="X24" s="7">
         <f>IF($A24&lt;VARIABLES!$B$50,0,(IF($A24&lt;VARIABLES!$B$50+1,0,X23)+U24)*(1+C24)-W24)</f>
-        <v>2472933.0117240045</v>
+        <v>2838919.6719306828</v>
       </c>
       <c r="Y24" s="7">
         <f t="shared" si="0"/>
@@ -7271,15 +7272,15 @@
       </c>
       <c r="AA24" s="7">
         <f t="shared" si="2"/>
-        <v>46654.214106438121</v>
+        <v>88147.342523560335</v>
       </c>
       <c r="AB24" s="17">
         <f t="shared" si="3"/>
-        <v>49691.714106438121</v>
+        <v>91184.842523560335</v>
       </c>
       <c r="AC24" s="18">
         <f t="shared" si="4"/>
-        <v>19850492.925009869</v>
+        <v>25096512.152917713</v>
       </c>
       <c r="AD24" s="7">
         <f>IF($A24=1,VARIABLES!$B$12,0)</f>
@@ -7311,11 +7312,11 @@
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="6"/>
-        <v>-11888.369226895213</v>
+        <v>29604.759190227</v>
       </c>
       <c r="AL24" s="21">
         <f t="shared" si="7"/>
-        <v>-580142.82719573984</v>
+        <v>-142525.43610510521</v>
       </c>
       <c r="AM24" s="22">
         <f t="shared" si="8"/>
@@ -7332,7 +7333,7 @@
       </c>
       <c r="C25" s="24">
         <f>IF($A25&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$21,0,IF($A25=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7344,11 +7345,11 @@
       </c>
       <c r="F25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$21,0,(IF($A25=VARIABLES!$B$21,0,G24)+D25)*C25*VARIABLES!$B$25)</f>
-        <v>5725.6188968331189</v>
+        <v>10504.038304531721</v>
       </c>
       <c r="G25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$21,0,(IF($A25=VARIABLES!$B$21,0,G24)+D25)*(1+C25)-F25)</f>
-        <v>7094041.8131762352</v>
+        <v>8812888.1375021134</v>
       </c>
       <c r="H25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$28,0,IF($A25=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7360,11 +7361,11 @@
       </c>
       <c r="J25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$28,0,(IF($A25=VARIABLES!$B$28,0,K24)+H25)*C25*VARIABLES!$B$32)</f>
-        <v>3823.5314298199869</v>
+        <v>6756.6273598004136</v>
       </c>
       <c r="K25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$28,0,(IF($A25=VARIABLES!$B$28,0,K24)+H25)*(1+C25)-J25)</f>
-        <v>1181471.2118143761</v>
+        <v>1412135.1181982863</v>
       </c>
       <c r="L25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$35,0,IF($A25=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7376,11 +7377,11 @@
       </c>
       <c r="N25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$35,0,(IF($A25=VARIABLES!$B$35,0,O24)+L25)*C25*VARIABLES!$B$39)</f>
-        <v>30101.853911156955</v>
+        <v>60292.850620935264</v>
       </c>
       <c r="O25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$35,0,(IF($A25=VARIABLES!$B$35,0,O24)+L25)*(1+C25)-N25)</f>
-        <v>9301472.8585474994</v>
+        <v>12601205.779775472</v>
       </c>
       <c r="P25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$42,0,IF($A25=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7392,11 +7393,11 @@
       </c>
       <c r="R25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$42,0,(IF($A25=VARIABLES!$B$42,0,S24)+P25)*C25*VARIABLES!$B$46)</f>
-        <v>491.00136232753323</v>
+        <v>880.58280151814768</v>
       </c>
       <c r="S25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$42,0,(IF($A25=VARIABLES!$B$42,0,S24)+P25)*(1+C25)-R25)</f>
-        <v>608350.68792381382</v>
+        <v>738808.97047372605</v>
       </c>
       <c r="T25" s="26">
         <f>IF($A25&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A25-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -7412,11 +7413,11 @@
       </c>
       <c r="W25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$50,0,(IF($A25&lt;VARIABLES!$B$50+1,0,X24)+U25)*C25*VARIABLES!$B$56)</f>
-        <v>8743.1100390800148</v>
+        <v>14944.598359653413</v>
       </c>
       <c r="X25" s="25">
         <f>IF($A25&lt;VARIABLES!$B$50,0,(IF($A25&lt;VARIABLES!$B$50+1,0,X24)+U25)*(1+C25)-W25)</f>
-        <v>2701621.0020757248</v>
+        <v>3123421.0571675641</v>
       </c>
       <c r="Y25" s="25">
         <f t="shared" si="0"/>
@@ -7428,15 +7429,15 @@
       </c>
       <c r="AA25" s="25">
         <f t="shared" si="2"/>
-        <v>48885.115639217605</v>
+        <v>93378.69744643895</v>
       </c>
       <c r="AB25" s="17">
         <f t="shared" si="3"/>
-        <v>51960.115639217605</v>
+        <v>96453.69744643895</v>
       </c>
       <c r="AC25" s="18">
         <f t="shared" si="4"/>
-        <v>20886957.573537651</v>
+        <v>26688459.063117161</v>
       </c>
       <c r="AD25" s="25">
         <f>IF($A25=1,VARIABLES!$B$12,0)</f>
@@ -7468,11 +7469,11 @@
       </c>
       <c r="AK25" s="27">
         <f t="shared" si="6"/>
-        <v>-9619.9676941157286</v>
+        <v>34873.614113105614</v>
       </c>
       <c r="AL25" s="27">
         <f t="shared" si="7"/>
-        <v>-589762.79488985555</v>
+        <v>-107651.8219919996</v>
       </c>
       <c r="AM25" s="22">
         <f t="shared" si="8"/>
@@ -7489,7 +7490,7 @@
       </c>
       <c r="C26" s="15">
         <f>IF($A26&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$21,0,IF($A26=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7501,11 +7502,11 @@
       </c>
       <c r="F26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$21,0,(IF($A26=VARIABLES!$B$21,0,G25)+D26)*C26*VARIABLES!$B$25)</f>
-        <v>6078.3681776468629</v>
+        <v>11266.110171877641</v>
       </c>
       <c r="G26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$21,0,(IF($A26=VARIABLES!$B$21,0,G25)+D26)*(1+C26)-F26)</f>
-        <v>7531098.1721044639</v>
+        <v>9452266.4342053421</v>
       </c>
       <c r="H26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$28,0,IF($A26=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7517,11 +7518,11 @@
       </c>
       <c r="J26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$28,0,(IF($A26=VARIABLES!$B$28,0,K25)+H26)*C26*VARIABLES!$B$32)</f>
-        <v>4071.5707060479203</v>
+        <v>7260.6755909914318</v>
       </c>
       <c r="K26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$28,0,(IF($A26=VARIABLES!$B$28,0,K25)+H26)*(1+C26)-J26)</f>
-        <v>1258115.3481688076</v>
+        <v>1517481.1985172092</v>
       </c>
       <c r="L26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$35,0,IF($A26=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7533,11 +7534,11 @@
       </c>
       <c r="N26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$35,0,(IF($A26=VARIABLES!$B$35,0,O25)+L26)*C26*VARIABLES!$B$39)</f>
-        <v>31004.909528491666</v>
+        <v>63006.028898877361</v>
       </c>
       <c r="O26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$35,0,(IF($A26=VARIABLES!$B$35,0,O25)+L26)*(1+C26)-N26)</f>
-        <v>9580517.0443039257</v>
+        <v>13168260.039865369</v>
       </c>
       <c r="P26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$42,0,IF($A26=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7549,11 +7550,11 @@
       </c>
       <c r="R26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$42,0,(IF($A26=VARIABLES!$B$42,0,S25)+P26)*C26*VARIABLES!$B$46)</f>
-        <v>523.62557326984495</v>
+        <v>948.5112130921575</v>
       </c>
       <c r="S26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$42,0,(IF($A26=VARIABLES!$B$42,0,S25)+P26)*(1+C26)-R26)</f>
-        <v>648772.08528133784</v>
+        <v>795800.9077843203</v>
       </c>
       <c r="T26" s="16">
         <f>IF($A26&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A26-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -7569,11 +7570,11 @@
       </c>
       <c r="W26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$50,0,(IF($A26&lt;VARIABLES!$B$50+1,0,X25)+U26)*C26*VARIABLES!$B$56)</f>
-        <v>9522.0700069190825</v>
+        <v>16392.105285837821</v>
       </c>
       <c r="X26" s="7">
         <f>IF($A26&lt;VARIABLES!$B$50,0,(IF($A26&lt;VARIABLES!$B$50+1,0,X25)+U26)*(1+C26)-W26)</f>
-        <v>2942319.6321379966</v>
+        <v>3425950.0047401045</v>
       </c>
       <c r="Y26" s="7">
         <f t="shared" si="0"/>
@@ -7585,15 +7586,15 @@
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="2"/>
-        <v>51200.543992375373</v>
+        <v>98873.431160676424</v>
       </c>
       <c r="AB26" s="17">
         <f t="shared" si="3"/>
-        <v>54313.043992375373</v>
+        <v>101985.93116067642</v>
       </c>
       <c r="AC26" s="18">
         <f t="shared" si="4"/>
-        <v>21960822.281996533</v>
+        <v>28359758.585112344</v>
       </c>
       <c r="AD26" s="7">
         <f>IF($A26=1,VARIABLES!$B$12,0)</f>
@@ -7625,11 +7626,11 @@
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="6"/>
-        <v>-7267.039340957961</v>
+        <v>40405.847827343088</v>
       </c>
       <c r="AL26" s="21">
         <f t="shared" si="7"/>
-        <v>-597029.83423081355</v>
+        <v>-67245.974164656509</v>
       </c>
       <c r="AM26" s="22">
         <f t="shared" si="8"/>
@@ -7646,7 +7647,7 @@
       </c>
       <c r="C27" s="24">
         <f>IF($A27&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$21,0,IF($A27=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7658,11 +7659,11 @@
       </c>
       <c r="F27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$21,0,(IF($A27=VARIABLES!$B$21,0,G26)+D27)*C27*VARIABLES!$B$25)</f>
-        <v>6442.5818100870529</v>
+        <v>12065.333042756676</v>
       </c>
       <c r="G27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$21,0,(IF($A27=VARIABLES!$B$21,0,G26)+D27)*(1+C27)-F27)</f>
-        <v>7982358.8626978602</v>
+        <v>10122814.422872853</v>
       </c>
       <c r="H27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$28,0,IF($A27=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7674,11 +7675,11 @@
       </c>
       <c r="J27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$28,0,(IF($A27=VARIABLES!$B$28,0,K26)+H27)*C27*VARIABLES!$B$32)</f>
-        <v>4327.0511605626916</v>
+        <v>7787.4059925860456</v>
       </c>
       <c r="K27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$28,0,(IF($A27=VARIABLES!$B$28,0,K26)+H27)*(1+C27)-J27)</f>
-        <v>1337058.8086138719</v>
+        <v>1627567.8524504837</v>
       </c>
       <c r="L27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$35,0,IF($A27=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7690,11 +7691,11 @@
       </c>
       <c r="N27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$35,0,(IF($A27=VARIABLES!$B$35,0,O26)+L27)*C27*VARIABLES!$B$39)</f>
-        <v>31935.056814346419</v>
+        <v>65841.300199326841</v>
       </c>
       <c r="O27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$35,0,(IF($A27=VARIABLES!$B$35,0,O26)+L27)*(1+C27)-N27)</f>
-        <v>9867932.5556330439</v>
+        <v>13760831.741659312</v>
       </c>
       <c r="P27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$42,0,IF($A27=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7706,11 +7707,11 @@
       </c>
       <c r="R27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$42,0,(IF($A27=VARIABLES!$B$42,0,S26)+P27)*C27*VARIABLES!$B$46)</f>
-        <v>557.31007106778156</v>
+        <v>1019.7511347304004</v>
       </c>
       <c r="S27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$42,0,(IF($A27=VARIABLES!$B$42,0,S26)+P27)*(1+C27)-R27)</f>
-        <v>690507.17805298138</v>
+        <v>855571.20203880593</v>
       </c>
       <c r="T27" s="26">
         <f>IF($A27&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A27-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -7726,11 +7727,11 @@
       </c>
       <c r="W27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$50,0,(IF($A27&lt;VARIABLES!$B$50+1,0,X26)+U27)*C27*VARIABLES!$B$56)</f>
-        <v>10341.06544045999</v>
+        <v>17929.750023700522</v>
       </c>
       <c r="X27" s="25">
         <f>IF($A27&lt;VARIABLES!$B$50,0,(IF($A27&lt;VARIABLES!$B$50+1,0,X26)+U27)*(1+C27)-W27)</f>
-        <v>3195389.2211021367</v>
+        <v>3747317.7549534095</v>
       </c>
       <c r="Y27" s="25">
         <f t="shared" si="0"/>
@@ -7742,15 +7743,15 @@
       </c>
       <c r="AA27" s="25">
         <f t="shared" si="2"/>
-        <v>53603.065296523942</v>
+        <v>104643.54039310047</v>
       </c>
       <c r="AB27" s="17">
         <f t="shared" si="3"/>
-        <v>56753.065296523942</v>
+        <v>107793.54039310047</v>
       </c>
       <c r="AC27" s="18">
         <f t="shared" si="4"/>
-        <v>23073246.626099892</v>
+        <v>30114102.973974865</v>
       </c>
       <c r="AD27" s="25">
         <f>IF($A27=1,VARIABLES!$B$12,0)</f>
@@ -7762,7 +7763,7 @@
       </c>
       <c r="AF27" s="25">
         <f>IF(MOD($A27,12)=0,AC27*VARIABLES!$B$16,0)</f>
-        <v>57683.116565249729</v>
+        <v>75285.257434937157</v>
       </c>
       <c r="AG27" s="25">
         <f>VARIABLES!$B$17</f>
@@ -7774,7 +7775,7 @@
       </c>
       <c r="AI27" s="19">
         <f t="shared" si="5"/>
-        <v>111683.11656524973</v>
+        <v>129285.25743493716</v>
       </c>
       <c r="AJ27" s="20">
         <f>IF($A27&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -7782,11 +7783,11 @@
       </c>
       <c r="AK27" s="27">
         <f t="shared" si="6"/>
-        <v>-65510.134602059123</v>
+        <v>-32071.800375170023</v>
       </c>
       <c r="AL27" s="27">
         <f t="shared" si="7"/>
-        <v>-662539.96883287269</v>
+        <v>-99317.774539826525</v>
       </c>
       <c r="AM27" s="22">
         <f t="shared" si="8"/>
@@ -7803,7 +7804,7 @@
       </c>
       <c r="C28" s="15">
         <f>IF($A28&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$21,0,IF($A28=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7815,11 +7816,11 @@
       </c>
       <c r="F28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$21,0,(IF($A28=VARIABLES!$B$21,0,G27)+D28)*C28*VARIABLES!$B$25)</f>
-        <v>6818.6323855815499</v>
+        <v>12903.518028591065</v>
       </c>
       <c r="G28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$21,0,(IF($A28=VARIABLES!$B$21,0,G27)+D28)*(1+C28)-F28)</f>
-        <v>8448285.5257355422</v>
+        <v>10826051.625987904</v>
       </c>
       <c r="H28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$28,0,IF($A28=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7831,11 +7832,11 @@
       </c>
       <c r="J28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$28,0,(IF($A28=VARIABLES!$B$28,0,K27)+H28)*C28*VARIABLES!$B$32)</f>
-        <v>4590.1960287129068</v>
+        <v>8337.839262252417</v>
       </c>
       <c r="K28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$28,0,(IF($A28=VARIABLES!$B$28,0,K27)+H28)*(1+C28)-J28)</f>
-        <v>1418370.5728722883</v>
+        <v>1742608.4058107554</v>
       </c>
       <c r="L28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$35,0,IF($A28=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -7847,11 +7848,11 @@
       </c>
       <c r="N28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$35,0,(IF($A28=VARIABLES!$B$35,0,O27)+L28)*C28*VARIABLES!$B$39)</f>
-        <v>32893.108518776811</v>
+        <v>68804.158708296556</v>
       </c>
       <c r="O28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$35,0,(IF($A28=VARIABLES!$B$35,0,O27)+L28)*(1+C28)-N28)</f>
-        <v>10163970.532302035</v>
+        <v>14380069.17003398</v>
       </c>
       <c r="P28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$42,0,IF($A28=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -7863,11 +7864,11 @@
       </c>
       <c r="R28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$42,0,(IF($A28=VARIABLES!$B$42,0,S27)+P28)*C28*VARIABLES!$B$46)</f>
-        <v>592.08931504415114</v>
+        <v>1094.4640025485073</v>
       </c>
       <c r="S28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$42,0,(IF($A28=VARIABLES!$B$42,0,S27)+P28)*(1+C28)-R28)</f>
-        <v>733598.66133970337</v>
+        <v>918255.29813819774</v>
       </c>
       <c r="T28" s="16">
         <f>IF($A28&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A28-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -7883,11 +7884,11 @@
       </c>
       <c r="W28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$50,0,(IF($A28&lt;VARIABLES!$B$50+1,0,X27)+U28)*C28*VARIABLES!$B$56)</f>
-        <v>11201.297403673789</v>
+        <v>19561.588774767046</v>
       </c>
       <c r="X28" s="7">
         <f>IF($A28&lt;VARIABLES!$B$50,0,(IF($A28&lt;VARIABLES!$B$50+1,0,X27)+U28)*(1+C28)-W28)</f>
-        <v>3461200.8977352013</v>
+        <v>4088372.0539263128</v>
       </c>
       <c r="Y28" s="7">
         <f t="shared" si="0"/>
@@ -7899,15 +7900,15 @@
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="2"/>
-        <v>56095.3236517892</v>
+        <v>110701.56877645561</v>
       </c>
       <c r="AB28" s="17">
         <f t="shared" si="3"/>
-        <v>59282.8236517892</v>
+        <v>113889.06877645561</v>
       </c>
       <c r="AC28" s="18">
         <f t="shared" si="4"/>
-        <v>24225426.189984772</v>
+        <v>31955356.553897146</v>
       </c>
       <c r="AD28" s="7">
         <f>IF($A28=1,VARIABLES!$B$12,0)</f>
@@ -7939,11 +7940,11 @@
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="6"/>
-        <v>-2297.2596815441339</v>
+        <v>52308.98544312227</v>
       </c>
       <c r="AL28" s="21">
         <f t="shared" si="7"/>
-        <v>-664837.22851441684</v>
+        <v>-47008.789096704255</v>
       </c>
       <c r="AM28" s="22">
         <f t="shared" si="8"/>
@@ -7960,7 +7961,7 @@
       </c>
       <c r="C29" s="24">
         <f>IF($A29&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$21,0,IF($A29=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -7972,11 +7973,11 @@
       </c>
       <c r="F29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$21,0,(IF($A29=VARIABLES!$B$21,0,G28)+D29)*C29*VARIABLES!$B$25)</f>
-        <v>7206.9046047796191</v>
+        <v>13782.564532484881</v>
       </c>
       <c r="G29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$21,0,(IF($A29=VARIABLES!$B$21,0,G28)+D29)*(1+C29)-F29)</f>
-        <v>8929354.8053219486</v>
+        <v>11563571.642754816</v>
       </c>
       <c r="H29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$28,0,IF($A29=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -7988,11 +7989,11 @@
       </c>
       <c r="J29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$28,0,(IF($A29=VARIABLES!$B$28,0,K28)+H29)*C29*VARIABLES!$B$32)</f>
-        <v>4861.2352429076273</v>
+        <v>8913.0420290537768</v>
       </c>
       <c r="K29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$28,0,(IF($A29=VARIABLES!$B$28,0,K28)+H29)*(1+C29)-J29)</f>
-        <v>1502121.690058457</v>
+        <v>1862825.7840722397</v>
       </c>
       <c r="L29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$35,0,IF($A29=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8004,11 +8005,11 @@
       </c>
       <c r="N29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$35,0,(IF($A29=VARIABLES!$B$35,0,O28)+L29)*C29*VARIABLES!$B$39)</f>
-        <v>33879.90177434012</v>
+        <v>71900.345850169891</v>
       </c>
       <c r="O29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$35,0,(IF($A29=VARIABLES!$B$35,0,O28)+L29)*(1+C29)-N29)</f>
-        <v>10468889.648271099</v>
+        <v>15027172.282685511</v>
       </c>
       <c r="P29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$42,0,IF($A29=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8020,11 +8021,11 @@
       </c>
       <c r="R29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$42,0,(IF($A29=VARIABLES!$B$42,0,S28)+P29)*C29*VARIABLES!$B$46)</f>
-        <v>627.99888444975284</v>
+        <v>1172.8191226727472</v>
       </c>
       <c r="S29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$42,0,(IF($A29=VARIABLES!$B$42,0,S28)+P29)*(1+C29)-R29)</f>
-        <v>778090.6178332438</v>
+        <v>983995.24392243486</v>
       </c>
       <c r="T29" s="26">
         <f>IF($A29&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A29-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -8040,11 +8041,11 @@
       </c>
       <c r="W29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$50,0,(IF($A29&lt;VARIABLES!$B$50+1,0,X28)+U29)*C29*VARIABLES!$B$56)</f>
-        <v>12104.002992450673</v>
+        <v>21291.860269631565</v>
       </c>
       <c r="X29" s="25">
         <f>IF($A29&lt;VARIABLES!$B$50,0,(IF($A29&lt;VARIABLES!$B$50+1,0,X28)+U29)*(1+C29)-W29)</f>
-        <v>3740136.9246672578</v>
+        <v>4449998.7963529984</v>
       </c>
       <c r="Y29" s="25">
         <f t="shared" si="0"/>
@@ -8056,15 +8057,15 @@
       </c>
       <c r="AA29" s="25">
         <f t="shared" si="2"/>
-        <v>58680.043498927786</v>
+        <v>117060.63180401287</v>
       </c>
       <c r="AB29" s="17">
         <f t="shared" si="3"/>
-        <v>61905.043498927786</v>
+        <v>120285.63180401287</v>
       </c>
       <c r="AC29" s="18">
         <f t="shared" si="4"/>
-        <v>25418593.686152007</v>
+        <v>33887563.749788001</v>
       </c>
       <c r="AD29" s="25">
         <f>IF($A29=1,VARIABLES!$B$12,0)</f>
@@ -8096,11 +8097,11 @@
       </c>
       <c r="AK29" s="27">
         <f t="shared" si="6"/>
-        <v>324.96016559445161</v>
+        <v>58705.548470679532</v>
       </c>
       <c r="AL29" s="27">
         <f t="shared" si="7"/>
-        <v>-664512.26834882237</v>
+        <v>11696.759373975277</v>
       </c>
       <c r="AM29" s="22">
         <f t="shared" si="8"/>
@@ -8117,7 +8118,7 @@
       </c>
       <c r="C30" s="15">
         <f>IF($A30&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$21,0,IF($A30=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8129,11 +8130,11 @@
       </c>
       <c r="F30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$21,0,(IF($A30=VARIABLES!$B$21,0,G29)+D30)*C30*VARIABLES!$B$25)</f>
-        <v>7607.7956711016232</v>
+        <v>14704.464553443519</v>
       </c>
       <c r="G30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$21,0,(IF($A30=VARIABLES!$B$21,0,G29)+D30)*(1+C30)-F30)</f>
-        <v>9426058.8364949133</v>
+        <v>12337045.760339113</v>
       </c>
       <c r="H30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$28,0,IF($A30=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8145,11 +8146,11 @@
       </c>
       <c r="J30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$28,0,(IF($A30=VARIABLES!$B$28,0,K29)+H30)*C30*VARIABLES!$B$32)</f>
-        <v>5140.4056335281903</v>
+        <v>9514.1289203611977</v>
       </c>
       <c r="K30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$28,0,(IF($A30=VARIABLES!$B$28,0,K29)+H30)*(1+C30)-J30)</f>
-        <v>1588385.3407602108</v>
+        <v>1988452.9443554906</v>
       </c>
       <c r="L30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$35,0,IF($A30=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8161,11 +8162,11 @@
       </c>
       <c r="N30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$35,0,(IF($A30=VARIABLES!$B$35,0,O29)+L30)*C30*VARIABLES!$B$39)</f>
-        <v>34896.298827570332</v>
+        <v>75135.861413427556</v>
       </c>
       <c r="O30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$35,0,(IF($A30=VARIABLES!$B$35,0,O29)+L30)*(1+C30)-N30)</f>
-        <v>10782956.337719234</v>
+        <v>15703395.03540636</v>
       </c>
       <c r="P30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$42,0,IF($A30=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8177,11 +8178,11 @@
       </c>
       <c r="R30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$42,0,(IF($A30=VARIABLES!$B$42,0,S29)+P30)*C30*VARIABLES!$B$46)</f>
-        <v>665.07551486103648</v>
+        <v>1254.9940549030434</v>
       </c>
       <c r="S30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$42,0,(IF($A30=VARIABLES!$B$42,0,S29)+P30)*(1+C30)-R30)</f>
-        <v>824028.56291282433</v>
+        <v>1052940.0120636537</v>
       </c>
       <c r="T30" s="16">
         <f>IF($A30&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A30-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -8197,11 +8198,11 @@
       </c>
       <c r="W30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$50,0,(IF($A30&lt;VARIABLES!$B$50+1,0,X29)+U30)*C30*VARIABLES!$B$56)</f>
-        <v>13050.456415557526</v>
+        <v>23124.99398176499</v>
       </c>
       <c r="X30" s="7">
         <f>IF($A30&lt;VARIABLES!$B$50,0,(IF($A30&lt;VARIABLES!$B$50+1,0,X29)+U30)*(1+C30)-W30)</f>
-        <v>4032591.0324072763</v>
+        <v>4833123.7421888839</v>
       </c>
       <c r="Y30" s="7">
         <f t="shared" si="0"/>
@@ -8213,15 +8214,15 @@
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="2"/>
-        <v>61360.032062618709</v>
+        <v>123734.44292390031</v>
       </c>
       <c r="AB30" s="17">
         <f t="shared" si="3"/>
-        <v>64622.532062618709</v>
+        <v>126996.94292390031</v>
       </c>
       <c r="AC30" s="18">
         <f t="shared" si="4"/>
-        <v>26654020.110294458</v>
+        <v>35914957.494353503</v>
       </c>
       <c r="AD30" s="7">
         <f>IF($A30=1,VARIABLES!$B$12,0)</f>
@@ -8253,11 +8254,11 @@
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="6"/>
-        <v>3042.4487292853755</v>
+        <v>65416.859590566972</v>
       </c>
       <c r="AL30" s="21">
         <f t="shared" si="7"/>
-        <v>-661469.81961953698</v>
+        <v>77113.618964542256</v>
       </c>
       <c r="AM30" s="22">
         <f t="shared" si="8"/>
@@ -8274,7 +8275,7 @@
       </c>
       <c r="C31" s="24">
         <f>IF($A31&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$21,0,IF($A31=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8286,11 +8287,11 @@
       </c>
       <c r="F31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$21,0,(IF($A31=VARIABLES!$B$21,0,G30)+D31)*C31*VARIABLES!$B$25)</f>
-        <v>8021.7156970790938</v>
+        <v>15671.307200423891</v>
       </c>
       <c r="G31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$21,0,(IF($A31=VARIABLES!$B$21,0,G30)+D31)*(1+C31)-F31)</f>
-        <v>9938905.7486809976</v>
+        <v>13148226.741155645</v>
       </c>
       <c r="H31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$28,0,IF($A31=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8302,11 +8303,11 @@
       </c>
       <c r="J31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$28,0,(IF($A31=VARIABLES!$B$28,0,K30)+H31)*C31*VARIABLES!$B$32)</f>
-        <v>5427.9511358673699</v>
+        <v>10142.264721777452</v>
       </c>
       <c r="K31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$28,0,(IF($A31=VARIABLES!$B$28,0,K30)+H31)*(1+C31)-J31)</f>
-        <v>1677236.9009830174</v>
+        <v>2119733.3268514881</v>
       </c>
       <c r="L31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$35,0,IF($A31=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8318,11 +8319,11 @@
       </c>
       <c r="N31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$35,0,(IF($A31=VARIABLES!$B$35,0,O30)+L31)*C31*VARIABLES!$B$39)</f>
-        <v>35943.187792397446</v>
+        <v>78516.975177031796</v>
       </c>
       <c r="O31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$35,0,(IF($A31=VARIABLES!$B$35,0,O30)+L31)*(1+C31)-N31)</f>
-        <v>11106445.02785081</v>
+        <v>16410047.811999649</v>
       </c>
       <c r="P31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$42,0,IF($A31=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8334,11 +8335,11 @@
       </c>
       <c r="R31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$42,0,(IF($A31=VARIABLES!$B$42,0,S30)+P31)*C31*VARIABLES!$B$46)</f>
-        <v>703.35713576068702</v>
+        <v>1341.1750150795669</v>
       </c>
       <c r="S31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$42,0,(IF($A31=VARIABLES!$B$42,0,S30)+P31)*(1+C31)-R31)</f>
-        <v>871459.49120749114</v>
+        <v>1125245.8376517568</v>
       </c>
       <c r="T31" s="26">
         <f>IF($A31&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A31-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -8354,11 +8355,11 @@
       </c>
       <c r="W31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$50,0,(IF($A31&lt;VARIABLES!$B$50+1,0,X30)+U31)*C31*VARIABLES!$B$56)</f>
-        <v>14041.970108024256</v>
+        <v>25065.618710944418</v>
       </c>
       <c r="X31" s="25">
         <f>IF($A31&lt;VARIABLES!$B$50,0,(IF($A31&lt;VARIABLES!$B$50+1,0,X30)+U31)*(1+C31)-W31)</f>
-        <v>4338968.7633794956</v>
+        <v>5238714.3105873838</v>
       </c>
       <c r="Y31" s="25">
         <f t="shared" si="0"/>
@@ -8370,15 +8371,15 @@
       </c>
       <c r="AA31" s="25">
         <f t="shared" si="2"/>
-        <v>64138.18186912885</v>
+        <v>130737.34082525712</v>
       </c>
       <c r="AB31" s="17">
         <f t="shared" si="3"/>
-        <v>67438.18186912885</v>
+        <v>134037.34082525712</v>
       </c>
       <c r="AC31" s="18">
         <f t="shared" si="4"/>
-        <v>27933015.932101812</v>
+        <v>38041968.028245926</v>
       </c>
       <c r="AD31" s="25">
         <f>IF($A31=1,VARIABLES!$B$12,0)</f>
@@ -8410,11 +8411,11 @@
       </c>
       <c r="AK31" s="27">
         <f t="shared" si="6"/>
-        <v>5858.098535795516</v>
+        <v>72457.257491923796</v>
       </c>
       <c r="AL31" s="27">
         <f t="shared" si="7"/>
-        <v>-655611.72108374152</v>
+        <v>149570.87645646604</v>
       </c>
       <c r="AM31" s="22">
         <f t="shared" si="8"/>
@@ -8431,7 +8432,7 @@
       </c>
       <c r="C32" s="15">
         <f>IF($A32&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$21,0,IF($A32=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8443,11 +8444,11 @@
       </c>
       <c r="F32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$21,0,(IF($A32=VARIABLES!$B$21,0,G31)+D32)*C32*VARIABLES!$B$25)</f>
-        <v>8449.0881239008322</v>
+        <v>16685.283426444556</v>
       </c>
       <c r="G32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$21,0,(IF($A32=VARIABLES!$B$21,0,G31)+D32)*(1+C32)-F32)</f>
-        <v>10468420.185513131</v>
+        <v>13998952.794786982</v>
       </c>
       <c r="H32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$28,0,IF($A32=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8459,11 +8460,11 @@
       </c>
       <c r="J32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$28,0,(IF($A32=VARIABLES!$B$28,0,K31)+H32)*C32*VARIABLES!$B$32)</f>
-        <v>5724.1230032767253</v>
+        <v>10798.666634257439</v>
       </c>
       <c r="K32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$28,0,(IF($A32=VARIABLES!$B$28,0,K31)+H32)*(1+C32)-J32)</f>
-        <v>1768754.008012508</v>
+        <v>2256921.3265598053</v>
       </c>
       <c r="L32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$35,0,IF($A32=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8475,11 +8476,11 @@
       </c>
       <c r="N32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$35,0,(IF($A32=VARIABLES!$B$35,0,O31)+L32)*C32*VARIABLES!$B$39)</f>
-        <v>37021.483426169369</v>
+        <v>82050.239059998246</v>
       </c>
       <c r="O32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$35,0,(IF($A32=VARIABLES!$B$35,0,O31)+L32)*(1+C32)-N32)</f>
-        <v>11439638.378686337</v>
+        <v>17148499.963539634</v>
       </c>
       <c r="P32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$42,0,IF($A32=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8491,11 +8492,11 @@
       </c>
       <c r="R32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$42,0,(IF($A32=VARIABLES!$B$42,0,S31)+P32)*C32*VARIABLES!$B$46)</f>
-        <v>742.88290933957603</v>
+        <v>1431.5572970646961</v>
       </c>
       <c r="S32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$42,0,(IF($A32=VARIABLES!$B$42,0,S31)+P32)*(1+C32)-R32)</f>
-        <v>920431.92467173468</v>
+        <v>1201076.57223728</v>
       </c>
       <c r="T32" s="16">
         <f>IF($A32&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A32-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -8511,11 +8512,11 @@
       </c>
       <c r="W32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$50,0,(IF($A32&lt;VARIABLES!$B$50+1,0,X31)+U32)*C32*VARIABLES!$B$56)</f>
-        <v>15079.895877931653</v>
+        <v>27118.571552936919</v>
       </c>
       <c r="X32" s="7">
         <f>IF($A32&lt;VARIABLES!$B$50,0,(IF($A32&lt;VARIABLES!$B$50+1,0,X31)+U32)*(1+C32)-W32)</f>
-        <v>4659687.8262808817</v>
+        <v>5667781.4545638161</v>
       </c>
       <c r="Y32" s="7">
         <f t="shared" si="0"/>
@@ -8527,15 +8528,15 @@
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="2"/>
-        <v>67017.473340618162</v>
+        <v>138084.31797070184</v>
       </c>
       <c r="AB32" s="17">
         <f t="shared" si="3"/>
-        <v>70354.973340618162</v>
+        <v>141421.81797070184</v>
       </c>
       <c r="AC32" s="18">
         <f t="shared" si="4"/>
-        <v>29256932.32316459</v>
+        <v>40273232.111687519</v>
       </c>
       <c r="AD32" s="7">
         <f>IF($A32=1,VARIABLES!$B$12,0)</f>
@@ -8567,11 +8568,11 @@
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="6"/>
-        <v>8774.8900072848282</v>
+        <v>79841.734637368514</v>
       </c>
       <c r="AL32" s="21">
         <f t="shared" si="7"/>
-        <v>-646836.8310764567</v>
+        <v>229412.61109383457</v>
       </c>
       <c r="AM32" s="22">
         <f t="shared" si="8"/>
@@ -8588,7 +8589,7 @@
       </c>
       <c r="C33" s="24">
         <f>IF($A33&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$21,0,IF($A33=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8600,11 +8601,11 @@
       </c>
       <c r="F33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$21,0,(IF($A33=VARIABLES!$B$21,0,G32)+D33)*C33*VARIABLES!$B$25)</f>
-        <v>8890.3501545942763</v>
+        <v>17748.690993483728</v>
       </c>
       <c r="G33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$21,0,(IF($A33=VARIABLES!$B$21,0,G32)+D33)*(1+C33)-F33)</f>
-        <v>11015143.841542309</v>
+        <v>14891151.743532848</v>
       </c>
       <c r="H33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$28,0,IF($A33=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8616,11 +8617,11 @@
       </c>
       <c r="J33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$28,0,(IF($A33=VARIABLES!$B$28,0,K32)+H33)*C33*VARIABLES!$B$32)</f>
-        <v>6029.1800267083599</v>
+        <v>11484.606632799027</v>
       </c>
       <c r="K33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$28,0,(IF($A33=VARIABLES!$B$28,0,K32)+H33)*(1+C33)-J33)</f>
-        <v>1863016.6282528834</v>
+        <v>2400282.7862549969</v>
       </c>
       <c r="L33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$35,0,IF($A33=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8632,11 +8633,11 @@
       </c>
       <c r="N33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$35,0,(IF($A33=VARIABLES!$B$35,0,O32)+L33)*C33*VARIABLES!$B$39)</f>
-        <v>38132.127928954455</v>
+        <v>85742.499817698161</v>
       </c>
       <c r="O33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$35,0,(IF($A33=VARIABLES!$B$35,0,O32)+L33)*(1+C33)-N33)</f>
-        <v>11782827.530046929</v>
+        <v>17920182.461898915</v>
       </c>
       <c r="P33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$42,0,IF($A33=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8648,11 +8649,11 @@
       </c>
       <c r="R33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$42,0,(IF($A33=VARIABLES!$B$42,0,S32)+P33)*C33*VARIABLES!$B$46)</f>
-        <v>783.69327055977897</v>
+        <v>1526.3457152966</v>
       </c>
       <c r="S33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$42,0,(IF($A33=VARIABLES!$B$42,0,S32)+P33)*(1+C33)-R33)</f>
-        <v>970995.96222356614</v>
+        <v>1280604.0551338473</v>
       </c>
       <c r="T33" s="26">
         <f>IF($A33&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A33-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -8668,11 +8669,11 @@
       </c>
       <c r="W33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$50,0,(IF($A33&lt;VARIABLES!$B$50+1,0,X32)+U33)*C33*VARIABLES!$B$56)</f>
-        <v>16165.626087602939</v>
+        <v>29288.90727281908</v>
       </c>
       <c r="X33" s="25">
         <f>IF($A33&lt;VARIABLES!$B$50,0,(IF($A33&lt;VARIABLES!$B$50+1,0,X32)+U33)*(1+C33)-W33)</f>
-        <v>4995178.4610693082</v>
+        <v>6121381.6200191882</v>
       </c>
       <c r="Y33" s="25">
         <f t="shared" si="0"/>
@@ -8684,15 +8685,15 @@
       </c>
       <c r="AA33" s="25">
         <f t="shared" si="2"/>
-        <v>70000.977468419806</v>
+        <v>145791.05043209658</v>
       </c>
       <c r="AB33" s="17">
         <f t="shared" si="3"/>
-        <v>73375.977468419806</v>
+        <v>149166.05043209658</v>
       </c>
       <c r="AC33" s="18">
         <f t="shared" si="4"/>
-        <v>30627162.423134997</v>
+        <v>42613602.666839801</v>
       </c>
       <c r="AD33" s="25">
         <f>IF($A33=1,VARIABLES!$B$12,0)</f>
@@ -8724,11 +8725,11 @@
       </c>
       <c r="AK33" s="27">
         <f t="shared" si="6"/>
-        <v>11795.894135086472</v>
+        <v>87585.967098763256</v>
       </c>
       <c r="AL33" s="27">
         <f t="shared" si="7"/>
-        <v>-635040.93694137025</v>
+        <v>316998.57819259784</v>
       </c>
       <c r="AM33" s="22">
         <f t="shared" si="8"/>
@@ -8745,7 +8746,7 @@
       </c>
       <c r="C34" s="15">
         <f>IF($A34&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$21,0,IF($A34=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8757,11 +8758,11 @@
       </c>
       <c r="F34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$21,0,(IF($A34=VARIABLES!$B$21,0,G33)+D34)*C34*VARIABLES!$B$25)</f>
-        <v>9345.9532012852578</v>
+        <v>18863.939679416057</v>
       </c>
       <c r="G34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$21,0,(IF($A34=VARIABLES!$B$21,0,G33)+D34)*(1+C34)-F34)</f>
-        <v>11579636.016392436</v>
+        <v>15826845.391030075</v>
       </c>
       <c r="H34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$28,0,IF($A34=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8773,11 +8774,11 @@
       </c>
       <c r="J34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$28,0,(IF($A34=VARIABLES!$B$28,0,K33)+H34)*C34*VARIABLES!$B$32)</f>
-        <v>6343.388760842945</v>
+        <v>12201.413931274983</v>
       </c>
       <c r="K34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$28,0,(IF($A34=VARIABLES!$B$28,0,K33)+H34)*(1+C34)-J34)</f>
-        <v>1960107.1271004702</v>
+        <v>2550095.5116364718</v>
       </c>
       <c r="L34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$35,0,IF($A34=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8789,11 +8790,11 @@
       </c>
       <c r="N34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$35,0,(IF($A34=VARIABLES!$B$35,0,O33)+L34)*C34*VARIABLES!$B$39)</f>
-        <v>39276.091766823098</v>
+        <v>89600.912309494568</v>
       </c>
       <c r="O34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$35,0,(IF($A34=VARIABLES!$B$35,0,O33)+L34)*(1+C34)-N34)</f>
-        <v>12136312.355948338</v>
+        <v>18726590.672684368</v>
       </c>
       <c r="P34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$42,0,IF($A34=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8805,11 +8806,11 @@
       </c>
       <c r="R34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$42,0,(IF($A34=VARIABLES!$B$42,0,S33)+P34)*C34*VARIABLES!$B$46)</f>
-        <v>825.82996851963844</v>
+        <v>1625.755068917309</v>
       </c>
       <c r="S34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$42,0,(IF($A34=VARIABLES!$B$42,0,S33)+P34)*(1+C34)-R34)</f>
-        <v>1023203.3309958321</v>
+        <v>1364008.5028216224</v>
       </c>
       <c r="T34" s="16">
         <f>IF($A34&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A34-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -8825,11 +8826,11 @@
       </c>
       <c r="W34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$50,0,(IF($A34&lt;VARIABLES!$B$50+1,0,X33)+U34)*C34*VARIABLES!$B$56)</f>
-        <v>17300.594870231027</v>
+        <v>31581.908100095941</v>
       </c>
       <c r="X34" s="7">
         <f>IF($A34&lt;VARIABLES!$B$50,0,(IF($A34&lt;VARIABLES!$B$50+1,0,X33)+U34)*(1+C34)-W34)</f>
-        <v>5345883.8149013883</v>
+        <v>6600618.7929200521</v>
       </c>
       <c r="Y34" s="7">
         <f t="shared" si="0"/>
@@ -8841,15 +8842,15 @@
       </c>
       <c r="AA34" s="7">
         <f t="shared" si="2"/>
-        <v>73091.858567701973</v>
+        <v>153873.92908919885</v>
       </c>
       <c r="AB34" s="17">
         <f t="shared" si="3"/>
-        <v>76504.358567701973</v>
+        <v>157286.42908919885</v>
       </c>
       <c r="AC34" s="18">
         <f t="shared" si="4"/>
-        <v>32045142.645338465</v>
+        <v>45068158.871092588</v>
       </c>
       <c r="AD34" s="7">
         <f>IF($A34=1,VARIABLES!$B$12,0)</f>
@@ -8881,11 +8882,11 @@
       </c>
       <c r="AK34" s="21">
         <f t="shared" si="6"/>
-        <v>14924.275234368639</v>
+        <v>95706.345755865521</v>
       </c>
       <c r="AL34" s="21">
         <f t="shared" si="7"/>
-        <v>-620116.66170700162</v>
+        <v>412704.92394846334</v>
       </c>
       <c r="AM34" s="22">
         <f t="shared" si="8"/>
@@ -8902,7 +8903,7 @@
       </c>
       <c r="C35" s="24">
         <f>IF($A35&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$21,0,IF($A35=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -8914,11 +8915,11 @@
       </c>
       <c r="F35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$21,0,(IF($A35=VARIABLES!$B$21,0,G34)+D35)*C35*VARIABLES!$B$25)</f>
-        <v>9816.3633469936958</v>
+        <v>20033.556738787593</v>
       </c>
       <c r="G35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$21,0,(IF($A35=VARIABLES!$B$21,0,G34)+D35)*(1+C35)-F35)</f>
-        <v>12162474.186925191</v>
+        <v>16808154.103842795</v>
       </c>
       <c r="H35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$28,0,IF($A35=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -8930,11 +8931,11 @@
       </c>
       <c r="J35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$28,0,(IF($A35=VARIABLES!$B$28,0,K34)+H35)*C35*VARIABLES!$B$32)</f>
-        <v>6667.023757001567</v>
+        <v>12950.477558182358</v>
       </c>
       <c r="K35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$28,0,(IF($A35=VARIABLES!$B$28,0,K34)+H35)*(1+C35)-J35)</f>
-        <v>2060110.3409134846</v>
+        <v>2706649.809660113</v>
       </c>
       <c r="L35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$35,0,IF($A35=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -8946,11 +8947,11 @@
       </c>
       <c r="N35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$35,0,(IF($A35=VARIABLES!$B$35,0,O34)+L35)*C35*VARIABLES!$B$39)</f>
-        <v>40454.374519827797</v>
+        <v>93632.953363421839</v>
       </c>
       <c r="O35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$35,0,(IF($A35=VARIABLES!$B$35,0,O34)+L35)*(1+C35)-N35)</f>
-        <v>12500401.726626789</v>
+        <v>19569287.252955165</v>
       </c>
       <c r="P35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$42,0,IF($A35=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -8962,11 +8963,11 @@
       </c>
       <c r="R35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$42,0,(IF($A35=VARIABLES!$B$42,0,S34)+P35)*C35*VARIABLES!$B$46)</f>
-        <v>869.33610916319344</v>
+        <v>1730.0106285270278</v>
       </c>
       <c r="S35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$42,0,(IF($A35=VARIABLES!$B$42,0,S34)+P35)*(1+C35)-R35)</f>
-        <v>1077107.4392531968</v>
+        <v>1451478.9173341766</v>
       </c>
       <c r="T35" s="26">
         <f>IF($A35&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A35-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -8982,11 +8983,11 @@
       </c>
       <c r="W35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$50,0,(IF($A35&lt;VARIABLES!$B$50+1,0,X34)+U35)*C35*VARIABLES!$B$56)</f>
-        <v>18486.279383004628</v>
+        <v>34003.093964600259</v>
       </c>
       <c r="X35" s="25">
         <f>IF($A35&lt;VARIABLES!$B$50,0,(IF($A35&lt;VARIABLES!$B$50+1,0,X34)+U35)*(1+C35)-W35)</f>
-        <v>5712260.32934843</v>
+        <v>7106646.6386014549</v>
       </c>
       <c r="Y35" s="25">
         <f t="shared" si="0"/>
@@ -8998,15 +8999,15 @@
       </c>
       <c r="AA35" s="25">
         <f t="shared" si="2"/>
-        <v>76293.377115990879</v>
+        <v>162350.09225351908</v>
       </c>
       <c r="AB35" s="17">
         <f t="shared" si="3"/>
-        <v>79743.377115990879</v>
+        <v>165800.09225351908</v>
       </c>
       <c r="AC35" s="18">
         <f t="shared" si="4"/>
-        <v>33512354.023067091</v>
+        <v>47642216.722393699</v>
       </c>
       <c r="AD35" s="25">
         <f>IF($A35=1,VARIABLES!$B$12,0)</f>
@@ -9038,11 +9039,11 @@
       </c>
       <c r="AK35" s="27">
         <f t="shared" si="6"/>
-        <v>18163.293782657543</v>
+        <v>104220.00892018575</v>
       </c>
       <c r="AL35" s="27">
         <f t="shared" si="7"/>
-        <v>-601953.36792434403</v>
+        <v>516924.93286864908</v>
       </c>
       <c r="AM35" s="22">
         <f t="shared" si="8"/>
@@ -9059,7 +9060,7 @@
       </c>
       <c r="C36" s="15">
         <f>IF($A36&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$21,0,IF($A36=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9071,11 +9072,11 @@
       </c>
       <c r="F36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$21,0,(IF($A36=VARIABLES!$B$21,0,G35)+D36)*C36*VARIABLES!$B$25)</f>
-        <v>10302.061822437659</v>
+        <v>21260.192629803496</v>
       </c>
       <c r="G36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$21,0,(IF($A36=VARIABLES!$B$21,0,G35)+D36)*(1+C36)-F36)</f>
-        <v>12764254.598000262</v>
+        <v>17837301.616405133</v>
       </c>
       <c r="H36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$28,0,IF($A36=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9087,11 +9088,11 @@
       </c>
       <c r="J36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$28,0,(IF($A36=VARIABLES!$B$28,0,K35)+H36)*C36*VARIABLES!$B$32)</f>
-        <v>7000.3678030449491</v>
+        <v>13733.249048300566</v>
       </c>
       <c r="K36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$28,0,(IF($A36=VARIABLES!$B$28,0,K35)+H36)*(1+C36)-J36)</f>
-        <v>2163113.6511408896</v>
+        <v>2870249.0510948184</v>
       </c>
       <c r="L36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$35,0,IF($A36=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9103,11 +9104,11 @@
       </c>
       <c r="N36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$35,0,(IF($A36=VARIABLES!$B$35,0,O35)+L36)*C36*VARIABLES!$B$39)</f>
-        <v>41668.005755422637</v>
+        <v>97846.43626477581</v>
       </c>
       <c r="O36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$35,0,(IF($A36=VARIABLES!$B$35,0,O35)+L36)*(1+C36)-N36)</f>
-        <v>12875413.778425595</v>
+        <v>20449905.17933815</v>
       </c>
       <c r="P36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$42,0,IF($A36=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9119,11 +9120,11 @@
       </c>
       <c r="R36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$42,0,(IF($A36=VARIABLES!$B$42,0,S35)+P36)*C36*VARIABLES!$B$46)</f>
-        <v>914.25619937766407</v>
+        <v>1839.3486466677205</v>
       </c>
       <c r="S36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$42,0,(IF($A36=VARIABLES!$B$42,0,S35)+P36)*(1+C36)-R36)</f>
-        <v>1132763.4310289258</v>
+        <v>1543213.5145542177</v>
       </c>
       <c r="T36" s="16">
         <f>IF($A36&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A36-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -9139,11 +9140,11 @@
       </c>
       <c r="W36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$50,0,(IF($A36&lt;VARIABLES!$B$50+1,0,X35)+U36)*C36*VARIABLES!$B$56)</f>
-        <v>19724.201097828103</v>
+        <v>36558.233193007269</v>
       </c>
       <c r="X36" s="7">
         <f>IF($A36&lt;VARIABLES!$B$50,0,(IF($A36&lt;VARIABLES!$B$50+1,0,X35)+U36)*(1+C36)-W36)</f>
-        <v>6094778.1392288832</v>
+        <v>7640670.7373385206</v>
       </c>
       <c r="Y36" s="7">
         <f t="shared" si="0"/>
@@ -9155,15 +9156,15 @@
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="2"/>
-        <v>79608.892678111006</v>
+        <v>171237.45978255486</v>
       </c>
       <c r="AB36" s="17">
         <f t="shared" si="3"/>
-        <v>83096.392678111006</v>
+        <v>174724.95978255486</v>
       </c>
       <c r="AC36" s="18">
         <f t="shared" si="4"/>
-        <v>35030323.597824551</v>
+        <v>50341340.09873084</v>
       </c>
       <c r="AD36" s="7">
         <f>IF($A36=1,VARIABLES!$B$12,0)</f>
@@ -9195,11 +9196,11 @@
       </c>
       <c r="AK36" s="21">
         <f t="shared" si="6"/>
-        <v>21516.30934477767</v>
+        <v>113144.87644922153</v>
       </c>
       <c r="AL36" s="21">
         <f t="shared" si="7"/>
-        <v>-580437.05857956631</v>
+        <v>630069.80931787065</v>
       </c>
       <c r="AM36" s="22">
         <f t="shared" si="8"/>
@@ -9216,7 +9217,7 @@
       </c>
       <c r="C37" s="24">
         <f>IF($A37&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$21,0,IF($A37=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9228,11 +9229,11 @@
       </c>
       <c r="F37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$21,0,(IF($A37=VARIABLES!$B$21,0,G36)+D37)*C37*VARIABLES!$B$25)</f>
-        <v>10803.545498333551</v>
+        <v>22546.627020506417</v>
       </c>
       <c r="G37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$21,0,(IF($A37=VARIABLES!$B$21,0,G36)+D37)*(1+C37)-F37)</f>
-        <v>13385592.872435272</v>
+        <v>18916620.070204884</v>
       </c>
       <c r="H37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$28,0,IF($A37=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9244,11 +9245,11 @@
       </c>
       <c r="J37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$28,0,(IF($A37=VARIABLES!$B$28,0,K36)+H37)*C37*VARIABLES!$B$32)</f>
-        <v>7343.7121704696319</v>
+        <v>14551.245255474092</v>
       </c>
       <c r="K37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$28,0,(IF($A37=VARIABLES!$B$28,0,K36)+H37)*(1+C37)-J37)</f>
-        <v>2269207.0606751167</v>
+        <v>3041210.2583940853</v>
       </c>
       <c r="L37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$35,0,IF($A37=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9260,11 +9261,11 @@
       </c>
       <c r="N37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$35,0,(IF($A37=VARIABLES!$B$35,0,O36)+L37)*C37*VARIABLES!$B$39)</f>
-        <v>42918.045928085317</v>
+        <v>102249.52589669074</v>
       </c>
       <c r="O37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$35,0,(IF($A37=VARIABLES!$B$35,0,O36)+L37)*(1+C37)-N37)</f>
-        <v>13261676.191778364</v>
+        <v>21370150.912408367</v>
       </c>
       <c r="P37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$42,0,IF($A37=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9276,11 +9277,11 @@
       </c>
       <c r="R37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$42,0,(IF($A37=VARIABLES!$B$42,0,S36)+P37)*C37*VARIABLES!$B$46)</f>
-        <v>960.6361925241049</v>
+        <v>1954.0168931927722</v>
       </c>
       <c r="S37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$42,0,(IF($A37=VARIABLES!$B$42,0,S36)+P37)*(1+C37)-R37)</f>
-        <v>1190228.242537366</v>
+        <v>1639420.1733887361</v>
       </c>
       <c r="T37" s="26">
         <f>IF($A37&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A37-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -9296,11 +9297,11 @@
       </c>
       <c r="W37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$50,0,(IF($A37&lt;VARIABLES!$B$50+1,0,X36)+U37)*C37*VARIABLES!$B$56)</f>
-        <v>21015.927130762946</v>
+        <v>39253.353686692601</v>
       </c>
       <c r="X37" s="25">
         <f>IF($A37&lt;VARIABLES!$B$50,0,(IF($A37&lt;VARIABLES!$B$50+1,0,X36)+U37)*(1+C37)-W37)</f>
-        <v>6493921.4834057512</v>
+        <v>8203950.920518755</v>
       </c>
       <c r="Y37" s="25">
         <f t="shared" si="0"/>
@@ -9312,15 +9313,15 @@
       </c>
       <c r="AA37" s="25">
         <f t="shared" si="2"/>
-        <v>83041.866920175555</v>
+        <v>180554.76875255664</v>
       </c>
       <c r="AB37" s="17">
         <f t="shared" si="3"/>
-        <v>86566.866920175555</v>
+        <v>184079.76875255664</v>
       </c>
       <c r="AC37" s="18">
         <f t="shared" si="4"/>
-        <v>36600625.850831866</v>
+        <v>53171352.334914826</v>
       </c>
       <c r="AD37" s="25">
         <f>IF($A37=1,VARIABLES!$B$12,0)</f>
@@ -9352,11 +9353,11 @@
       </c>
       <c r="AK37" s="27">
         <f t="shared" si="6"/>
-        <v>24986.783586842219</v>
+        <v>122499.68541922331</v>
       </c>
       <c r="AL37" s="27">
         <f t="shared" si="7"/>
-        <v>-555450.27499272407</v>
+        <v>752569.49473709392</v>
       </c>
       <c r="AM37" s="22">
         <f t="shared" si="8"/>
@@ -9373,7 +9374,7 @@
       </c>
       <c r="C38" s="15">
         <f>IF($A38&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$21,0,IF($A38=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9385,11 +9386,11 @@
       </c>
       <c r="F38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$21,0,(IF($A38=VARIABLES!$B$21,0,G37)+D38)*C38*VARIABLES!$B$25)</f>
-        <v>11321.327393696061</v>
+        <v>23895.775087756105</v>
       </c>
       <c r="G38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$21,0,(IF($A38=VARIABLES!$B$21,0,G37)+D38)*(1+C38)-F38)</f>
-        <v>14027124.640789419</v>
+        <v>20048555.298627373</v>
       </c>
       <c r="H38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$28,0,IF($A38=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9401,11 +9402,11 @@
       </c>
       <c r="J38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$28,0,(IF($A38=VARIABLES!$B$28,0,K37)+H38)*C38*VARIABLES!$B$32)</f>
-        <v>7697.3568689170561</v>
+        <v>15406.051291970427</v>
       </c>
       <c r="K38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$28,0,(IF($A38=VARIABLES!$B$28,0,K37)+H38)*(1+C38)-J38)</f>
-        <v>2378483.2724953704</v>
+        <v>3219864.7200218192</v>
       </c>
       <c r="L38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$35,0,IF($A38=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9417,11 +9418,11 @@
       </c>
       <c r="N38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$35,0,(IF($A38=VARIABLES!$B$35,0,O37)+L38)*C38*VARIABLES!$B$39)</f>
-        <v>44205.587305927882</v>
+        <v>106850.75456204182</v>
       </c>
       <c r="O38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$35,0,(IF($A38=VARIABLES!$B$35,0,O37)+L38)*(1+C38)-N38)</f>
-        <v>13659526.477531716</v>
+        <v>22331807.703466743</v>
       </c>
       <c r="P38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$42,0,IF($A38=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9433,11 +9434,11 @@
       </c>
       <c r="R38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$42,0,(IF($A38=VARIABLES!$B$42,0,S37)+P38)*C38*VARIABLES!$B$46)</f>
-        <v>1008.523535447805</v>
+        <v>2074.2752167359199</v>
       </c>
       <c r="S38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$42,0,(IF($A38=VARIABLES!$B$42,0,S37)+P38)*(1+C38)-R38)</f>
-        <v>1249560.6604198304</v>
+        <v>1740316.9068414371</v>
       </c>
       <c r="T38" s="16">
         <f>IF($A38&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A38-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -9453,11 +9454,11 @@
       </c>
       <c r="W38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$50,0,(IF($A38&lt;VARIABLES!$B$50+1,0,X37)+U38)*C38*VARIABLES!$B$56)</f>
-        <v>22363.071611352505</v>
+        <v>42094.754602593777</v>
       </c>
       <c r="X38" s="7">
         <f>IF($A38&lt;VARIABLES!$B$50,0,(IF($A38&lt;VARIABLES!$B$50+1,0,X37)+U38)*(1+C38)-W38)</f>
-        <v>6910189.1279079244</v>
+        <v>8797803.711942099</v>
       </c>
       <c r="Y38" s="7">
         <f t="shared" si="0"/>
@@ -9469,15 +9470,15 @@
       </c>
       <c r="AA38" s="7">
         <f t="shared" si="2"/>
-        <v>86595.866715341312</v>
+        <v>190321.61076109807</v>
       </c>
       <c r="AB38" s="17">
         <f t="shared" si="3"/>
-        <v>90158.366715341312</v>
+        <v>193884.11076109807</v>
       </c>
       <c r="AC38" s="18">
         <f t="shared" si="4"/>
-        <v>38224884.179144263</v>
+        <v>56138348.340899467</v>
       </c>
       <c r="AD38" s="7">
         <f>IF($A38=1,VARIABLES!$B$12,0)</f>
@@ -9509,11 +9510,11 @@
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="6"/>
-        <v>28578.283382007976</v>
+        <v>132304.02742776473</v>
       </c>
       <c r="AL38" s="21">
         <f t="shared" si="7"/>
-        <v>-526871.9916107161</v>
+        <v>884873.52216485864</v>
       </c>
       <c r="AM38" s="22">
         <f t="shared" si="8"/>
@@ -9530,7 +9531,7 @@
       </c>
       <c r="C39" s="24">
         <f>IF($A39&lt;VARIABLES!$B$7,VARIABLES!$B$5/12,VARIABLES!$B$6/12)</f>
-        <v>3.3333333333333333E-2</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="D39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$21,0,IF($A39=VARIABLES!$B$21,VARIABLES!$B$22+VARIABLES!$B$23,VARIABLES!$B$23))</f>
@@ -9542,11 +9543,11 @@
       </c>
       <c r="F39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$21,0,(IF($A39=VARIABLES!$B$21,0,G38)+D39)*C39*VARIABLES!$B$25)</f>
-        <v>11855.937200657849</v>
+        <v>25310.694123284215</v>
       </c>
       <c r="G39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$21,0,(IF($A39=VARIABLES!$B$21,0,G38)+D39)*(1+C39)-F39)</f>
-        <v>14689506.191615077</v>
+        <v>21235672.369435459</v>
       </c>
       <c r="H39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$28,0,IF($A39=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9558,11 +9559,11 @@
       </c>
       <c r="J39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$28,0,(IF($A39=VARIABLES!$B$28,0,K38)+H39)*C39*VARIABLES!$B$32)</f>
-        <v>8061.6109083179008</v>
+        <v>16299.323600109097</v>
       </c>
       <c r="K39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$28,0,(IF($A39=VARIABLES!$B$28,0,K38)+H39)*(1+C39)-J39)</f>
-        <v>2491037.7706702319</v>
+        <v>3406558.6324228011</v>
       </c>
       <c r="L39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$35,0,IF($A39=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9574,11 +9575,11 @@
       </c>
       <c r="N39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$35,0,(IF($A39=VARIABLES!$B$35,0,O38)+L39)*C39*VARIABLES!$B$39)</f>
-        <v>45531.754925105721</v>
+        <v>111659.03851733371</v>
       </c>
       <c r="O39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$35,0,(IF($A39=VARIABLES!$B$35,0,O38)+L39)*(1+C39)-N39)</f>
-        <v>14069312.27185767</v>
+        <v>23336739.050122749</v>
       </c>
       <c r="P39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$42,0,IF($A39=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9590,11 +9591,11 @@
       </c>
       <c r="R39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$42,0,(IF($A39=VARIABLES!$B$42,0,S38)+P39)*C39*VARIABLES!$B$46)</f>
-        <v>1057.9672170165254</v>
+        <v>2200.3961335517961</v>
       </c>
       <c r="S39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$42,0,(IF($A39=VARIABLES!$B$42,0,S38)+P39)*(1+C39)-R39)</f>
-        <v>1310821.381883475</v>
+        <v>1846132.3560499572</v>
       </c>
       <c r="T39" s="26">
         <f>IF($A39&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A39-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -9610,11 +9611,11 @@
       </c>
       <c r="W39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$50,0,(IF($A39&lt;VARIABLES!$B$50+1,0,X38)+U39)*C39*VARIABLES!$B$56)</f>
-        <v>23767.297093026413</v>
+        <v>45089.018559710494</v>
       </c>
       <c r="X39" s="25">
         <f>IF($A39&lt;VARIABLES!$B$50,0,(IF($A39&lt;VARIABLES!$B$50+1,0,X38)+U39)*(1+C39)-W39)</f>
-        <v>7344094.8017451633</v>
+        <v>9423604.8789794929</v>
       </c>
       <c r="Y39" s="25">
         <f t="shared" si="0"/>
@@ -9626,15 +9627,15 @@
       </c>
       <c r="AA39" s="25">
         <f t="shared" si="2"/>
-        <v>90274.567344124414</v>
+        <v>200558.4709339893</v>
       </c>
       <c r="AB39" s="17">
         <f t="shared" si="3"/>
-        <v>93874.567344124414</v>
+        <v>204158.4709339893</v>
       </c>
       <c r="AC39" s="18">
         <f t="shared" si="4"/>
-        <v>39904772.417771623</v>
+        <v>59248707.287010461</v>
       </c>
       <c r="AD39" s="25">
         <f>IF($A39=1,VARIABLES!$B$12,0)</f>
@@ -9646,7 +9647,7 @@
       </c>
       <c r="AF39" s="25">
         <f>IF(MOD($A39,12)=0,AC39*VARIABLES!$B$16,0)</f>
-        <v>99761.93104442906</v>
+        <v>148121.76821752614</v>
       </c>
       <c r="AG39" s="25">
         <f>VARIABLES!$B$17</f>
@@ -9658,7 +9659,7 @@
       </c>
       <c r="AI39" s="19">
         <f t="shared" si="5"/>
-        <v>153761.93104442907</v>
+        <v>202121.76821752614</v>
       </c>
       <c r="AJ39" s="20">
         <f>IF($A39&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -9666,11 +9667,11 @@
       </c>
       <c r="AK39" s="27">
         <f t="shared" si="6"/>
-        <v>-70467.447033637989</v>
+        <v>-8543.3806168701758</v>
       </c>
       <c r="AL39" s="27">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM39" s="22">
         <f t="shared" si="8"/>
@@ -9699,11 +9700,11 @@
       </c>
       <c r="F40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$21,0,(IF($A40=VARIABLES!$B$21,0,G39)+D40)*C40*VARIABLES!$B$25)</f>
-        <v>3101.9804565864742</v>
+        <v>4465.7650769657212</v>
       </c>
       <c r="G40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$21,0,(IF($A40=VARIABLES!$B$21,0,G39)+D40)*(1+C40)-F40)</f>
-        <v>15010483.429421948</v>
+        <v>21609837.207437124</v>
       </c>
       <c r="H40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$28,0,IF($A40=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9715,11 +9716,11 @@
       </c>
       <c r="J40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$28,0,(IF($A40=VARIABLES!$B$28,0,K39)+H40)*C40*VARIABLES!$B$32)</f>
-        <v>2109.1981422251934</v>
+        <v>2872.1321936856675</v>
       </c>
       <c r="K40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$28,0,(IF($A40=VARIABLES!$B$28,0,K39)+H40)*(1+C40)-J40)</f>
-        <v>2550020.5539502585</v>
+        <v>3472407.8221659721</v>
       </c>
       <c r="L40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$35,0,IF($A40=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9731,11 +9732,11 @@
       </c>
       <c r="N40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$35,0,(IF($A40=VARIABLES!$B$35,0,O39)+L40)*C40*VARIABLES!$B$39)</f>
-        <v>11724.426893214724</v>
+        <v>19447.282541768956</v>
       </c>
       <c r="O40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$35,0,(IF($A40=VARIABLES!$B$35,0,O39)+L40)*(1+C40)-N40)</f>
-        <v>14174832.113896601</v>
+        <v>23511764.592998669</v>
       </c>
       <c r="P40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$42,0,IF($A40=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9747,11 +9748,11 @@
       </c>
       <c r="R40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$42,0,(IF($A40=VARIABLES!$B$42,0,S39)+P40)*C40*VARIABLES!$B$46)</f>
-        <v>277.25445455905731</v>
+        <v>388.77757417707443</v>
       </c>
       <c r="S40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$42,0,(IF($A40=VARIABLES!$B$42,0,S39)+P40)*(1+C40)-R40)</f>
-        <v>1341634.3056112784</v>
+        <v>1881294.6814428631</v>
       </c>
       <c r="T40" s="16">
         <f>IF($A40&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A40-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -9767,11 +9768,11 @@
       </c>
       <c r="W40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$50,0,(IF($A40&lt;VARIABLES!$B$50+1,0,X39)+U40)*C40*VARIABLES!$B$56)</f>
-        <v>6307.5790014543027</v>
+        <v>8040.5040658162443</v>
       </c>
       <c r="X40" s="7">
         <f>IF($A40&lt;VARIABLES!$B$50,0,(IF($A40&lt;VARIABLES!$B$50+1,0,X39)+U40)*(1+C40)-W40)</f>
-        <v>7625863.0127582513</v>
+        <v>9720969.4155718405</v>
       </c>
       <c r="Y40" s="7">
         <f t="shared" si="0"/>
@@ -9783,15 +9784,15 @@
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="2"/>
-        <v>23520.438948039751</v>
+        <v>35214.461452413663</v>
       </c>
       <c r="AB40" s="17">
         <f t="shared" si="3"/>
-        <v>27157.938948039751</v>
+        <v>38851.961452413663</v>
       </c>
       <c r="AC40" s="18">
         <f t="shared" si="4"/>
-        <v>40702833.415638342</v>
+        <v>60196273.719616465</v>
       </c>
       <c r="AD40" s="7">
         <f>IF($A40=1,VARIABLES!$B$12,0)</f>
@@ -9823,15 +9824,15 @@
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="6"/>
-        <v>-23842.061051960249</v>
+        <v>-12148.038547586337</v>
       </c>
       <c r="AL40" s="21">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM40" s="22">
         <f t="shared" si="8"/>
-        <v>357040.93894803966</v>
+        <v>368734.96145241352</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.2">
@@ -9856,11 +9857,11 @@
       </c>
       <c r="F41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$21,0,(IF($A41=VARIABLES!$B$21,0,G40)+D41)*C41*VARIABLES!$B$25)</f>
-        <v>3168.8507144629057</v>
+        <v>4543.7160848827343</v>
       </c>
       <c r="G41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$21,0,(IF($A41=VARIABLES!$B$21,0,G40)+D41)*(1+C41)-F41)</f>
-        <v>15334068.607286001</v>
+        <v>21987042.13474755</v>
       </c>
       <c r="H41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$28,0,IF($A41=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -9872,11 +9873,11 @@
       </c>
       <c r="J41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$28,0,(IF($A41=VARIABLES!$B$28,0,K40)+H41)*C41*VARIABLES!$B$32)</f>
-        <v>2158.3504616252153</v>
+        <v>2927.0065184716436</v>
       </c>
       <c r="K41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$28,0,(IF($A41=VARIABLES!$B$28,0,K40)+H41)*(1+C41)-J41)</f>
-        <v>2609445.7081048856</v>
+        <v>3538750.8808322167</v>
       </c>
       <c r="L41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$35,0,IF($A41=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -9888,11 +9889,11 @@
       </c>
       <c r="N41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$35,0,(IF($A41=VARIABLES!$B$35,0,O40)+L41)*C41*VARIABLES!$B$39)</f>
-        <v>11812.360094913834</v>
+        <v>19593.137160832222</v>
       </c>
       <c r="O41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$35,0,(IF($A41=VARIABLES!$B$35,0,O40)+L41)*(1+C41)-N41)</f>
-        <v>14281143.354750825</v>
+        <v>23688102.827446155</v>
       </c>
       <c r="P41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$42,0,IF($A41=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -9904,11 +9905,11 @@
       </c>
       <c r="R41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$42,0,(IF($A41=VARIABLES!$B$42,0,S40)+P41)*C41*VARIABLES!$B$46)</f>
-        <v>283.67381366901634</v>
+        <v>396.10305863392983</v>
       </c>
       <c r="S41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$42,0,(IF($A41=VARIABLES!$B$42,0,S40)+P41)*(1+C41)-R41)</f>
-        <v>1372697.5843443701</v>
+        <v>1916742.7007295864</v>
       </c>
       <c r="T41" s="26">
         <f>IF($A41&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A41-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -9924,11 +9925,11 @@
       </c>
       <c r="W41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$50,0,(IF($A41&lt;VARIABLES!$B$50+1,0,X40)+U41)*C41*VARIABLES!$B$56)</f>
-        <v>6546.5525106318764</v>
+        <v>8292.4745129765342</v>
       </c>
       <c r="X41" s="25">
         <f>IF($A41&lt;VARIABLES!$B$50,0,(IF($A41&lt;VARIABLES!$B$50+1,0,X40)+U41)*(1+C41)-W41)</f>
-        <v>7914781.9853539374</v>
+        <v>10025601.686188631</v>
       </c>
       <c r="Y41" s="25">
         <f t="shared" si="0"/>
@@ -9940,15 +9941,15 @@
       </c>
       <c r="AA41" s="25">
         <f t="shared" si="2"/>
-        <v>23969.787595302849</v>
+        <v>35752.437335797062</v>
       </c>
       <c r="AB41" s="17">
         <f t="shared" si="3"/>
-        <v>27644.787595302849</v>
+        <v>39427.437335797062</v>
       </c>
       <c r="AC41" s="18">
         <f t="shared" si="4"/>
-        <v>41512137.239840023</v>
+        <v>61156240.22994414</v>
       </c>
       <c r="AD41" s="25">
         <f>IF($A41=1,VARIABLES!$B$12,0)</f>
@@ -9980,15 +9981,15 @@
       </c>
       <c r="AK41" s="27">
         <f t="shared" si="6"/>
-        <v>-23355.212404697151</v>
+        <v>-11572.562664202938</v>
       </c>
       <c r="AL41" s="27">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM41" s="22">
         <f t="shared" si="8"/>
-        <v>333685.72654334252</v>
+        <v>357162.39878821059</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.2">
@@ -10013,11 +10014,11 @@
       </c>
       <c r="F42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$21,0,(IF($A42=VARIABLES!$B$21,0,G41)+D42)*C42*VARIABLES!$B$25)</f>
-        <v>3236.2642931845839</v>
+        <v>4622.3004447390731</v>
       </c>
       <c r="G42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$21,0,(IF($A42=VARIABLES!$B$21,0,G41)+D42)*(1+C42)-F42)</f>
-        <v>15660282.914720198</v>
+        <v>22367311.85209237</v>
       </c>
       <c r="H42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$28,0,IF($A42=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10029,11 +10030,11 @@
       </c>
       <c r="J42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$28,0,(IF($A42=VARIABLES!$B$28,0,K41)+H42)*C42*VARIABLES!$B$32)</f>
-        <v>2207.8714234207378</v>
+        <v>2982.2924006935141</v>
       </c>
       <c r="K42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$28,0,(IF($A42=VARIABLES!$B$28,0,K41)+H42)*(1+C42)-J42)</f>
-        <v>2669316.550915672</v>
+        <v>3605591.5124384584</v>
       </c>
       <c r="L42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$35,0,IF($A42=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10045,11 +10046,11 @@
       </c>
       <c r="N42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$35,0,(IF($A42=VARIABLES!$B$35,0,O41)+L42)*C42*VARIABLES!$B$39)</f>
-        <v>11900.952795625688</v>
+        <v>19740.085689538464</v>
       </c>
       <c r="O42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$35,0,(IF($A42=VARIABLES!$B$35,0,O41)+L42)*(1+C42)-N42)</f>
-        <v>14388251.929911455</v>
+        <v>23865763.598652001</v>
       </c>
       <c r="P42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$42,0,IF($A42=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10061,11 +10062,11 @@
       </c>
       <c r="R42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$42,0,(IF($A42=VARIABLES!$B$42,0,S41)+P42)*C42*VARIABLES!$B$46)</f>
-        <v>290.14533007174379</v>
+        <v>403.48806265199715</v>
       </c>
       <c r="S42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$42,0,(IF($A42=VARIABLES!$B$42,0,S41)+P42)*(1+C42)-R42)</f>
-        <v>1404013.252217168</v>
+        <v>1952478.7351730142</v>
       </c>
       <c r="T42" s="16">
         <f>IF($A42&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A42-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -10081,11 +10082,11 @@
       </c>
       <c r="W42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$50,0,(IF($A42&lt;VARIABLES!$B$50+1,0,X41)+U42)*C42*VARIABLES!$B$56)</f>
-        <v>6791.4849877949491</v>
+        <v>8550.5014051571925</v>
       </c>
       <c r="X42" s="7">
         <f>IF($A42&lt;VARIABLES!$B$50,0,(IF($A42&lt;VARIABLES!$B$50+1,0,X41)+U42)*(1+C42)-W42)</f>
-        <v>8210905.3502440909</v>
+        <v>10337556.198835045</v>
       </c>
       <c r="Y42" s="7">
         <f t="shared" si="0"/>
@@ -10097,15 +10098,15 @@
       </c>
       <c r="AA42" s="7">
         <f t="shared" si="2"/>
-        <v>24426.718830097703</v>
+        <v>36298.668002780243</v>
       </c>
       <c r="AB42" s="17">
         <f t="shared" si="3"/>
-        <v>28139.218830097703</v>
+        <v>40011.168002780243</v>
       </c>
       <c r="AC42" s="18">
         <f t="shared" si="4"/>
-        <v>42332769.998008579</v>
+        <v>62128701.897190891</v>
       </c>
       <c r="AD42" s="7">
         <f>IF($A42=1,VARIABLES!$B$12,0)</f>
@@ -10137,15 +10138,15 @@
       </c>
       <c r="AK42" s="21">
         <f t="shared" si="6"/>
-        <v>-22860.781169902297</v>
+        <v>-10988.831997219757</v>
       </c>
       <c r="AL42" s="21">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM42" s="22">
         <f t="shared" si="8"/>
-        <v>310824.94537344022</v>
+        <v>346173.56679099082</v>
       </c>
     </row>
     <row r="43" spans="1:39" x14ac:dyDescent="0.2">
@@ -10170,11 +10171,11 @@
       </c>
       <c r="F43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$21,0,(IF($A43=VARIABLES!$B$21,0,G42)+D43)*C43*VARIABLES!$B$25)</f>
-        <v>3304.2256072333748</v>
+        <v>4701.5233025192438</v>
       </c>
       <c r="G43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$21,0,(IF($A43=VARIABLES!$B$21,0,G42)+D43)*(1+C43)-F43)</f>
-        <v>15989147.713402299</v>
+        <v>22750671.260890622</v>
       </c>
       <c r="H43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$28,0,IF($A43=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10186,11 +10187,11 @@
       </c>
       <c r="J43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$28,0,(IF($A43=VARIABLES!$B$28,0,K42)+H43)*C43*VARIABLES!$B$32)</f>
-        <v>2257.7637924297264</v>
+        <v>3037.9929270320486</v>
       </c>
       <c r="K43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$28,0,(IF($A43=VARIABLES!$B$28,0,K42)+H43)*(1+C43)-J43)</f>
-        <v>2729636.4250475396</v>
+        <v>3672933.4487817469</v>
       </c>
       <c r="L43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$35,0,IF($A43=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10202,11 +10203,11 @@
       </c>
       <c r="N43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$35,0,(IF($A43=VARIABLES!$B$35,0,O42)+L43)*C43*VARIABLES!$B$39)</f>
-        <v>11990.209941592881</v>
+        <v>19888.136332210004</v>
       </c>
       <c r="O43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$35,0,(IF($A43=VARIABLES!$B$35,0,O42)+L43)*(1+C43)-N43)</f>
-        <v>14496163.819385791</v>
+        <v>24044756.825641889</v>
       </c>
       <c r="P43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$42,0,IF($A43=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10218,11 +10219,11 @@
       </c>
       <c r="R43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$42,0,(IF($A43=VARIABLES!$B$42,0,S42)+P43)*C43*VARIABLES!$B$46)</f>
-        <v>296.66942754524337</v>
+        <v>410.93306982771128</v>
       </c>
       <c r="S43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$42,0,(IF($A43=VARIABLES!$B$42,0,S42)+P43)*(1+C43)-R43)</f>
-        <v>1435583.3598914323</v>
+        <v>1988505.1248962949</v>
       </c>
       <c r="T43" s="26">
         <f>IF($A43&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A43-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -10238,11 +10239,11 @@
       </c>
       <c r="W43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$50,0,(IF($A43&lt;VARIABLES!$B$50+1,0,X42)+U43)*C43*VARIABLES!$B$56)</f>
-        <v>7042.4211252034092</v>
+        <v>8814.6301656958713</v>
       </c>
       <c r="X43" s="25">
         <f>IF($A43&lt;VARIABLES!$B$50,0,(IF($A43&lt;VARIABLES!$B$50+1,0,X42)+U43)*(1+C43)-W43)</f>
-        <v>8514287.1403709203</v>
+        <v>10656887.870326307</v>
       </c>
       <c r="Y43" s="25">
         <f t="shared" si="0"/>
@@ -10254,15 +10255,15 @@
       </c>
       <c r="AA43" s="25">
         <f t="shared" si="2"/>
-        <v>24891.289894004636</v>
+        <v>36853.21579728488</v>
       </c>
       <c r="AB43" s="17">
         <f t="shared" si="3"/>
-        <v>28641.289894004636</v>
+        <v>40603.21579728488</v>
       </c>
       <c r="AC43" s="18">
         <f t="shared" si="4"/>
-        <v>43164818.458097979</v>
+        <v>63113754.53053686</v>
       </c>
       <c r="AD43" s="25">
         <f>IF($A43=1,VARIABLES!$B$12,0)</f>
@@ -10294,15 +10295,15 @@
       </c>
       <c r="AK43" s="27">
         <f t="shared" si="6"/>
-        <v>-22358.710105995364</v>
+        <v>-10396.78420271512</v>
       </c>
       <c r="AL43" s="27">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM43" s="22">
         <f t="shared" si="8"/>
-        <v>288466.23526744486</v>
+        <v>335776.78258827573</v>
       </c>
     </row>
     <row r="44" spans="1:39" x14ac:dyDescent="0.2">
@@ -10327,11 +10328,11 @@
       </c>
       <c r="F44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$21,0,(IF($A44=VARIABLES!$B$21,0,G43)+D44)*C44*VARIABLES!$B$25)</f>
-        <v>3372.739106958812</v>
+        <v>4781.3898460188793</v>
       </c>
       <c r="G44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$21,0,(IF($A44=VARIABLES!$B$21,0,G43)+D44)*(1+C44)-F44)</f>
-        <v>16320684.538573692</v>
+        <v>23137145.464885358</v>
       </c>
       <c r="H44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$28,0,IF($A44=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10343,11 +10344,11 @@
       </c>
       <c r="J44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$28,0,(IF($A44=VARIABLES!$B$28,0,K43)+H44)*C44*VARIABLES!$B$32)</f>
-        <v>2308.0303542062829</v>
+        <v>3094.1112073181225</v>
       </c>
       <c r="K44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$28,0,(IF($A44=VARIABLES!$B$28,0,K43)+H44)*(1+C44)-J44)</f>
-        <v>2790408.6982353958</v>
+        <v>3740780.4496476101</v>
       </c>
       <c r="L44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$35,0,IF($A44=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10359,11 +10360,11 @@
       </c>
       <c r="N44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$35,0,(IF($A44=VARIABLES!$B$35,0,O43)+L44)*C44*VARIABLES!$B$39)</f>
-        <v>12080.136516154826</v>
+        <v>20037.297354701575</v>
       </c>
       <c r="O44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$35,0,(IF($A44=VARIABLES!$B$35,0,O43)+L44)*(1+C44)-N44)</f>
-        <v>14604885.048031183</v>
+        <v>24225092.501834203</v>
       </c>
       <c r="P44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$42,0,IF($A44=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10375,11 +10376,11 @@
       </c>
       <c r="R44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$42,0,(IF($A44=VARIABLES!$B$42,0,S43)+P44)*C44*VARIABLES!$B$46)</f>
-        <v>303.24653331071511</v>
+        <v>418.43856768672816</v>
       </c>
       <c r="S44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$42,0,(IF($A44=VARIABLES!$B$42,0,S43)+P44)*(1+C44)-R44)</f>
-        <v>1467409.9746905502</v>
+        <v>2024824.2290360772</v>
       </c>
       <c r="T44" s="16">
         <f>IF($A44&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A44-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -10395,11 +10396,11 @@
       </c>
       <c r="W44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$50,0,(IF($A44&lt;VARIABLES!$B$50+1,0,X43)+U44)*C44*VARIABLES!$B$56)</f>
-        <v>7299.4059503091012</v>
+        <v>9084.9065586052566</v>
       </c>
       <c r="X44" s="7">
         <f>IF($A44&lt;VARIABLES!$B$50,0,(IF($A44&lt;VARIABLES!$B$50+1,0,X43)+U44)*(1+C44)-W44)</f>
-        <v>8824981.7939237021</v>
+        <v>10983652.029353755</v>
       </c>
       <c r="Y44" s="7">
         <f t="shared" si="0"/>
@@ -10411,15 +10412,15 @@
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="2"/>
-        <v>25363.558460939734</v>
+        <v>37416.143534330564</v>
       </c>
       <c r="AB44" s="17">
         <f t="shared" si="3"/>
-        <v>29151.058460939734</v>
+        <v>41203.643534330564</v>
       </c>
       <c r="AC44" s="18">
         <f t="shared" si="4"/>
-        <v>44008370.053454518</v>
+        <v>64111494.674757004</v>
       </c>
       <c r="AD44" s="7">
         <f>IF($A44=1,VARIABLES!$B$12,0)</f>
@@ -10451,15 +10452,15 @@
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="6"/>
-        <v>-21848.941539060266</v>
+        <v>-9796.3564656694361</v>
       </c>
       <c r="AL44" s="21">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM44" s="22">
         <f t="shared" si="8"/>
-        <v>266617.2937283846</v>
+        <v>325980.42612260627</v>
       </c>
     </row>
     <row r="45" spans="1:39" x14ac:dyDescent="0.2">
@@ -10484,11 +10485,11 @@
       </c>
       <c r="F45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$21,0,(IF($A45=VARIABLES!$B$21,0,G44)+D45)*C45*VARIABLES!$B$25)</f>
-        <v>3441.8092788695194</v>
+        <v>4861.9053051844494</v>
       </c>
       <c r="G45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$21,0,(IF($A45=VARIABLES!$B$21,0,G44)+D45)*(1+C45)-F45)</f>
-        <v>16654915.100449601</v>
+        <v>23526759.77178755</v>
       </c>
       <c r="H45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$28,0,IF($A45=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10500,11 +10501,11 @@
       </c>
       <c r="J45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$28,0,(IF($A45=VARIABLES!$B$28,0,K44)+H45)*C45*VARIABLES!$B$32)</f>
-        <v>2358.6739151961633</v>
+        <v>3150.6503747063416</v>
       </c>
       <c r="K45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$28,0,(IF($A45=VARIABLES!$B$28,0,K44)+H45)*(1+C45)-J45)</f>
-        <v>2851636.7634721613</v>
+        <v>3809136.3030199669</v>
       </c>
       <c r="L45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$35,0,IF($A45=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10516,11 +10517,11 @@
       </c>
       <c r="N45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$35,0,(IF($A45=VARIABLES!$B$35,0,O44)+L45)*C45*VARIABLES!$B$39)</f>
-        <v>12170.737540025986</v>
+        <v>20187.577084861838</v>
       </c>
       <c r="O45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$35,0,(IF($A45=VARIABLES!$B$35,0,O44)+L45)*(1+C45)-N45)</f>
-        <v>14714421.685891418</v>
+        <v>24406780.695597958</v>
       </c>
       <c r="P45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$42,0,IF($A45=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10532,11 +10533,11 @@
       </c>
       <c r="R45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$42,0,(IF($A45=VARIABLES!$B$42,0,S44)+P45)*C45*VARIABLES!$B$46)</f>
-        <v>309.87707806053135</v>
+        <v>426.0050477158494</v>
       </c>
       <c r="S45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$42,0,(IF($A45=VARIABLES!$B$42,0,S44)+P45)*(1+C45)-R45)</f>
-        <v>1499495.180734911</v>
+        <v>2061438.4258969952</v>
       </c>
       <c r="T45" s="26">
         <f>IF($A45&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A45-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -10552,11 +10553,11 @@
       </c>
       <c r="W45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$50,0,(IF($A45&lt;VARIABLES!$B$50+1,0,X44)+U45)*C45*VARIABLES!$B$56)</f>
-        <v>7562.4848282697531</v>
+        <v>9361.3766911281291</v>
       </c>
       <c r="X45" s="25">
         <f>IF($A45&lt;VARIABLES!$B$50,0,(IF($A45&lt;VARIABLES!$B$50+1,0,X44)+U45)*(1+C45)-W45)</f>
-        <v>9143044.1573781297</v>
+        <v>11317904.419573907</v>
       </c>
       <c r="Y45" s="25">
         <f t="shared" si="0"/>
@@ -10568,15 +10569,15 @@
       </c>
       <c r="AA45" s="25">
         <f t="shared" si="2"/>
-        <v>25843.582640421952</v>
+        <v>37987.514503596605</v>
       </c>
       <c r="AB45" s="17">
         <f t="shared" si="3"/>
-        <v>29668.582640421952</v>
+        <v>41812.514503596605</v>
       </c>
       <c r="AC45" s="18">
         <f t="shared" si="4"/>
-        <v>44863512.887926221</v>
+        <v>65122019.615876377</v>
       </c>
       <c r="AD45" s="25">
         <f>IF($A45=1,VARIABLES!$B$12,0)</f>
@@ -10608,15 +10609,15 @@
       </c>
       <c r="AK45" s="27">
         <f t="shared" si="6"/>
-        <v>-21331.417359578048</v>
+        <v>-9187.4854964033948</v>
       </c>
       <c r="AL45" s="27">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM45" s="22">
         <f t="shared" si="8"/>
-        <v>245285.87636880655</v>
+        <v>316792.94062620285</v>
       </c>
     </row>
     <row r="46" spans="1:39" x14ac:dyDescent="0.2">
@@ -10641,11 +10642,11 @@
       </c>
       <c r="F46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$21,0,(IF($A46=VARIABLES!$B$21,0,G45)+D46)*C46*VARIABLES!$B$25)</f>
-        <v>3511.4406459270003</v>
+        <v>4943.0749524557395</v>
       </c>
       <c r="G46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$21,0,(IF($A46=VARIABLES!$B$21,0,G45)+D46)*(1+C46)-F46)</f>
-        <v>16991861.285640754</v>
+        <v>23919539.694933321</v>
       </c>
       <c r="H46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$28,0,IF($A46=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10657,11 +10658,11 @@
       </c>
       <c r="J46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$28,0,(IF($A46=VARIABLES!$B$28,0,K45)+H46)*C46*VARIABLES!$B$32)</f>
-        <v>2409.6973028934676</v>
+        <v>3207.6135858499729</v>
       </c>
       <c r="K46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$28,0,(IF($A46=VARIABLES!$B$28,0,K45)+H46)*(1+C46)-J46)</f>
-        <v>2913324.0391982025</v>
+        <v>3878004.8252926166</v>
       </c>
       <c r="L46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$35,0,IF($A46=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10673,11 +10674,11 @@
       </c>
       <c r="N46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$35,0,(IF($A46=VARIABLES!$B$35,0,O45)+L46)*C46*VARIABLES!$B$39)</f>
-        <v>12262.018071576182</v>
+        <v>20338.983912998301</v>
       </c>
       <c r="O46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$35,0,(IF($A46=VARIABLES!$B$35,0,O45)+L46)*(1+C46)-N46)</f>
-        <v>14824779.848535603</v>
+        <v>24589831.550814942</v>
       </c>
       <c r="P46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$42,0,IF($A46=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10689,11 +10690,11 @@
       </c>
       <c r="R46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$42,0,(IF($A46=VARIABLES!$B$42,0,S45)+P46)*C46*VARIABLES!$B$46)</f>
-        <v>316.56149598643981</v>
+        <v>433.63300539520736</v>
       </c>
       <c r="S46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$42,0,(IF($A46=VARIABLES!$B$42,0,S45)+P46)*(1+C46)-R46)</f>
-        <v>1531841.0790783821</v>
+        <v>2098350.1131074084</v>
       </c>
       <c r="T46" s="16">
         <f>IF($A46&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A46-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -10709,11 +10710,11 @@
       </c>
       <c r="W46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$50,0,(IF($A46&lt;VARIABLES!$B$50+1,0,X45)+U46)*C46*VARIABLES!$B$56)</f>
-        <v>7831.703464481775</v>
+        <v>9644.0870163115887</v>
       </c>
       <c r="X46" s="7">
         <f>IF($A46&lt;VARIABLES!$B$50,0,(IF($A46&lt;VARIABLES!$B$50+1,0,X45)+U46)*(1+C46)-W46)</f>
-        <v>9468529.4885584656</v>
+        <v>11659701.202720709</v>
       </c>
       <c r="Y46" s="7">
         <f t="shared" si="0"/>
@@ -10725,15 +10726,15 @@
       </c>
       <c r="AA46" s="7">
         <f t="shared" si="2"/>
-        <v>26331.420980864867</v>
+        <v>38567.392473010812</v>
       </c>
       <c r="AB46" s="17">
         <f t="shared" si="3"/>
-        <v>30193.920980864867</v>
+        <v>42429.892473010812</v>
       </c>
       <c r="AC46" s="18">
         <f t="shared" si="4"/>
-        <v>45730335.741011404</v>
+        <v>66145427.386868998</v>
       </c>
       <c r="AD46" s="7">
         <f>IF($A46=1,VARIABLES!$B$12,0)</f>
@@ -10765,15 +10766,15 @@
       </c>
       <c r="AK46" s="21">
         <f t="shared" si="6"/>
-        <v>-20806.079019135133</v>
+        <v>-8570.107526989188</v>
       </c>
       <c r="AL46" s="21">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM46" s="22">
         <f t="shared" si="8"/>
-        <v>224479.79734967143</v>
+        <v>308222.83309921366</v>
       </c>
     </row>
     <row r="47" spans="1:39" x14ac:dyDescent="0.2">
@@ -10798,11 +10799,11 @@
       </c>
       <c r="F47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$21,0,(IF($A47=VARIABLES!$B$21,0,G46)+D47)*C47*VARIABLES!$B$25)</f>
-        <v>3581.6377678418235</v>
+        <v>5024.9041031111083</v>
       </c>
       <c r="G47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$21,0,(IF($A47=VARIABLES!$B$21,0,G46)+D47)*(1+C47)-F47)</f>
-        <v>17331545.158586588</v>
+        <v>24315510.954954654</v>
       </c>
       <c r="H47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$28,0,IF($A47=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10814,11 +10815,11 @@
       </c>
       <c r="J47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$28,0,(IF($A47=VARIABLES!$B$28,0,K46)+H47)*C47*VARIABLES!$B$32)</f>
-        <v>2461.1033659985023</v>
+        <v>3265.0040210771804</v>
       </c>
       <c r="K47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$28,0,(IF($A47=VARIABLES!$B$28,0,K46)+H47)*(1+C47)-J47)</f>
-        <v>2975473.9694921887</v>
+        <v>3947389.8614823115</v>
       </c>
       <c r="L47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$35,0,IF($A47=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10830,11 +10831,11 @@
       </c>
       <c r="N47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$35,0,(IF($A47=VARIABLES!$B$35,0,O46)+L47)*C47*VARIABLES!$B$39)</f>
-        <v>12353.983207113002</v>
+        <v>20491.526292345785</v>
       </c>
       <c r="O47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$35,0,(IF($A47=VARIABLES!$B$35,0,O46)+L47)*(1+C47)-N47)</f>
-        <v>14935965.69739962</v>
+        <v>24774255.287446052</v>
       </c>
       <c r="P47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$42,0,IF($A47=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -10846,11 +10847,11 @@
       </c>
       <c r="R47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$42,0,(IF($A47=VARIABLES!$B$42,0,S46)+P47)*C47*VARIABLES!$B$46)</f>
-        <v>323.3002248079963</v>
+        <v>441.32294023071012</v>
       </c>
       <c r="S47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$42,0,(IF($A47=VARIABLES!$B$42,0,S46)+P47)*(1+C47)-R47)</f>
-        <v>1564449.7878458938</v>
+        <v>2135561.7077764058</v>
       </c>
       <c r="T47" s="26">
         <f>IF($A47&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A47-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -10866,11 +10867,11 @@
       </c>
       <c r="W47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$50,0,(IF($A47&lt;VARIABLES!$B$50+1,0,X46)+U47)*C47*VARIABLES!$B$56)</f>
-        <v>8107.1079071320555</v>
+        <v>9933.0843356005917</v>
       </c>
       <c r="X47" s="25">
         <f>IF($A47&lt;VARIABLES!$B$50,0,(IF($A47&lt;VARIABLES!$B$50+1,0,X46)+U47)*(1+C47)-W47)</f>
-        <v>9801493.4597226549</v>
+        <v>12009098.961741114</v>
       </c>
       <c r="Y47" s="25">
         <f t="shared" si="0"/>
@@ -10882,15 +10883,15 @@
       </c>
       <c r="AA47" s="25">
         <f t="shared" si="2"/>
-        <v>26827.13247289338</v>
+        <v>39155.841692365379</v>
       </c>
       <c r="AB47" s="17">
         <f t="shared" si="3"/>
-        <v>30727.13247289338</v>
+        <v>43055.841692365379</v>
       </c>
       <c r="AC47" s="18">
         <f t="shared" si="4"/>
-        <v>46608928.073046945</v>
+        <v>67181816.77340053</v>
       </c>
       <c r="AD47" s="25">
         <f>IF($A47=1,VARIABLES!$B$12,0)</f>
@@ -10922,15 +10923,15 @@
       </c>
       <c r="AK47" s="27">
         <f t="shared" si="6"/>
-        <v>-20272.86752710662</v>
+        <v>-7944.1583076346215</v>
       </c>
       <c r="AL47" s="27">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM47" s="22">
         <f t="shared" si="8"/>
-        <v>204206.92982256479</v>
+        <v>300278.67479157902</v>
       </c>
     </row>
     <row r="48" spans="1:39" x14ac:dyDescent="0.2">
@@ -10955,11 +10956,11 @@
       </c>
       <c r="F48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$21,0,(IF($A48=VARIABLES!$B$21,0,G47)+D48)*C48*VARIABLES!$B$25)</f>
-        <v>3652.4052413722056</v>
+        <v>5107.3981156155533</v>
       </c>
       <c r="G48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$21,0,(IF($A48=VARIABLES!$B$21,0,G47)+D48)*(1+C48)-F48)</f>
-        <v>17673988.9630001</v>
+        <v>24714699.48146366</v>
       </c>
       <c r="H48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$28,0,IF($A48=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -10971,11 +10972,11 @@
       </c>
       <c r="J48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$28,0,(IF($A48=VARIABLES!$B$28,0,K47)+H48)*C48*VARIABLES!$B$32)</f>
-        <v>2512.8949745768241</v>
+        <v>3322.824884568593</v>
       </c>
       <c r="K48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$28,0,(IF($A48=VARIABLES!$B$28,0,K47)+H48)*(1+C48)-J48)</f>
-        <v>3038090.0242633801</v>
+        <v>4017295.2854434284</v>
       </c>
       <c r="L48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$35,0,IF($A48=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -10987,11 +10988,11 @@
       </c>
       <c r="N48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$35,0,(IF($A48=VARIABLES!$B$35,0,O47)+L48)*C48*VARIABLES!$B$39)</f>
-        <v>12446.638081166351</v>
+        <v>20645.212739538376</v>
       </c>
       <c r="O48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$35,0,(IF($A48=VARIABLES!$B$35,0,O47)+L48)*(1+C48)-N48)</f>
-        <v>15047985.440130116</v>
+        <v>24960062.202101897</v>
       </c>
       <c r="P48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$42,0,IF($A48=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -11003,11 +11004,11 @@
       </c>
       <c r="R48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$42,0,(IF($A48=VARIABLES!$B$42,0,S47)+P48)*C48*VARIABLES!$B$46)</f>
-        <v>330.09370580122788</v>
+        <v>449.07535578675129</v>
       </c>
       <c r="S48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$42,0,(IF($A48=VARIABLES!$B$42,0,S47)+P48)*(1+C48)-R48)</f>
-        <v>1597323.4423721416</v>
+        <v>2173075.646652089</v>
       </c>
       <c r="T48" s="16">
         <f>IF($A48&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A48-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -11023,11 +11024,11 @@
       </c>
       <c r="W48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$50,0,(IF($A48&lt;VARIABLES!$B$50+1,0,X47)+U48)*C48*VARIABLES!$B$56)</f>
-        <v>8388.7445497688805</v>
+        <v>10228.41580145093</v>
       </c>
       <c r="X48" s="7">
         <f>IF($A48&lt;VARIABLES!$B$50,0,(IF($A48&lt;VARIABLES!$B$50+1,0,X47)+U48)*(1+C48)-W48)</f>
-        <v>10141992.160670575</v>
+        <v>12366154.703954173</v>
       </c>
       <c r="Y48" s="7">
         <f t="shared" si="0"/>
@@ -11039,15 +11040,15 @@
       </c>
       <c r="AA48" s="7">
         <f t="shared" si="2"/>
-        <v>27330.776552685493</v>
+        <v>39752.926896960198</v>
       </c>
       <c r="AB48" s="17">
         <f t="shared" si="3"/>
-        <v>31268.276552685493</v>
+        <v>43690.426896960198</v>
       </c>
       <c r="AC48" s="18">
         <f t="shared" si="4"/>
-        <v>47499380.030436307</v>
+        <v>68231287.319615245</v>
       </c>
       <c r="AD48" s="7">
         <f>IF($A48=1,VARIABLES!$B$12,0)</f>
@@ -11079,15 +11080,15 @@
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="6"/>
-        <v>-19731.723447314507</v>
+        <v>-7309.5731030398019</v>
       </c>
       <c r="AL48" s="21">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM48" s="22">
         <f t="shared" si="8"/>
-        <v>184475.2063752503</v>
+        <v>292969.1016885392</v>
       </c>
     </row>
     <row r="49" spans="1:39" x14ac:dyDescent="0.2">
@@ -11112,11 +11113,11 @@
       </c>
       <c r="F49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$21,0,(IF($A49=VARIABLES!$B$21,0,G48)+D49)*C49*VARIABLES!$B$25)</f>
-        <v>3723.747700625021</v>
+        <v>5190.5623919715963</v>
       </c>
       <c r="G49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$21,0,(IF($A49=VARIABLES!$B$21,0,G48)+D49)*(1+C49)-F49)</f>
-        <v>18019215.123324476</v>
+        <v>25117131.414750554</v>
       </c>
       <c r="H49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$28,0,IF($A49=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -11128,11 +11129,11 @@
       </c>
       <c r="J49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$28,0,(IF($A49=VARIABLES!$B$28,0,K48)+H49)*C49*VARIABLES!$B$32)</f>
-        <v>2565.0750202194836</v>
+        <v>3381.0794045361904</v>
       </c>
       <c r="K49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$28,0,(IF($A49=VARIABLES!$B$28,0,K48)+H49)*(1+C49)-J49)</f>
-        <v>3101175.6994453552</v>
+        <v>4087725.000084254</v>
       </c>
       <c r="L49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$35,0,IF($A49=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -11144,11 +11145,11 @@
       </c>
       <c r="N49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$35,0,(IF($A49=VARIABLES!$B$35,0,O48)+L49)*C49*VARIABLES!$B$39)</f>
-        <v>12539.987866775096</v>
+        <v>20800.051835084916</v>
       </c>
       <c r="O49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$35,0,(IF($A49=VARIABLES!$B$35,0,O48)+L49)*(1+C49)-N49)</f>
-        <v>15160845.330931094</v>
+        <v>25147262.668617658</v>
       </c>
       <c r="P49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$42,0,IF($A49=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -11160,11 +11161,11 @@
       </c>
       <c r="R49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$42,0,(IF($A49=VARIABLES!$B$42,0,S48)+P49)*C49*VARIABLES!$B$46)</f>
-        <v>336.94238382752951</v>
+        <v>456.89075971918521</v>
       </c>
       <c r="S49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$42,0,(IF($A49=VARIABLES!$B$42,0,S48)+P49)*(1+C49)-R49)</f>
-        <v>1630464.1953414152</v>
+        <v>2210894.3862811374</v>
       </c>
       <c r="T49" s="26">
         <f>IF($A49&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A49-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -11180,11 +11181,11 @@
       </c>
       <c r="W49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$50,0,(IF($A49&lt;VARIABLES!$B$50+1,0,X48)+U49)*C49*VARIABLES!$B$56)</f>
-        <v>8676.6601338921446</v>
+        <v>10530.128919961811</v>
       </c>
       <c r="X49" s="25">
         <f>IF($A49&lt;VARIABLES!$B$50,0,(IF($A49&lt;VARIABLES!$B$50+1,0,X48)+U49)*(1+C49)-W49)</f>
-        <v>10490082.101875603</v>
+        <v>12730925.864233831</v>
       </c>
       <c r="Y49" s="25">
         <f t="shared" si="0"/>
@@ -11196,15 +11197,15 @@
       </c>
       <c r="AA49" s="25">
         <f t="shared" si="2"/>
-        <v>27842.41310533927</v>
+        <v>40358.713311273699</v>
       </c>
       <c r="AB49" s="17">
         <f t="shared" si="3"/>
-        <v>31817.41310533927</v>
+        <v>44333.713311273699</v>
       </c>
       <c r="AC49" s="18">
         <f t="shared" si="4"/>
-        <v>48401782.450917944</v>
+        <v>69293939.333967432</v>
       </c>
       <c r="AD49" s="25">
         <f>IF($A49=1,VARIABLES!$B$12,0)</f>
@@ -11236,15 +11237,15 @@
       </c>
       <c r="AK49" s="27">
         <f t="shared" si="6"/>
-        <v>-19182.58689466073</v>
+        <v>-6666.2866887263008</v>
       </c>
       <c r="AL49" s="27">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM49" s="22">
         <f t="shared" si="8"/>
-        <v>165292.61948058958</v>
+        <v>286302.81499981292</v>
       </c>
     </row>
     <row r="50" spans="1:39" x14ac:dyDescent="0.2">
@@ -11269,11 +11270,11 @@
       </c>
       <c r="F50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$21,0,(IF($A50=VARIABLES!$B$21,0,G49)+D50)*C50*VARIABLES!$B$25)</f>
-        <v>3795.6698173592663</v>
+        <v>5274.4023780730322</v>
       </c>
       <c r="G50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$21,0,(IF($A50=VARIABLES!$B$21,0,G49)+D50)*(1+C50)-F50)</f>
-        <v>18367246.246201489</v>
+        <v>25522833.107495401</v>
       </c>
       <c r="H50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$28,0,IF($A50=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -11285,11 +11286,11 @@
       </c>
       <c r="J50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$28,0,(IF($A50=VARIABLES!$B$28,0,K49)+H50)*C50*VARIABLES!$B$32)</f>
-        <v>2617.6464162044631</v>
+        <v>3439.7708334035451</v>
       </c>
       <c r="K50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$28,0,(IF($A50=VARIABLES!$B$28,0,K49)+H50)*(1+C50)-J50)</f>
-        <v>3164734.5171911954</v>
+        <v>4158682.9375848859</v>
       </c>
       <c r="L50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$35,0,IF($A50=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -11301,11 +11302,11 @@
       </c>
       <c r="N50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$35,0,(IF($A50=VARIABLES!$B$35,0,O49)+L50)*C50*VARIABLES!$B$39)</f>
-        <v>12634.037775775912</v>
+        <v>20956.052223848048</v>
       </c>
       <c r="O50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$35,0,(IF($A50=VARIABLES!$B$35,0,O49)+L50)*(1+C50)-N50)</f>
-        <v>15274551.670913076</v>
+        <v>25335867.13863229</v>
       </c>
       <c r="P50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$42,0,IF($A50=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -11317,11 +11318,11 @@
       </c>
       <c r="R50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$42,0,(IF($A50=VARIABLES!$B$42,0,S49)+P50)*C50*VARIABLES!$B$46)</f>
-        <v>343.84670736279486</v>
+        <v>464.76966380857033</v>
       </c>
       <c r="S50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$42,0,(IF($A50=VARIABLES!$B$42,0,S49)+P50)*(1+C50)-R50)</f>
-        <v>1663874.2169285642</v>
+        <v>2249020.4031696715</v>
       </c>
       <c r="T50" s="16">
         <f>IF($A50&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A50-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -11337,11 +11338,11 @@
       </c>
       <c r="W50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$50,0,(IF($A50&lt;VARIABLES!$B$50+1,0,X49)+U50)*C50*VARIABLES!$B$56)</f>
-        <v>8970.9017515630021</v>
+        <v>10838.271553528193</v>
       </c>
       <c r="X50" s="7">
         <f>IF($A50&lt;VARIABLES!$B$50,0,(IF($A50&lt;VARIABLES!$B$50+1,0,X49)+U50)*(1+C50)-W50)</f>
-        <v>10845820.21763967</v>
+        <v>13103470.308215585</v>
       </c>
       <c r="Y50" s="7">
         <f t="shared" si="0"/>
@@ -11353,15 +11354,15 @@
       </c>
       <c r="AA50" s="7">
         <f t="shared" si="2"/>
-        <v>28362.102468265439</v>
+        <v>40973.26665266139</v>
       </c>
       <c r="AB50" s="17">
         <f t="shared" si="3"/>
-        <v>32374.602468265439</v>
+        <v>44985.76665266139</v>
       </c>
       <c r="AC50" s="18">
         <f t="shared" si="4"/>
-        <v>49316226.868873991</v>
+        <v>70369873.895097822</v>
       </c>
       <c r="AD50" s="7">
         <f>IF($A50=1,VARIABLES!$B$12,0)</f>
@@ -11393,15 +11394,15 @@
       </c>
       <c r="AK50" s="21">
         <f t="shared" si="6"/>
-        <v>-18625.397531734561</v>
+        <v>-6014.2333473386097</v>
       </c>
       <c r="AL50" s="21">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM50" s="22">
         <f t="shared" si="8"/>
-        <v>146667.22194885503</v>
+        <v>280288.5816524743</v>
       </c>
     </row>
     <row r="51" spans="1:39" x14ac:dyDescent="0.2">
@@ -11426,11 +11427,11 @@
       </c>
       <c r="F51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$21,0,(IF($A51=VARIABLES!$B$21,0,G50)+D51)*C51*VARIABLES!$B$25)</f>
-        <v>3868.1763012919773</v>
+        <v>5358.9235640615425</v>
       </c>
       <c r="G51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$21,0,(IF($A51=VARIABLES!$B$21,0,G50)+D51)*(1+C51)-F51)</f>
-        <v>18718105.121951874</v>
+        <v>25931831.1264938</v>
       </c>
       <c r="H51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$28,0,IF($A51=VARIABLES!$B$28,VARIABLES!$B$29+VARIABLES!$B$30,VARIABLES!$B$30))</f>
@@ -11442,11 +11443,11 @@
       </c>
       <c r="J51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$28,0,(IF($A51=VARIABLES!$B$28,0,K50)+H51)*C51*VARIABLES!$B$32)</f>
-        <v>2670.6120976593297</v>
+        <v>3498.9024479874056</v>
       </c>
       <c r="K51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$28,0,(IF($A51=VARIABLES!$B$28,0,K50)+H51)*(1+C51)-J51)</f>
-        <v>3228770.0260701296</v>
+        <v>4230173.0596167725</v>
       </c>
       <c r="L51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$35,0,IF($A51=VARIABLES!$B$35,VARIABLES!$B$36+VARIABLES!$B$37,VARIABLES!$B$37))</f>
@@ -11458,11 +11459,11 @@
       </c>
       <c r="N51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$35,0,(IF($A51=VARIABLES!$B$35,0,O50)+L51)*C51*VARIABLES!$B$39)</f>
-        <v>12728.793059094231</v>
+        <v>21113.222615526909</v>
       </c>
       <c r="O51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$35,0,(IF($A51=VARIABLES!$B$35,0,O50)+L51)*(1+C51)-N51)</f>
-        <v>15389110.808444925</v>
+        <v>25525886.142172035</v>
       </c>
       <c r="P51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$42,0,IF($A51=VARIABLES!$B$42,VARIABLES!$B$43+VARIABLES!$B$44,VARIABLES!$B$44))</f>
@@ -11474,11 +11475,11 @@
       </c>
       <c r="R51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$42,0,(IF($A51=VARIABLES!$B$42,0,S50)+P51)*C51*VARIABLES!$B$46)</f>
-        <v>350.80712852678425</v>
+        <v>472.71258399368156</v>
       </c>
       <c r="S51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$42,0,(IF($A51=VARIABLES!$B$42,0,S50)+P51)*(1+C51)-R51)</f>
-        <v>1697555.6949411088</v>
+        <v>2287456.1939454251</v>
       </c>
       <c r="T51" s="26">
         <f>IF($A51&lt;VARIABLES!$B$50,0,MIN(VARIABLES!$B$49,INT(($A51-VARIABLES!$B$50)/VARIABLES!$B$51)+1)*VARIABLES!$B$52)</f>
@@ -11494,11 +11495,11 @@
       </c>
       <c r="W51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$50,0,(IF($A51&lt;VARIABLES!$B$50+1,0,X50)+U51)*C51*VARIABLES!$B$56)</f>
-        <v>9271.5168480330594</v>
+        <v>11152.891923512987</v>
       </c>
       <c r="X51" s="25">
         <f>IF($A51&lt;VARIABLES!$B$50,0,(IF($A51&lt;VARIABLES!$B$50+1,0,X50)+U51)*(1+C51)-W51)</f>
-        <v>11209263.869271968</v>
+        <v>13483846.3355272</v>
       </c>
       <c r="Y51" s="25">
         <f t="shared" si="0"/>
@@ -11510,15 +11511,15 @@
       </c>
       <c r="AA51" s="25">
         <f t="shared" si="2"/>
-        <v>28889.905434605382</v>
+        <v>41596.653135082524</v>
       </c>
       <c r="AB51" s="17">
         <f t="shared" si="3"/>
-        <v>32939.905434605382</v>
+        <v>45646.653135082524</v>
       </c>
       <c r="AC51" s="18">
         <f t="shared" si="4"/>
-        <v>50242805.52068001</v>
+        <v>71459192.857755229</v>
       </c>
       <c r="AD51" s="25">
         <f>IF($A51=1,VARIABLES!$B$12,0)</f>
@@ -11530,7 +11531,7 @@
       </c>
       <c r="AF51" s="25">
         <f>IF(MOD($A51,12)=0,AC51*VARIABLES!$B$16,0)</f>
-        <v>125607.01380170003</v>
+        <v>178647.98214438808</v>
       </c>
       <c r="AG51" s="25">
         <f>VARIABLES!$B$17</f>
@@ -11542,7 +11543,7 @@
       </c>
       <c r="AI51" s="19">
         <f t="shared" si="5"/>
-        <v>179607.01380170003</v>
+        <v>232647.98214438808</v>
       </c>
       <c r="AJ51" s="20">
         <f>IF($A51&lt;VARIABLES!$B$7,VARIABLES!$B$9,0)</f>
@@ -11550,19 +11551,19 @@
       </c>
       <c r="AK51" s="27">
         <f t="shared" si="6"/>
-        <v>-146667.10836709465</v>
+        <v>-187001.32900930557</v>
       </c>
       <c r="AL51" s="27">
         <f t="shared" si="7"/>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM51" s="22">
         <f t="shared" si="8"/>
-        <v>0.11358176037902012</v>
+        <v>93287.252643168729</v>
       </c>
     </row>
     <row r="52" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="37" t="s">
         <v>111</v>
       </c>
       <c r="B52" s="30"/>
@@ -11576,15 +11577,15 @@
       </c>
       <c r="AA52" s="28">
         <f>SUM(AA4:AA51)</f>
-        <v>1939101.3982898265</v>
+        <v>3629501.1448412449</v>
       </c>
       <c r="AB52" s="28">
         <f>SUM(AB4:AB51)</f>
-        <v>2129788.8982898267</v>
+        <v>3820188.6448412449</v>
       </c>
       <c r="AC52" s="28">
         <f>AC51</f>
-        <v>50242805.52068001</v>
+        <v>71459192.857755229</v>
       </c>
       <c r="AD52" s="28">
         <f t="shared" ref="AD52:AK52" si="9">SUM(AD4:AD51)</f>
@@ -11596,7 +11597,7 @@
       </c>
       <c r="AF52" s="28">
         <f t="shared" si="9"/>
-        <v>313128.22335241991</v>
+        <v>436571.25065008667</v>
       </c>
       <c r="AG52" s="28">
         <f t="shared" si="9"/>
@@ -11608,7 +11609,7 @@
       </c>
       <c r="AI52" s="28">
         <f t="shared" si="9"/>
-        <v>2727128.2233524197</v>
+        <v>2850571.2506500864</v>
       </c>
       <c r="AJ52" s="28">
         <f t="shared" si="9"/>
@@ -11616,19 +11617,19 @@
       </c>
       <c r="AK52" s="28">
         <f t="shared" si="9"/>
-        <v>-978222.32506259379</v>
+        <v>588734.39419115754</v>
       </c>
       <c r="AL52" s="28">
         <f>AL51</f>
-        <v>-597339.43864435412</v>
+        <v>876330.14154798852</v>
       </c>
       <c r="AM52" s="28">
         <f>AM51</f>
-        <v>0.11358176037902012</v>
+        <v>93287.252643168729</v>
       </c>
     </row>
-    <row r="54" spans="1:39" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="37" t="s">
+    <row r="54" spans="1:39" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="29" t="s">
         <v>119</v>
       </c>
       <c r="B54" s="30"/>
